--- a/research/traditional_assets/database/data/morocco/morocco_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_oil_gas_distribution.xlsx
@@ -617,7 +617,7 @@
         <v>48.1</v>
       </c>
       <c r="N2">
-        <v>0.02441996243082703</v>
+        <v>0.03143996339630041</v>
       </c>
       <c r="O2">
         <v>0.6784203102961918</v>
@@ -626,7 +626,7 @@
         <v>48.1</v>
       </c>
       <c r="Q2">
-        <v>0.02441996243082703</v>
+        <v>0.03143996339630041</v>
       </c>
       <c r="R2">
         <v>0.6784203102961918</v>
@@ -641,16 +641,16 @@
         <v>60.6</v>
       </c>
       <c r="V2">
-        <v>0.03076610651368229</v>
+        <v>0.03961043205438264</v>
       </c>
       <c r="W2">
         <v>0.268662372110648</v>
       </c>
       <c r="X2">
-        <v>0.06563327040081483</v>
+        <v>0.1088568580441495</v>
       </c>
       <c r="Y2">
-        <v>0.2030291017098332</v>
+        <v>0.1598055140664986</v>
       </c>
       <c r="Z2">
         <v>2.527114967462039</v>
@@ -659,10 +659,10 @@
         <v>0.2430234872411387</v>
       </c>
       <c r="AB2">
-        <v>0.06339462110107441</v>
+        <v>0.1043841996434637</v>
       </c>
       <c r="AC2">
-        <v>0.1796288661400643</v>
+        <v>0.138639287597675</v>
       </c>
       <c r="AD2">
         <v>135.2</v>
@@ -677,13 +677,13 @@
         <v>74.59999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.06423107986127606</v>
+        <v>0.08119632454507235</v>
       </c>
       <c r="AI2">
         <v>0.304093567251462</v>
       </c>
       <c r="AJ2">
-        <v>0.03649170865332876</v>
+        <v>0.04649423496416329</v>
       </c>
       <c r="AK2">
         <v>0.1942708333333333</v>
@@ -751,7 +751,7 @@
         <v>48.1</v>
       </c>
       <c r="N3">
-        <v>0.02441996243082703</v>
+        <v>0.03143996339630041</v>
       </c>
       <c r="O3">
         <v>0.6784203102961918</v>
@@ -760,7 +760,7 @@
         <v>48.1</v>
       </c>
       <c r="Q3">
-        <v>0.02441996243082703</v>
+        <v>0.03143996339630041</v>
       </c>
       <c r="R3">
         <v>0.6784203102961918</v>
@@ -775,16 +775,16 @@
         <v>60.6</v>
       </c>
       <c r="V3">
-        <v>0.03076610651368229</v>
+        <v>0.03961043205438264</v>
       </c>
       <c r="W3">
         <v>0.268662372110648</v>
       </c>
       <c r="X3">
-        <v>0.06563327040081483</v>
+        <v>0.1088568580441495</v>
       </c>
       <c r="Y3">
-        <v>0.2030291017098332</v>
+        <v>0.1598055140664986</v>
       </c>
       <c r="Z3">
         <v>2.527114967462039</v>
@@ -793,10 +793,10 @@
         <v>0.2430234872411387</v>
       </c>
       <c r="AB3">
-        <v>0.06339462110107441</v>
+        <v>0.1043841996434637</v>
       </c>
       <c r="AC3">
-        <v>0.1796288661400643</v>
+        <v>0.138639287597675</v>
       </c>
       <c r="AD3">
         <v>135.2</v>
@@ -811,13 +811,13 @@
         <v>74.59999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.06423107986127606</v>
+        <v>0.08119632454507235</v>
       </c>
       <c r="AI3">
         <v>0.304093567251462</v>
       </c>
       <c r="AJ3">
-        <v>0.03649170865332876</v>
+        <v>0.04649423496416329</v>
       </c>
       <c r="AK3">
         <v>0.1942708333333333</v>
@@ -1090,40 +1090,40 @@
         </is>
       </c>
       <c r="E2">
-        <v>0.0642310798612761</v>
+        <v>0.08119632454507229</v>
       </c>
       <c r="F2">
-        <v>0.38</v>
+        <v>0.24</v>
       </c>
       <c r="G2">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="H2">
-        <v>1496.50925475647</v>
+        <v>1388.49462967415</v>
       </c>
       <c r="I2">
-        <v>2044.3</v>
+        <v>1604.5</v>
       </c>
       <c r="J2">
-        <v>2235.77125475647</v>
+        <v>1727.51862967415</v>
       </c>
       <c r="K2">
         <v>135.2</v>
       </c>
       <c r="L2">
-        <v>799.862</v>
+        <v>399.624</v>
       </c>
       <c r="M2">
-        <v>0.0633946211010744</v>
+        <v>0.104384199643464</v>
       </c>
       <c r="N2">
-        <v>0.0592586739729689</v>
+        <v>0.09971387179296939</v>
       </c>
       <c r="O2">
-        <v>0.0307802163251964</v>
+        <v>0.0537723646788991</v>
       </c>
       <c r="P2">
-        <v>0.0192951157058568</v>
+        <v>0.03795</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -1136,19 +1136,19 @@
         </is>
       </c>
       <c r="S2">
-        <v>0.06563327040081481</v>
+        <v>0.108856858044149</v>
       </c>
       <c r="T2">
-        <v>0.083752467749586</v>
+        <v>0.11921825235917</v>
       </c>
       <c r="U2">
-        <v>0.780883564399268</v>
+        <v>0.684475243413075</v>
       </c>
       <c r="V2">
-        <v>1.06087698848476</v>
+        <v>0.785708985460189</v>
       </c>
       <c r="W2">
-        <v>4.569172292674102</v>
+        <v>4.649825381312979</v>
       </c>
       <c r="X2">
         <v>0</v>
@@ -1157,19 +1157,19 @@
         <v>0</v>
       </c>
       <c r="Z2">
-        <v>0.0151</v>
+        <v>0.0388</v>
       </c>
       <c r="AA2">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="AB2">
-        <v>0.06471293891258929</v>
+        <v>0.1023511934410034</v>
       </c>
       <c r="AC2">
-        <v>0.04460900916695127</v>
+        <v>0.0779309633027523</v>
       </c>
       <c r="AD2">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.06334816368708154</v>
+        <v>0.1048305442879964</v>
       </c>
       <c r="C2">
-        <v>2106.868424996267</v>
+        <v>1654.254110572994</v>
       </c>
       <c r="D2">
-        <v>2046.268424996267</v>
+        <v>1593.654110572994</v>
       </c>
       <c r="E2">
         <v>-135.2</v>
@@ -1376,7 +1376,7 @@
         <v>60.6</v>
       </c>
       <c r="H2">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1397,7 +1397,7 @@
         <v>102.2</v>
       </c>
       <c r="O2">
-        <v>31.682</v>
+        <v>31.68200000000001</v>
       </c>
       <c r="P2">
         <v>70.518</v>
@@ -1409,19 +1409,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.06334816368708154</v>
+        <v>0.1048305442879964</v>
       </c>
       <c r="T2">
-        <v>0.7455721297444476</v>
+        <v>0.6451370234979946</v>
       </c>
       <c r="U2">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V2">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W2">
-        <v>0.015014622037056</v>
+        <v>0.031533</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1440,25 +1440,25 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.06319774060002215</v>
+        <v>0.1045531796007036</v>
       </c>
       <c r="C3">
-        <v>2092.219019022934</v>
+        <v>1644.325574440387</v>
       </c>
       <c r="D3">
-        <v>2052.668019022934</v>
+        <v>1600.376574440387</v>
       </c>
       <c r="E3">
-        <v>-114.151</v>
+        <v>-118.549</v>
       </c>
       <c r="F3">
-        <v>21.049</v>
+        <v>16.651</v>
       </c>
       <c r="G3">
         <v>60.6</v>
       </c>
       <c r="H3">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1473,37 +1473,37 @@
         <v>102.2</v>
       </c>
       <c r="M3">
-        <v>0.4580330134173793</v>
+        <v>0.7609507000000002</v>
       </c>
       <c r="N3">
-        <v>101.7419669865826</v>
+        <v>101.4390493</v>
       </c>
       <c r="O3">
-        <v>31.54000976584061</v>
+        <v>31.44610528300001</v>
       </c>
       <c r="P3">
-        <v>70.20195722074202</v>
+        <v>69.992944017</v>
       </c>
       <c r="Q3">
-        <v>108.001957220742</v>
+        <v>107.792944017</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.06368443876732484</v>
+        <v>0.1052907571724279</v>
       </c>
       <c r="T3">
-        <v>0.7507685415578181</v>
+        <v>0.649633433055708</v>
       </c>
       <c r="U3">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V3">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W3">
-        <v>0.015014622037056</v>
+        <v>0.031533</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>223.1280213569911</v>
+        <v>134.3056784099154</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1522,25 +1522,25 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.06304731751296276</v>
+        <v>0.1042758149134108</v>
       </c>
       <c r="C4">
-        <v>2077.609767399807</v>
+        <v>1634.453992897528</v>
       </c>
       <c r="D4">
-        <v>2059.107767399807</v>
+        <v>1607.155992897528</v>
       </c>
       <c r="E4">
-        <v>-93.10199999999998</v>
+        <v>-101.898</v>
       </c>
       <c r="F4">
-        <v>42.09800000000001</v>
+        <v>33.30200000000001</v>
       </c>
       <c r="G4">
         <v>60.6</v>
       </c>
       <c r="H4">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1555,37 +1555,37 @@
         <v>102.2</v>
       </c>
       <c r="M4">
-        <v>0.9160660268347587</v>
+        <v>1.5219014</v>
       </c>
       <c r="N4">
-        <v>101.2839339731652</v>
+        <v>100.6780986</v>
       </c>
       <c r="O4">
-        <v>31.39801953168122</v>
+        <v>31.210210566</v>
       </c>
       <c r="P4">
-        <v>69.88591444148402</v>
+        <v>69.467888034</v>
       </c>
       <c r="Q4">
-        <v>107.685914441484</v>
+        <v>107.267888034</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.0640275766043078</v>
+        <v>0.1057603621565416</v>
       </c>
       <c r="T4">
-        <v>0.7560710025918695</v>
+        <v>0.6542216060737828</v>
       </c>
       <c r="U4">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V4">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W4">
-        <v>0.015014622037056</v>
+        <v>0.031533</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>111.5640106784955</v>
+        <v>67.15283920495767</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1604,25 +1604,25 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.06289689442590335</v>
+        <v>0.103998450226118</v>
       </c>
       <c r="C5">
-        <v>2063.041049239885</v>
+        <v>1624.640092826358</v>
       </c>
       <c r="D5">
-        <v>2065.588049239885</v>
+        <v>1613.993092826358</v>
       </c>
       <c r="E5">
-        <v>-72.053</v>
+        <v>-85.24699999999999</v>
       </c>
       <c r="F5">
-        <v>63.147</v>
+        <v>49.953</v>
       </c>
       <c r="G5">
         <v>60.6</v>
       </c>
       <c r="H5">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1637,37 +1637,37 @@
         <v>102.2</v>
       </c>
       <c r="M5">
-        <v>1.374099040252138</v>
+        <v>2.2828521</v>
       </c>
       <c r="N5">
-        <v>100.8259009597479</v>
+        <v>99.9171479</v>
       </c>
       <c r="O5">
-        <v>31.25602929752184</v>
+        <v>30.97431584900001</v>
       </c>
       <c r="P5">
-        <v>69.56987166222603</v>
+        <v>68.942832051</v>
       </c>
       <c r="Q5">
-        <v>107.369871662226</v>
+        <v>106.742832051</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.06437778944823884</v>
+        <v>0.1062396497176474</v>
       </c>
       <c r="T5">
-        <v>0.7614827927194064</v>
+        <v>0.6589043805973848</v>
       </c>
       <c r="U5">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V5">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W5">
-        <v>0.015014622037056</v>
+        <v>0.031533</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>74.37600711899704</v>
+        <v>44.76855946997179</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1686,25 +1686,25 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.06274647133884396</v>
+        <v>0.1037210855388252</v>
       </c>
       <c r="C6">
-        <v>2048.513248443704</v>
+        <v>1614.884613530749</v>
       </c>
       <c r="D6">
-        <v>2072.109248443704</v>
+        <v>1620.888613530749</v>
       </c>
       <c r="E6">
-        <v>-51.00399999999998</v>
+        <v>-68.59599999999998</v>
       </c>
       <c r="F6">
-        <v>84.19600000000001</v>
+        <v>66.60400000000001</v>
       </c>
       <c r="G6">
         <v>60.6</v>
       </c>
       <c r="H6">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1719,37 +1719,37 @@
         <v>102.2</v>
       </c>
       <c r="M6">
-        <v>1.832132053669517</v>
+        <v>3.043802800000001</v>
       </c>
       <c r="N6">
-        <v>100.3678679463305</v>
+        <v>99.15619720000001</v>
       </c>
       <c r="O6">
-        <v>31.11403906336245</v>
+        <v>30.73842113200001</v>
       </c>
       <c r="P6">
-        <v>69.25382888296804</v>
+        <v>68.41777606799999</v>
       </c>
       <c r="Q6">
-        <v>107.053828882968</v>
+        <v>106.217776068</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.06473529839308513</v>
+        <v>0.1067289224362763</v>
       </c>
       <c r="T6">
-        <v>0.7670073284746005</v>
+        <v>0.663684712923562</v>
       </c>
       <c r="U6">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V6">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W6">
-        <v>0.015014622037056</v>
+        <v>0.031533</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>55.78200533924777</v>
+        <v>33.57641960247884</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1768,25 +1768,25 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.06259604825178458</v>
+        <v>0.1034437208515324</v>
       </c>
       <c r="C7">
-        <v>2034.026753775155</v>
+        <v>1605.188307003003</v>
       </c>
       <c r="D7">
-        <v>2078.671753775155</v>
+        <v>1627.843307003003</v>
       </c>
       <c r="E7">
-        <v>-29.95499999999998</v>
+        <v>-51.94499999999998</v>
       </c>
       <c r="F7">
-        <v>105.245</v>
+        <v>83.25500000000001</v>
       </c>
       <c r="G7">
         <v>60.6</v>
       </c>
       <c r="H7">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1801,37 +1801,37 @@
         <v>102.2</v>
       </c>
       <c r="M7">
-        <v>2.290165067086896</v>
+        <v>3.804753500000001</v>
       </c>
       <c r="N7">
-        <v>99.9098349329131</v>
+        <v>98.3952465</v>
       </c>
       <c r="O7">
-        <v>30.97204882920306</v>
+        <v>30.50252641500001</v>
       </c>
       <c r="P7">
-        <v>68.93778610371004</v>
+        <v>67.89272008499999</v>
       </c>
       <c r="Q7">
-        <v>106.73778610371</v>
+        <v>105.692720085</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.06510033384203345</v>
+        <v>0.107228495633192</v>
       </c>
       <c r="T7">
-        <v>0.7726481702456934</v>
+        <v>0.6685656838250271</v>
       </c>
       <c r="U7">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V7">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W7">
-        <v>0.015014622037056</v>
+        <v>0.031533</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>44.62560427139822</v>
+        <v>26.86113568198307</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1850,25 +1850,25 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.06244562516472518</v>
+        <v>0.1031663561642396</v>
       </c>
       <c r="C8">
-        <v>2019.58195893874</v>
+        <v>1595.551938197232</v>
       </c>
       <c r="D8">
-        <v>2085.27595893874</v>
+        <v>1634.857938197232</v>
       </c>
       <c r="E8">
-        <v>-8.905999999999992</v>
+        <v>-35.29399999999998</v>
       </c>
       <c r="F8">
-        <v>126.294</v>
+        <v>99.90600000000001</v>
       </c>
       <c r="G8">
         <v>60.6</v>
       </c>
       <c r="H8">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1883,37 +1883,37 @@
         <v>102.2</v>
       </c>
       <c r="M8">
-        <v>2.748198080504276</v>
+        <v>4.565704200000001</v>
       </c>
       <c r="N8">
-        <v>99.45180191949572</v>
+        <v>97.6342958</v>
       </c>
       <c r="O8">
-        <v>30.83005859504367</v>
+        <v>30.266631698</v>
       </c>
       <c r="P8">
-        <v>68.62174332445204</v>
+        <v>67.36766410199999</v>
       </c>
       <c r="Q8">
-        <v>106.421743324452</v>
+        <v>105.167664102</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.06547313600266151</v>
+        <v>0.1077386980470634</v>
       </c>
       <c r="T8">
-        <v>0.7784090299268095</v>
+        <v>0.6735505051712042</v>
       </c>
       <c r="U8">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V8">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W8">
-        <v>0.015014622037056</v>
+        <v>0.031533</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.18800355949852</v>
+        <v>22.3842797349859</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1932,25 +1932,25 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.06229520207766579</v>
+        <v>0.1028889914769469</v>
       </c>
       <c r="C9">
-        <v>2005.179262658302</v>
+        <v>1585.976285309838</v>
       </c>
       <c r="D9">
-        <v>2091.922262658302</v>
+        <v>1641.933285309838</v>
       </c>
       <c r="E9">
-        <v>12.14300000000003</v>
+        <v>-18.64299999999997</v>
       </c>
       <c r="F9">
-        <v>147.343</v>
+        <v>116.557</v>
       </c>
       <c r="G9">
         <v>60.6</v>
       </c>
       <c r="H9">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1965,37 +1965,37 @@
         <v>102.2</v>
       </c>
       <c r="M9">
-        <v>3.206231093921655</v>
+        <v>5.326654900000001</v>
       </c>
       <c r="N9">
-        <v>98.99376890607834</v>
+        <v>96.87334509999999</v>
       </c>
       <c r="O9">
-        <v>30.68806836088429</v>
+        <v>30.030736981</v>
       </c>
       <c r="P9">
-        <v>68.30570054519406</v>
+        <v>66.84260811899999</v>
       </c>
       <c r="Q9">
-        <v>106.1057005451941</v>
+        <v>104.642608119</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.06585395541405578</v>
+        <v>0.1082598725558568</v>
       </c>
       <c r="T9">
-        <v>0.7842937790634336</v>
+        <v>0.6786425269764389</v>
       </c>
       <c r="U9">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V9">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W9">
-        <v>0.015014622037056</v>
+        <v>0.031533</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.8754316224273</v>
+        <v>19.18652548713077</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2014,25 +2014,25 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.0621447789906064</v>
+        <v>0.1026116267896541</v>
       </c>
       <c r="C10">
-        <v>1990.819068757278</v>
+        <v>1576.462140067306</v>
       </c>
       <c r="D10">
-        <v>2098.611068757278</v>
+        <v>1649.070140067306</v>
       </c>
       <c r="E10">
-        <v>33.19200000000004</v>
+        <v>-1.991999999999962</v>
       </c>
       <c r="F10">
-        <v>168.392</v>
+        <v>133.208</v>
       </c>
       <c r="G10">
         <v>60.6</v>
       </c>
       <c r="H10">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -2047,37 +2047,37 @@
         <v>102.2</v>
       </c>
       <c r="M10">
-        <v>3.664264107339035</v>
+        <v>6.087605600000002</v>
       </c>
       <c r="N10">
-        <v>98.53573589266097</v>
+        <v>96.1123944</v>
       </c>
       <c r="O10">
-        <v>30.5460781267249</v>
+        <v>29.794842264</v>
       </c>
       <c r="P10">
-        <v>67.98965776593607</v>
+        <v>66.31755213599999</v>
       </c>
       <c r="Q10">
-        <v>105.7896577659361</v>
+        <v>104.117552136</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.06624305350830643</v>
+        <v>0.1087923769452762</v>
       </c>
       <c r="T10">
-        <v>0.7903064575291145</v>
+        <v>0.6838452449078744</v>
       </c>
       <c r="U10">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V10">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W10">
-        <v>0.015014622037056</v>
+        <v>0.031533</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.89100266962388</v>
+        <v>16.78820980123942</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2096,25 +2096,25 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.06199435590354701</v>
+        <v>0.1023342621023613</v>
       </c>
       <c r="C11">
-        <v>1976.501786240481</v>
+        <v>1567.010308021547</v>
       </c>
       <c r="D11">
-        <v>2105.342786240481</v>
+        <v>1656.269308021547</v>
       </c>
       <c r="E11">
-        <v>54.24100000000001</v>
+        <v>14.65900000000002</v>
       </c>
       <c r="F11">
-        <v>189.441</v>
+        <v>149.859</v>
       </c>
       <c r="G11">
         <v>60.6</v>
       </c>
       <c r="H11">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2129,37 +2129,37 @@
         <v>102.2</v>
       </c>
       <c r="M11">
-        <v>4.122297120756413</v>
+        <v>6.848556300000001</v>
       </c>
       <c r="N11">
-        <v>98.07770287924359</v>
+        <v>95.3514437</v>
       </c>
       <c r="O11">
-        <v>30.40408789256551</v>
+        <v>29.55894754700001</v>
       </c>
       <c r="P11">
-        <v>67.67361498667807</v>
+        <v>65.792496153</v>
       </c>
       <c r="Q11">
-        <v>105.4736149866781</v>
+        <v>103.592496153</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.06664070320902414</v>
+        <v>0.1093365847278695</v>
       </c>
       <c r="T11">
-        <v>0.796451282774261</v>
+        <v>0.6891623082883523</v>
       </c>
       <c r="U11">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V11">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W11">
-        <v>0.015014622037056</v>
+        <v>0.031533</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.79200237299901</v>
+        <v>14.92285315665726</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2178,25 +2178,25 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.06184393281648762</v>
+        <v>0.1020568974150685</v>
       </c>
       <c r="C12">
-        <v>1962.227829377476</v>
+        <v>1557.621608852992</v>
       </c>
       <c r="D12">
-        <v>2112.117829377476</v>
+        <v>1663.531608852992</v>
       </c>
       <c r="E12">
-        <v>75.29000000000002</v>
+        <v>31.31000000000003</v>
       </c>
       <c r="F12">
-        <v>210.49</v>
+        <v>166.51</v>
       </c>
       <c r="G12">
         <v>60.6</v>
       </c>
       <c r="H12">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2211,37 +2211,37 @@
         <v>102.2</v>
       </c>
       <c r="M12">
-        <v>4.580330134173793</v>
+        <v>7.609507000000002</v>
       </c>
       <c r="N12">
-        <v>97.61966986582621</v>
+        <v>94.590493</v>
       </c>
       <c r="O12">
-        <v>30.26209765840613</v>
+        <v>29.32305283</v>
       </c>
       <c r="P12">
-        <v>67.35757220742008</v>
+        <v>65.26744016999999</v>
       </c>
       <c r="Q12">
-        <v>105.1575722074201</v>
+        <v>103.06744017</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.06704718956975779</v>
+        <v>0.1098928860167428</v>
       </c>
       <c r="T12">
-        <v>0.802732659691522</v>
+        <v>0.6945975286328409</v>
       </c>
       <c r="U12">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V12">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W12">
-        <v>0.015014622037056</v>
+        <v>0.031533</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.31280213569911</v>
+        <v>13.43056784099154</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2260,25 +2260,25 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.06169350972942821</v>
+        <v>0.1019009727277757</v>
       </c>
       <c r="C13">
-        <v>1947.997617787561</v>
+        <v>1545.081253026911</v>
       </c>
       <c r="D13">
-        <v>2118.936617787561</v>
+        <v>1667.642253026911</v>
       </c>
       <c r="E13">
-        <v>96.33900000000003</v>
+        <v>47.96100000000004</v>
       </c>
       <c r="F13">
-        <v>231.539</v>
+        <v>183.161</v>
       </c>
       <c r="G13">
         <v>60.6</v>
       </c>
       <c r="H13">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -2293,45 +2293,45 @@
         <v>102.2</v>
       </c>
       <c r="M13">
-        <v>5.038363147591173</v>
+        <v>8.663515300000002</v>
       </c>
       <c r="N13">
-        <v>97.16163685240883</v>
+        <v>93.5364847</v>
       </c>
       <c r="O13">
-        <v>30.12010742424674</v>
+        <v>28.996310257</v>
       </c>
       <c r="P13">
-        <v>67.04152942816209</v>
+        <v>64.540174443</v>
       </c>
       <c r="Q13">
-        <v>104.8415294281621</v>
+        <v>102.340174443</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.06746281045545174</v>
+        <v>0.1104616884581749</v>
       </c>
       <c r="T13">
-        <v>0.8091551911462493</v>
+        <v>0.7001548887603517</v>
       </c>
       <c r="U13">
-        <v>0.02176032179283478</v>
+        <v>0.0473</v>
       </c>
       <c r="V13">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W13">
-        <v>0.015014622037056</v>
+        <v>0.032637</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>20.28436557790828</v>
+        <v>11.79659716189339</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2342,25 +2342,25 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.06154308664236882</v>
+        <v>0.1016346480404829</v>
       </c>
       <c r="C14">
-        <v>1933.811576526397</v>
+        <v>1535.498555554324</v>
       </c>
       <c r="D14">
-        <v>2125.799576526397</v>
+        <v>1674.710555554324</v>
       </c>
       <c r="E14">
-        <v>117.388</v>
+        <v>64.61200000000002</v>
       </c>
       <c r="F14">
-        <v>252.588</v>
+        <v>199.812</v>
       </c>
       <c r="G14">
         <v>60.6</v>
       </c>
       <c r="H14">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -2375,45 +2375,45 @@
         <v>102.2</v>
       </c>
       <c r="M14">
-        <v>5.496396161008551</v>
+        <v>9.4511076</v>
       </c>
       <c r="N14">
-        <v>96.70360383899146</v>
+        <v>92.7488924</v>
       </c>
       <c r="O14">
-        <v>29.97811719008735</v>
+        <v>28.75215664400001</v>
       </c>
       <c r="P14">
-        <v>66.72548664890411</v>
+        <v>63.99673575599999</v>
       </c>
       <c r="Q14">
-        <v>104.5254866489041</v>
+        <v>101.796735756</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.06788787727036602</v>
+        <v>0.1110434182278215</v>
       </c>
       <c r="T14">
-        <v>0.8157236892249479</v>
+        <v>0.705838552527124</v>
       </c>
       <c r="U14">
-        <v>0.02176032179283478</v>
+        <v>0.0473</v>
       </c>
       <c r="V14">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W14">
-        <v>0.015014622037056</v>
+        <v>0.032637</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>18.59400177974926</v>
+        <v>10.81354739840228</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2424,25 +2424,25 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.06139266355530944</v>
+        <v>0.1017091833531901</v>
       </c>
       <c r="C15">
-        <v>1919.670136174344</v>
+        <v>1516.863344850912</v>
       </c>
       <c r="D15">
-        <v>2132.707136174344</v>
+        <v>1672.726344850912</v>
       </c>
       <c r="E15">
-        <v>138.437</v>
+        <v>81.26300000000003</v>
       </c>
       <c r="F15">
-        <v>273.637</v>
+        <v>216.463</v>
       </c>
       <c r="G15">
         <v>60.6</v>
       </c>
       <c r="H15">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -2457,45 +2457,45 @@
         <v>102.2</v>
       </c>
       <c r="M15">
-        <v>5.954429174425931</v>
+        <v>11.0612593</v>
       </c>
       <c r="N15">
-        <v>96.24557082557408</v>
+        <v>91.1387407</v>
       </c>
       <c r="O15">
-        <v>29.83612695592796</v>
+        <v>28.253009617</v>
       </c>
       <c r="P15">
-        <v>66.40944386964611</v>
+        <v>62.885731083</v>
       </c>
       <c r="Q15">
-        <v>104.2094438696461</v>
+        <v>100.685731083</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.06832271573619789</v>
+        <v>0.1116385210956208</v>
       </c>
       <c r="T15">
-        <v>0.8224431872594787</v>
+        <v>0.7116528752310638</v>
       </c>
       <c r="U15">
-        <v>0.02176032179283478</v>
+        <v>0.0511</v>
       </c>
       <c r="V15">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W15">
-        <v>0.015014622037056</v>
+        <v>0.035259</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>17.16369395053778</v>
+        <v>9.239454317827988</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2506,25 +2506,25 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.06124224046825004</v>
+        <v>0.1014690786658973</v>
       </c>
       <c r="C16">
-        <v>1905.573732926504</v>
+        <v>1506.621078543935</v>
       </c>
       <c r="D16">
-        <v>2139.659732926505</v>
+        <v>1679.135078543935</v>
       </c>
       <c r="E16">
-        <v>159.486</v>
+        <v>97.91400000000004</v>
       </c>
       <c r="F16">
-        <v>294.686</v>
+        <v>233.114</v>
       </c>
       <c r="G16">
         <v>60.6</v>
       </c>
       <c r="H16">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -2539,45 +2539,45 @@
         <v>102.2</v>
       </c>
       <c r="M16">
-        <v>6.41246218784331</v>
+        <v>11.9121254</v>
       </c>
       <c r="N16">
-        <v>95.7875378121567</v>
+        <v>90.28787460000001</v>
       </c>
       <c r="O16">
-        <v>29.69413672176858</v>
+        <v>27.98924112600001</v>
       </c>
       <c r="P16">
-        <v>66.09340109038813</v>
+        <v>62.298633474</v>
       </c>
       <c r="Q16">
-        <v>103.8934010903881</v>
+        <v>100.098633474</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.06876766672449093</v>
+        <v>0.1122474635649969</v>
       </c>
       <c r="T16">
-        <v>0.8293189526901611</v>
+        <v>0.7176024147420716</v>
       </c>
       <c r="U16">
-        <v>0.02176032179283478</v>
+        <v>0.0511</v>
       </c>
       <c r="V16">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W16">
-        <v>0.015014622037056</v>
+        <v>0.035259</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>15.93771581121365</v>
+        <v>8.579493295125991</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2588,25 +2588,25 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.06109181738119065</v>
+        <v>0.1012289739786045</v>
       </c>
       <c r="C17">
-        <v>1891.522808684544</v>
+        <v>1496.428108802358</v>
       </c>
       <c r="D17">
-        <v>2146.657808684544</v>
+        <v>1685.593108802358</v>
       </c>
       <c r="E17">
-        <v>180.535</v>
+        <v>114.565</v>
       </c>
       <c r="F17">
-        <v>315.735</v>
+        <v>249.765</v>
       </c>
       <c r="G17">
         <v>60.6</v>
       </c>
       <c r="H17">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -2621,45 +2621,45 @@
         <v>102.2</v>
       </c>
       <c r="M17">
-        <v>6.870495201260689</v>
+        <v>12.7629915</v>
       </c>
       <c r="N17">
-        <v>95.32950479873931</v>
+        <v>89.4370085</v>
       </c>
       <c r="O17">
-        <v>29.55214648760919</v>
+        <v>27.72547263500001</v>
       </c>
       <c r="P17">
-        <v>65.77735831113011</v>
+        <v>61.711535865</v>
       </c>
       <c r="Q17">
-        <v>103.5773583111301</v>
+        <v>99.511535865</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.06922308714780265</v>
+        <v>0.1128707340924759</v>
       </c>
       <c r="T17">
-        <v>0.8363565008368599</v>
+        <v>0.7236919434180445</v>
       </c>
       <c r="U17">
-        <v>0.02176032179283478</v>
+        <v>0.0511</v>
       </c>
       <c r="V17">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W17">
-        <v>0.015014622037056</v>
+        <v>0.035259</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>14.87520142379941</v>
+        <v>8.007527075450923</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2670,25 +2670,25 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.06094139429413126</v>
+        <v>0.1011986292913117</v>
       </c>
       <c r="C18">
-        <v>1877.51781115032</v>
+        <v>1480.596819048727</v>
       </c>
       <c r="D18">
-        <v>2153.70181115032</v>
+        <v>1686.412819048727</v>
       </c>
       <c r="E18">
-        <v>201.5840000000001</v>
+        <v>131.2160000000001</v>
       </c>
       <c r="F18">
-        <v>336.784</v>
+        <v>266.4160000000001</v>
       </c>
       <c r="G18">
         <v>60.6</v>
       </c>
       <c r="H18">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -2703,45 +2703,45 @@
         <v>102.2</v>
       </c>
       <c r="M18">
-        <v>7.328528214678069</v>
+        <v>14.120048</v>
       </c>
       <c r="N18">
-        <v>94.87147178532193</v>
+        <v>88.07995199999999</v>
       </c>
       <c r="O18">
-        <v>29.4101562534498</v>
+        <v>27.30478512</v>
       </c>
       <c r="P18">
-        <v>65.46131553187213</v>
+        <v>60.77516687999999</v>
       </c>
       <c r="Q18">
-        <v>103.2613155318721</v>
+        <v>98.57516687999998</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.06968935091452655</v>
+        <v>0.1135088443944187</v>
       </c>
       <c r="T18">
-        <v>0.843561609653718</v>
+        <v>0.7299264608720167</v>
       </c>
       <c r="U18">
-        <v>0.02176032179283478</v>
+        <v>0.05300000000000001</v>
       </c>
       <c r="V18">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W18">
-        <v>0.015014622037056</v>
+        <v>0.03657</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>13.94550133481194</v>
+        <v>7.237935735062655</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2752,25 +2752,25 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.06097698448000032</v>
+        <v>0.100971634604019</v>
       </c>
       <c r="C19">
-        <v>1854.79802461903</v>
+        <v>1470.103076340492</v>
       </c>
       <c r="D19">
-        <v>2152.03102461903</v>
+        <v>1692.570076340492</v>
       </c>
       <c r="E19">
-        <v>222.633</v>
+        <v>147.8670000000001</v>
       </c>
       <c r="F19">
-        <v>357.833</v>
+        <v>283.0670000000001</v>
       </c>
       <c r="G19">
         <v>60.6</v>
       </c>
       <c r="H19">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -2785,45 +2785,45 @@
         <v>102.2</v>
       </c>
       <c r="M19">
-        <v>8.354009544308651</v>
+        <v>15.00255100000001</v>
       </c>
       <c r="N19">
-        <v>93.84599045569135</v>
+        <v>87.19744899999999</v>
       </c>
       <c r="O19">
-        <v>29.09225704126432</v>
+        <v>27.03120919</v>
       </c>
       <c r="P19">
-        <v>64.75373341442703</v>
+        <v>60.16623980999999</v>
       </c>
       <c r="Q19">
-        <v>102.553733414427</v>
+        <v>97.96623980999999</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07016684995273777</v>
+        <v>0.1141623308482156</v>
       </c>
       <c r="T19">
-        <v>0.8509403355505003</v>
+        <v>0.7363112076622292</v>
       </c>
       <c r="U19">
-        <v>0.02334611269589068</v>
+        <v>0.05300000000000001</v>
       </c>
       <c r="V19">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W19">
-        <v>0.01610881776016457</v>
+        <v>0.03657</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>12.23364654516417</v>
+        <v>6.812174809470733</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2834,25 +2834,25 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.06083750335017201</v>
+        <v>0.1007446399167262</v>
       </c>
       <c r="C20">
-        <v>1840.311860295506</v>
+        <v>1459.654459883548</v>
       </c>
       <c r="D20">
-        <v>2158.593860295506</v>
+        <v>1698.772459883548</v>
       </c>
       <c r="E20">
-        <v>243.682</v>
+        <v>164.518</v>
       </c>
       <c r="F20">
-        <v>378.882</v>
+        <v>299.718</v>
       </c>
       <c r="G20">
         <v>60.6</v>
       </c>
       <c r="H20">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -2867,45 +2867,45 @@
         <v>102.2</v>
       </c>
       <c r="M20">
-        <v>8.845421870444452</v>
+        <v>15.885054</v>
       </c>
       <c r="N20">
-        <v>93.35457812955555</v>
+        <v>86.31494600000001</v>
       </c>
       <c r="O20">
-        <v>28.93991922016222</v>
+        <v>26.75763326000001</v>
       </c>
       <c r="P20">
-        <v>64.41465890939332</v>
+        <v>59.55731274</v>
       </c>
       <c r="Q20">
-        <v>102.2146589093933</v>
+        <v>97.35731274</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07065599530895413</v>
+        <v>0.1148317559960075</v>
       </c>
       <c r="T20">
-        <v>0.8584990303715944</v>
+        <v>0.7428516799839103</v>
       </c>
       <c r="U20">
-        <v>0.02334611269589068</v>
+        <v>0.05300000000000001</v>
       </c>
       <c r="V20">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W20">
-        <v>0.01610881776016457</v>
+        <v>0.03657</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>11.55399951487727</v>
+        <v>6.433720653389028</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2916,25 +2916,25 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.06069802222034371</v>
+        <v>0.1007798452294334</v>
       </c>
       <c r="C21">
-        <v>1825.865846473711</v>
+        <v>1442.038536278992</v>
       </c>
       <c r="D21">
-        <v>2165.196846473712</v>
+        <v>1697.807536278992</v>
       </c>
       <c r="E21">
-        <v>264.7310000000001</v>
+        <v>181.169</v>
       </c>
       <c r="F21">
-        <v>399.931</v>
+        <v>316.369</v>
       </c>
       <c r="G21">
         <v>60.6</v>
       </c>
       <c r="H21">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -2949,45 +2949,45 @@
         <v>102.2</v>
       </c>
       <c r="M21">
-        <v>9.336834196580257</v>
+        <v>17.400295</v>
       </c>
       <c r="N21">
-        <v>92.86316580341975</v>
+        <v>84.799705</v>
       </c>
       <c r="O21">
-        <v>28.78758139906012</v>
+        <v>26.28790855</v>
       </c>
       <c r="P21">
-        <v>64.07558440435963</v>
+        <v>58.51179645</v>
       </c>
       <c r="Q21">
-        <v>101.8755844043596</v>
+        <v>96.31179645</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07115721832828696</v>
+        <v>0.1155177101597943</v>
       </c>
       <c r="T21">
-        <v>0.8662443596327157</v>
+        <v>0.7495536454493368</v>
       </c>
       <c r="U21">
-        <v>0.02334611269589068</v>
+        <v>0.055</v>
       </c>
       <c r="V21">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W21">
-        <v>0.01610881776016457</v>
+        <v>0.03795</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.94589427725215</v>
+        <v>5.873463639553236</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -2998,25 +2998,25 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.06055854109051539</v>
+        <v>0.1005666505421406</v>
       </c>
       <c r="C22">
-        <v>1811.460352736825</v>
+        <v>1431.247713957453</v>
       </c>
       <c r="D22">
-        <v>2171.840352736825</v>
+        <v>1703.667713957453</v>
       </c>
       <c r="E22">
-        <v>285.78</v>
+        <v>197.8200000000001</v>
       </c>
       <c r="F22">
-        <v>420.98</v>
+        <v>333.02</v>
       </c>
       <c r="G22">
         <v>60.6</v>
       </c>
       <c r="H22">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -3031,45 +3031,45 @@
         <v>102.2</v>
       </c>
       <c r="M22">
-        <v>9.828246522716059</v>
+        <v>18.3161</v>
       </c>
       <c r="N22">
-        <v>92.37175347728395</v>
+        <v>83.8839</v>
       </c>
       <c r="O22">
-        <v>28.63524357795802</v>
+        <v>26.004009</v>
       </c>
       <c r="P22">
-        <v>63.73650989932592</v>
+        <v>57.87989099999999</v>
       </c>
       <c r="Q22">
-        <v>101.5365098993259</v>
+        <v>95.679891</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.07167097192310309</v>
+        <v>0.1162208131776757</v>
       </c>
       <c r="T22">
-        <v>0.8741833221253648</v>
+        <v>0.7564231600513986</v>
       </c>
       <c r="U22">
-        <v>0.02334611269589068</v>
+        <v>0.055</v>
       </c>
       <c r="V22">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W22">
-        <v>0.01610881776016457</v>
+        <v>0.03795</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>10.39859956338954</v>
+        <v>5.579790457575575</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3080,25 +3080,25 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.06071777539309575</v>
+        <v>0.1003534558548478</v>
       </c>
       <c r="C23">
-        <v>1782.830284153278</v>
+        <v>1420.497485904108</v>
       </c>
       <c r="D23">
-        <v>2164.259284153278</v>
+        <v>1709.568485904108</v>
       </c>
       <c r="E23">
-        <v>306.829</v>
+        <v>214.471</v>
       </c>
       <c r="F23">
-        <v>442.029</v>
+        <v>349.671</v>
       </c>
       <c r="G23">
         <v>60.6</v>
       </c>
       <c r="H23">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -3113,45 +3113,45 @@
         <v>102.2</v>
       </c>
       <c r="M23">
-        <v>11.23091408606485</v>
+        <v>19.231905</v>
       </c>
       <c r="N23">
-        <v>90.96908591393516</v>
+        <v>82.96809500000001</v>
       </c>
       <c r="O23">
-        <v>28.2004166333199</v>
+        <v>25.72010945000001</v>
       </c>
       <c r="P23">
-        <v>62.76866928061526</v>
+        <v>57.24798555</v>
       </c>
       <c r="Q23">
-        <v>100.5686692806153</v>
+        <v>95.04798554999999</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.07219773193804119</v>
+        <v>0.1169417162719593</v>
       </c>
       <c r="T23">
-        <v>0.8823232710102331</v>
+        <v>0.7634665864155382</v>
       </c>
       <c r="U23">
-        <v>0.0254076408698634</v>
+        <v>0.055</v>
       </c>
       <c r="V23">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W23">
-        <v>0.01753127220020574</v>
+        <v>0.03795</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>9.099882629038028</v>
+        <v>5.314086150071977</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3162,25 +3162,25 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.06059251880766784</v>
+        <v>0.100140261167555</v>
       </c>
       <c r="C24">
-        <v>1767.740235976979</v>
+        <v>1409.788275388218</v>
       </c>
       <c r="D24">
-        <v>2170.218235976979</v>
+        <v>1715.510275388218</v>
       </c>
       <c r="E24">
-        <v>327.878</v>
+        <v>231.1220000000001</v>
       </c>
       <c r="F24">
-        <v>463.078</v>
+        <v>366.3220000000001</v>
       </c>
       <c r="G24">
         <v>60.6</v>
       </c>
       <c r="H24">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -3195,45 +3195,45 @@
         <v>102.2</v>
       </c>
       <c r="M24">
-        <v>11.7657195187346</v>
+        <v>20.14771</v>
       </c>
       <c r="N24">
-        <v>90.4342804812654</v>
+        <v>82.05229</v>
       </c>
       <c r="O24">
-        <v>28.03462694919228</v>
+        <v>25.43620990000001</v>
       </c>
       <c r="P24">
-        <v>62.39965353207313</v>
+        <v>56.61608009999999</v>
       </c>
       <c r="Q24">
-        <v>100.1996535320731</v>
+        <v>94.41608009999999</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.07273799862002894</v>
+        <v>0.117681104060968</v>
       </c>
       <c r="T24">
-        <v>0.8906719365331748</v>
+        <v>0.7706906134556812</v>
       </c>
       <c r="U24">
-        <v>0.0254076408698634</v>
+        <v>0.055</v>
       </c>
       <c r="V24">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W24">
-        <v>0.01753127220020574</v>
+        <v>0.03795</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>8.686251600445388</v>
+        <v>5.072536779614158</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3244,25 +3244,25 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.06046726222223994</v>
+        <v>0.09992706648026223</v>
       </c>
       <c r="C25">
-        <v>1752.683092495457</v>
+        <v>1399.120511584038</v>
       </c>
       <c r="D25">
-        <v>2176.210092495457</v>
+        <v>1721.493511584038</v>
       </c>
       <c r="E25">
-        <v>348.9270000000001</v>
+        <v>247.7730000000001</v>
       </c>
       <c r="F25">
-        <v>484.1270000000001</v>
+        <v>382.9730000000001</v>
       </c>
       <c r="G25">
         <v>60.6</v>
       </c>
       <c r="H25">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -3277,45 +3277,45 @@
         <v>102.2</v>
       </c>
       <c r="M25">
-        <v>12.30052495140436</v>
+        <v>21.063515</v>
       </c>
       <c r="N25">
-        <v>89.89947504859565</v>
+        <v>81.13648499999999</v>
       </c>
       <c r="O25">
-        <v>27.86883726506465</v>
+        <v>25.15231035</v>
       </c>
       <c r="P25">
-        <v>62.03063778353099</v>
+        <v>55.98417464999999</v>
       </c>
       <c r="Q25">
-        <v>99.83063778353099</v>
+        <v>93.78417464999998</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.07329229820284756</v>
+        <v>0.1184396967276133</v>
       </c>
       <c r="T25">
-        <v>0.8992374505112578</v>
+        <v>0.7781022775618021</v>
       </c>
       <c r="U25">
-        <v>0.0254076408698634</v>
+        <v>0.055</v>
       </c>
       <c r="V25">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W25">
-        <v>0.01753127220020574</v>
+        <v>0.03795</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>8.308588487382547</v>
+        <v>4.85199170223963</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3326,25 +3326,25 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.06034200563681205</v>
+        <v>0.09971387179296945</v>
       </c>
       <c r="C26">
-        <v>1737.659127007585</v>
+        <v>1388.494629674152</v>
       </c>
       <c r="D26">
-        <v>2182.235127007585</v>
+        <v>1727.518629674152</v>
       </c>
       <c r="E26">
-        <v>369.976</v>
+        <v>264.424</v>
       </c>
       <c r="F26">
-        <v>505.176</v>
+        <v>399.624</v>
       </c>
       <c r="G26">
         <v>60.6</v>
       </c>
       <c r="H26">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -3359,45 +3359,45 @@
         <v>102.2</v>
       </c>
       <c r="M26">
-        <v>12.83533038407411</v>
+        <v>21.97932</v>
       </c>
       <c r="N26">
-        <v>89.36466961592589</v>
+        <v>80.22068</v>
       </c>
       <c r="O26">
-        <v>27.70304758093702</v>
+        <v>24.8684108</v>
       </c>
       <c r="P26">
-        <v>61.66162203498887</v>
+        <v>55.35226919999999</v>
       </c>
       <c r="Q26">
-        <v>99.46162203498886</v>
+        <v>93.15226919999999</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.07386118461679299</v>
+        <v>0.1192182523591703</v>
       </c>
       <c r="T26">
-        <v>0.9080283727519219</v>
+        <v>0.7857089854601892</v>
       </c>
       <c r="U26">
-        <v>0.0254076408698634</v>
+        <v>0.055</v>
       </c>
       <c r="V26">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W26">
-        <v>0.01753127220020574</v>
+        <v>0.03795</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.962397300408274</v>
+        <v>4.649825381312979</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3408,25 +3408,25 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.06040166812858949</v>
+        <v>0.1001561771056766</v>
       </c>
       <c r="C27">
-        <v>1713.73611395906</v>
+        <v>1359.390267946782</v>
       </c>
       <c r="D27">
-        <v>2179.36111395906</v>
+        <v>1715.065267946782</v>
       </c>
       <c r="E27">
-        <v>391.025</v>
+        <v>281.075</v>
       </c>
       <c r="F27">
-        <v>526.225</v>
+        <v>416.275</v>
       </c>
       <c r="G27">
         <v>60.6</v>
       </c>
       <c r="H27">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -3441,45 +3441,45 @@
         <v>102.2</v>
       </c>
       <c r="M27">
-        <v>13.93424620168518</v>
+        <v>24.47697000000001</v>
       </c>
       <c r="N27">
-        <v>88.26575379831482</v>
+        <v>77.72302999999999</v>
       </c>
       <c r="O27">
-        <v>27.3623836774776</v>
+        <v>24.0941393</v>
       </c>
       <c r="P27">
-        <v>60.90337012083722</v>
+        <v>53.62889069999999</v>
       </c>
       <c r="Q27">
-        <v>98.70337012083722</v>
+        <v>91.42889069999998</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.0744452413351103</v>
+        <v>0.1200175694742355</v>
       </c>
       <c r="T27">
-        <v>0.9170537195856706</v>
+        <v>0.7935185389025333</v>
       </c>
       <c r="U27">
-        <v>0.0264796355203291</v>
+        <v>0.05880000000000001</v>
       </c>
       <c r="V27">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W27">
-        <v>0.01827094850902708</v>
+        <v>0.040572</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.334447699627995</v>
+        <v>4.17535340362798</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3490,25 +3490,25 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.0602838083062498</v>
+        <v>0.09996920241838386</v>
       </c>
       <c r="C28">
-        <v>1698.371874127221</v>
+        <v>1347.981673920424</v>
       </c>
       <c r="D28">
-        <v>2185.045874127221</v>
+        <v>1720.307673920424</v>
       </c>
       <c r="E28">
-        <v>412.074</v>
+        <v>297.7260000000001</v>
       </c>
       <c r="F28">
-        <v>547.274</v>
+        <v>432.926</v>
       </c>
       <c r="G28">
         <v>60.6</v>
       </c>
       <c r="H28">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -3523,45 +3523,45 @@
         <v>102.2</v>
       </c>
       <c r="M28">
-        <v>14.49161604975259</v>
+        <v>25.4560488</v>
       </c>
       <c r="N28">
-        <v>87.70838395024741</v>
+        <v>76.7439512</v>
       </c>
       <c r="O28">
-        <v>27.1895990245767</v>
+        <v>23.790624872</v>
       </c>
       <c r="P28">
-        <v>60.51878492567072</v>
+        <v>52.953326328</v>
       </c>
       <c r="Q28">
-        <v>98.31878492567071</v>
+        <v>90.75332632799999</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.07504508337013888</v>
+        <v>0.1208384897545728</v>
       </c>
       <c r="T28">
-        <v>0.9263229947122232</v>
+        <v>0.8015391613568328</v>
       </c>
       <c r="U28">
-        <v>0.0264796355203291</v>
+        <v>0.05880000000000001</v>
       </c>
       <c r="V28">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W28">
-        <v>0.01827094850902708</v>
+        <v>0.040572</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>7.052353557334611</v>
+        <v>4.014762888103828</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3572,25 +3572,25 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.06016594848391012</v>
+        <v>0.1005646877310911</v>
       </c>
       <c r="C29">
-        <v>1683.037368711101</v>
+        <v>1314.744854566537</v>
       </c>
       <c r="D29">
-        <v>2190.760368711101</v>
+        <v>1703.721854566537</v>
       </c>
       <c r="E29">
-        <v>433.1230000000001</v>
+        <v>314.3770000000001</v>
       </c>
       <c r="F29">
-        <v>568.3230000000001</v>
+        <v>449.5770000000001</v>
       </c>
       <c r="G29">
         <v>60.6</v>
       </c>
       <c r="H29">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -3605,45 +3605,45 @@
         <v>102.2</v>
       </c>
       <c r="M29">
-        <v>15.04898589782</v>
+        <v>28.323351</v>
       </c>
       <c r="N29">
-        <v>87.15101410218</v>
+        <v>73.876649</v>
       </c>
       <c r="O29">
-        <v>27.0168143716758</v>
+        <v>22.90176119000001</v>
       </c>
       <c r="P29">
-        <v>60.1341997305042</v>
+        <v>50.97488781</v>
       </c>
       <c r="Q29">
-        <v>97.93419973050419</v>
+        <v>88.77488781</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.07566135943352441</v>
+        <v>0.1216819010014946</v>
       </c>
       <c r="T29">
-        <v>0.935846222581969</v>
+        <v>0.8097795268920719</v>
       </c>
       <c r="U29">
-        <v>0.0264796355203291</v>
+        <v>0.063</v>
       </c>
       <c r="V29">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W29">
-        <v>0.01827094850902708</v>
+        <v>0.04346999999999999</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>6.791155277433327</v>
+        <v>3.608330101900725</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3654,25 +3654,25 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.06004808866157044</v>
+        <v>0.1017784130437983</v>
       </c>
       <c r="C30">
-        <v>1667.732831613388</v>
+        <v>1265.259582619072</v>
       </c>
       <c r="D30">
-        <v>2196.504831613388</v>
+        <v>1670.887582619072</v>
       </c>
       <c r="E30">
-        <v>454.1720000000001</v>
+        <v>331.0280000000001</v>
       </c>
       <c r="F30">
-        <v>589.3720000000001</v>
+        <v>466.2280000000001</v>
       </c>
       <c r="G30">
         <v>60.6</v>
       </c>
       <c r="H30">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -3687,45 +3687,45 @@
         <v>102.2</v>
       </c>
       <c r="M30">
-        <v>15.6063557458874</v>
+        <v>32.68258280000001</v>
       </c>
       <c r="N30">
-        <v>86.5936442541126</v>
+        <v>69.5174172</v>
       </c>
       <c r="O30">
-        <v>26.84402971877491</v>
+        <v>21.550399332</v>
       </c>
       <c r="P30">
-        <v>59.7496145353377</v>
+        <v>47.967017868</v>
       </c>
       <c r="Q30">
-        <v>97.5496145353377</v>
+        <v>85.767017868</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.07629475427644841</v>
+        <v>0.1225487403386087</v>
       </c>
       <c r="T30">
-        <v>0.9456339845592078</v>
+        <v>0.8182487914699565</v>
       </c>
       <c r="U30">
-        <v>0.0264796355203291</v>
+        <v>0.0701</v>
       </c>
       <c r="V30">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W30">
-        <v>0.01827094850902708</v>
+        <v>0.048369</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.548614017524995</v>
+        <v>3.127047841518816</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3736,25 +3736,25 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.06022723732631136</v>
+        <v>0.1016694083565055</v>
       </c>
       <c r="C31">
-        <v>1637.964022225653</v>
+        <v>1251.505612879194</v>
       </c>
       <c r="D31">
-        <v>2187.785022225653</v>
+        <v>1673.784612879194</v>
       </c>
       <c r="E31">
-        <v>475.2209999999999</v>
+        <v>347.679</v>
       </c>
       <c r="F31">
-        <v>610.4209999999999</v>
+        <v>482.879</v>
       </c>
       <c r="G31">
         <v>60.6</v>
       </c>
       <c r="H31">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -3769,45 +3769,45 @@
         <v>102.2</v>
       </c>
       <c r="M31">
-        <v>17.06977365838375</v>
+        <v>33.8498179</v>
       </c>
       <c r="N31">
-        <v>85.13022634161626</v>
+        <v>68.35018210000001</v>
       </c>
       <c r="O31">
-        <v>26.39037016590104</v>
+        <v>21.18855645100001</v>
       </c>
       <c r="P31">
-        <v>58.73985617571522</v>
+        <v>47.161625649</v>
       </c>
       <c r="Q31">
-        <v>96.53985617571522</v>
+        <v>84.961625649</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.07694599122762381</v>
+        <v>0.123439997685219</v>
       </c>
       <c r="T31">
-        <v>0.9556974581414392</v>
+        <v>0.826956626881021</v>
       </c>
       <c r="U31">
-        <v>0.0279639358055895</v>
+        <v>0.0701</v>
       </c>
       <c r="V31">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W31">
-        <v>0.01929511570585675</v>
+        <v>0.048369</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>5.987191280055721</v>
+        <v>3.019218605604375</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3818,25 +3818,25 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.06011961917593998</v>
+        <v>0.1059695036692127</v>
       </c>
       <c r="C32">
-        <v>1622.144861611499</v>
+        <v>1127.701321948711</v>
       </c>
       <c r="D32">
-        <v>2193.014861611499</v>
+        <v>1566.631321948712</v>
       </c>
       <c r="E32">
-        <v>496.27</v>
+        <v>364.33</v>
       </c>
       <c r="F32">
-        <v>631.47</v>
+        <v>499.53</v>
       </c>
       <c r="G32">
         <v>60.6</v>
       </c>
       <c r="H32">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -3851,45 +3851,45 @@
         <v>102.2</v>
       </c>
       <c r="M32">
-        <v>17.6583865431556</v>
+        <v>45.657042</v>
       </c>
       <c r="N32">
-        <v>84.5416134568444</v>
+        <v>56.542958</v>
       </c>
       <c r="O32">
-        <v>26.20790017162177</v>
+        <v>17.52831698</v>
       </c>
       <c r="P32">
-        <v>58.33371328522264</v>
+        <v>39.01464102</v>
       </c>
       <c r="Q32">
-        <v>96.13371328522263</v>
+        <v>76.81464102</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.0776158349488328</v>
+        <v>0.1243567195274467</v>
       </c>
       <c r="T32">
-        <v>0.9660484595403058</v>
+        <v>0.8359132575895445</v>
       </c>
       <c r="U32">
-        <v>0.0279639358055895</v>
+        <v>0.09140000000000001</v>
       </c>
       <c r="V32">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W32">
-        <v>0.01929511570585675</v>
+        <v>0.063066</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y32">
-        <v>5.787618237387195</v>
+        <v>2.23842797349859</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3900,25 +3900,25 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.0600120010255686</v>
+        <v>0.1060074689819199</v>
       </c>
       <c r="C33">
-        <v>1606.350764482766</v>
+        <v>1110.165336262809</v>
       </c>
       <c r="D33">
-        <v>2198.269764482766</v>
+        <v>1565.746336262809</v>
       </c>
       <c r="E33">
-        <v>517.319</v>
+        <v>380.9810000000001</v>
       </c>
       <c r="F33">
-        <v>652.519</v>
+        <v>516.181</v>
       </c>
       <c r="G33">
         <v>60.6</v>
       </c>
       <c r="H33">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -3933,45 +3933,45 @@
         <v>102.2</v>
       </c>
       <c r="M33">
-        <v>18.24699942792746</v>
+        <v>47.17894340000001</v>
       </c>
       <c r="N33">
-        <v>83.95300057207254</v>
+        <v>55.02105659999999</v>
       </c>
       <c r="O33">
-        <v>26.02543017734249</v>
+        <v>17.056527546</v>
       </c>
       <c r="P33">
-        <v>57.92757039473005</v>
+        <v>37.964529054</v>
       </c>
       <c r="Q33">
-        <v>95.72757039473005</v>
+        <v>75.76452905399999</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.07830509443007683</v>
+        <v>0.1253000130172753</v>
       </c>
       <c r="T33">
-        <v>0.9766994899652265</v>
+        <v>0.845129500782373</v>
       </c>
       <c r="U33">
-        <v>0.0279639358055895</v>
+        <v>0.09140000000000001</v>
       </c>
       <c r="V33">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W33">
-        <v>0.01929511570585675</v>
+        <v>0.063066</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y33">
-        <v>5.600920874890834</v>
+        <v>2.166220619514764</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -3982,25 +3982,25 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.05990438287519721</v>
+        <v>0.1060454342946271</v>
       </c>
       <c r="C34">
-        <v>1590.58191144361</v>
+        <v>1092.630349864329</v>
       </c>
       <c r="D34">
-        <v>2203.549911443611</v>
+        <v>1564.862349864329</v>
       </c>
       <c r="E34">
-        <v>538.3680000000002</v>
+        <v>397.6320000000001</v>
       </c>
       <c r="F34">
-        <v>673.5680000000001</v>
+        <v>532.8320000000001</v>
       </c>
       <c r="G34">
         <v>60.6</v>
       </c>
       <c r="H34">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -4015,45 +4015,45 @@
         <v>102.2</v>
       </c>
       <c r="M34">
-        <v>18.83561231269931</v>
+        <v>48.70084480000001</v>
       </c>
       <c r="N34">
-        <v>83.36438768730069</v>
+        <v>53.49915519999999</v>
       </c>
       <c r="O34">
-        <v>25.84296018306322</v>
+        <v>16.584738112</v>
       </c>
       <c r="P34">
-        <v>57.52142750423748</v>
+        <v>36.91441708799999</v>
       </c>
       <c r="Q34">
-        <v>95.32142750423748</v>
+        <v>74.71441708799999</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.07901462624900449</v>
+        <v>0.1262710504332752</v>
       </c>
       <c r="T34">
-        <v>0.98766378599088</v>
+        <v>0.8546168099514612</v>
       </c>
       <c r="U34">
-        <v>0.0279639358055895</v>
+        <v>0.09140000000000001</v>
       </c>
       <c r="V34">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W34">
-        <v>0.01929511570585675</v>
+        <v>0.063066</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y34">
-        <v>5.425892097550495</v>
+        <v>2.098526225154927</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4064,25 +4064,25 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.05979676472482582</v>
+        <v>0.1060833996073343</v>
       </c>
       <c r="C35">
-        <v>1574.838484837581</v>
+        <v>1075.096361061696</v>
       </c>
       <c r="D35">
-        <v>2208.855484837581</v>
+        <v>1563.979361061696</v>
       </c>
       <c r="E35">
-        <v>559.4170000000001</v>
+        <v>414.2830000000001</v>
       </c>
       <c r="F35">
-        <v>694.6170000000001</v>
+        <v>549.4830000000001</v>
       </c>
       <c r="G35">
         <v>60.6</v>
       </c>
       <c r="H35">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -4097,45 +4097,45 @@
         <v>102.2</v>
       </c>
       <c r="M35">
-        <v>19.42422519747116</v>
+        <v>50.22274620000001</v>
       </c>
       <c r="N35">
-        <v>82.77577480252884</v>
+        <v>51.97725379999999</v>
       </c>
       <c r="O35">
-        <v>25.66049018878394</v>
+        <v>16.112948678</v>
       </c>
       <c r="P35">
-        <v>57.1152846137449</v>
+        <v>35.86430512199999</v>
       </c>
       <c r="Q35">
-        <v>94.9152846137449</v>
+        <v>73.66430512199999</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.0797453381222285</v>
+        <v>0.1272710740407975</v>
       </c>
       <c r="T35">
-        <v>0.99895537443521</v>
+        <v>0.8643873223793281</v>
       </c>
       <c r="U35">
-        <v>0.0279639358055895</v>
+        <v>0.09140000000000001</v>
       </c>
       <c r="V35">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W35">
-        <v>0.01929511570585675</v>
+        <v>0.063066</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y35">
-        <v>5.261471124897451</v>
+        <v>2.034934521362354</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4146,25 +4146,25 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.05968914657445443</v>
+        <v>0.1110714249200416</v>
       </c>
       <c r="C36">
-        <v>1559.120668768607</v>
+        <v>950.5027177533851</v>
       </c>
       <c r="D36">
-        <v>2214.186668768607</v>
+        <v>1456.036717753385</v>
       </c>
       <c r="E36">
-        <v>580.4660000000001</v>
+        <v>430.9340000000001</v>
       </c>
       <c r="F36">
-        <v>715.6660000000001</v>
+        <v>566.1340000000001</v>
       </c>
       <c r="G36">
         <v>60.6</v>
       </c>
       <c r="H36">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -4179,45 +4179,45 @@
         <v>102.2</v>
       </c>
       <c r="M36">
-        <v>20.01283808224302</v>
+        <v>63.69007500000001</v>
       </c>
       <c r="N36">
-        <v>82.18716191775698</v>
+        <v>38.50992499999999</v>
       </c>
       <c r="O36">
-        <v>25.47802019450467</v>
+        <v>11.93807675</v>
       </c>
       <c r="P36">
-        <v>56.70914172325232</v>
+        <v>26.57184824999999</v>
       </c>
       <c r="Q36">
-        <v>94.50914172325231</v>
+        <v>64.37184824999999</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.08049819277948961</v>
+        <v>0.1283014013940024</v>
       </c>
       <c r="T36">
-        <v>1.010589132226338</v>
+        <v>0.8744539109413727</v>
       </c>
       <c r="U36">
-        <v>0.0279639358055895</v>
+        <v>0.1125</v>
       </c>
       <c r="V36">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W36">
-        <v>0.01929511570585675</v>
+        <v>0.077625</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>5.106721974165172</v>
+        <v>1.60464562178644</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4228,25 +4228,25 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.05958152842408306</v>
+        <v>0.1112549802327488</v>
       </c>
       <c r="C37">
-        <v>1543.428649122296</v>
+        <v>930.1630372212553</v>
       </c>
       <c r="D37">
-        <v>2219.543649122296</v>
+        <v>1452.348037221255</v>
       </c>
       <c r="E37">
-        <v>601.5150000000001</v>
+        <v>447.5850000000001</v>
       </c>
       <c r="F37">
-        <v>736.7150000000001</v>
+        <v>582.7850000000001</v>
       </c>
       <c r="G37">
         <v>60.6</v>
       </c>
       <c r="H37">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -4261,45 +4261,45 @@
         <v>102.2</v>
       </c>
       <c r="M37">
-        <v>20.60145096701487</v>
+        <v>65.56331250000001</v>
       </c>
       <c r="N37">
-        <v>81.59854903298513</v>
+        <v>36.63668749999999</v>
       </c>
       <c r="O37">
-        <v>25.29555020022539</v>
+        <v>11.357373125</v>
       </c>
       <c r="P37">
-        <v>56.30299883275974</v>
+        <v>25.27931437499999</v>
       </c>
       <c r="Q37">
-        <v>94.10299883275974</v>
+        <v>63.07931437499999</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.08127421219543569</v>
+        <v>0.1293634311273058</v>
       </c>
       <c r="T37">
-        <v>1.022580851795654</v>
+        <v>0.8848302406899419</v>
       </c>
       <c r="U37">
-        <v>0.0279639358055895</v>
+        <v>0.1125</v>
       </c>
       <c r="V37">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W37">
-        <v>0.01929511570585675</v>
+        <v>0.077625</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.960815632046167</v>
+        <v>1.558798604021113</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4310,25 +4310,25 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.05947391027371167</v>
+        <v>0.111438535545456</v>
       </c>
       <c r="C38">
-        <v>1527.762613587535</v>
+        <v>909.8419990503313</v>
       </c>
       <c r="D38">
-        <v>2224.926613587535</v>
+        <v>1448.677999050331</v>
       </c>
       <c r="E38">
-        <v>622.5640000000001</v>
+        <v>464.236</v>
       </c>
       <c r="F38">
-        <v>757.764</v>
+        <v>599.436</v>
       </c>
       <c r="G38">
         <v>60.6</v>
       </c>
       <c r="H38">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -4343,45 +4343,45 @@
         <v>102.2</v>
       </c>
       <c r="M38">
-        <v>21.19006385178672</v>
+        <v>67.43655000000001</v>
       </c>
       <c r="N38">
-        <v>81.00993614821328</v>
+        <v>34.76344999999999</v>
       </c>
       <c r="O38">
-        <v>25.11308020594612</v>
+        <v>10.7766695</v>
       </c>
       <c r="P38">
-        <v>55.89685594226717</v>
+        <v>23.98678049999999</v>
       </c>
       <c r="Q38">
-        <v>93.69685594226716</v>
+        <v>61.78678049999999</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08207448221813006</v>
+        <v>0.130458649289775</v>
       </c>
       <c r="T38">
-        <v>1.034947312601511</v>
+        <v>0.8955308307431539</v>
       </c>
       <c r="U38">
-        <v>0.0279639358055895</v>
+        <v>0.1125</v>
       </c>
       <c r="V38">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="W38">
-        <v>0.01929511570585675</v>
+        <v>0.077625</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.823015197822663</v>
+        <v>1.515498642798304</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4392,25 +4392,25 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.05936629212334029</v>
+        <v>0.1377989765837166</v>
       </c>
       <c r="C39">
-        <v>1512.122751678414</v>
+        <v>507.4517490581977</v>
       </c>
       <c r="D39">
-        <v>2230.335751678414</v>
+        <v>1062.938749058198</v>
       </c>
       <c r="E39">
-        <v>643.6130000000001</v>
+        <v>480.887</v>
       </c>
       <c r="F39">
-        <v>778.813</v>
+        <v>616.087</v>
       </c>
       <c r="G39">
         <v>60.6</v>
       </c>
       <c r="H39">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -4425,45 +4425,45 @@
         <v>102.2</v>
       </c>
       <c r="M39">
-        <v>21.77867673655858</v>
+        <v>121.1227042</v>
       </c>
       <c r="N39">
-        <v>80.42132326344142</v>
+        <v>-18.9227042</v>
       </c>
       <c r="O39">
-        <v>24.93061021166684</v>
+        <v>-5.866038302000001</v>
       </c>
       <c r="P39">
-        <v>55.49071305177458</v>
+        <v>-13.056665898</v>
       </c>
       <c r="Q39">
-        <v>93.29071305177457</v>
+        <v>24.743334102</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.0829001576383703</v>
+        <v>0.1334667651492846</v>
       </c>
       <c r="T39">
-        <v>1.047706359464698</v>
+        <v>0.9249209703045803</v>
       </c>
       <c r="U39">
-        <v>0.0279639358055895</v>
+        <v>0.1966</v>
       </c>
       <c r="V39">
-        <v>0.31</v>
+        <v>0.2615694572644788</v>
       </c>
       <c r="W39">
-        <v>0.01929511570585675</v>
+        <v>0.1451754447018034</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.692663435719348</v>
+        <v>0.8437724427886412</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4474,25 +4474,25 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.0592586739729689</v>
+        <v>0.1393769765837166</v>
       </c>
       <c r="C40">
-        <v>1496.509254756467</v>
+        <v>474.1237977022611</v>
       </c>
       <c r="D40">
-        <v>2235.771254756467</v>
+        <v>1046.261797702261</v>
       </c>
       <c r="E40">
-        <v>664.662</v>
+        <v>497.5380000000001</v>
       </c>
       <c r="F40">
-        <v>799.8620000000001</v>
+        <v>632.7380000000001</v>
       </c>
       <c r="G40">
         <v>60.6</v>
       </c>
       <c r="H40">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -4507,45 +4507,45 @@
         <v>102.2</v>
       </c>
       <c r="M40">
-        <v>22.36728962133043</v>
+        <v>124.3962908</v>
       </c>
       <c r="N40">
-        <v>79.83271037866957</v>
+        <v>-22.1962908</v>
       </c>
       <c r="O40">
-        <v>24.74814021738757</v>
+        <v>-6.880850148000001</v>
       </c>
       <c r="P40">
-        <v>55.084570161282</v>
+        <v>-15.315440652</v>
       </c>
       <c r="Q40">
-        <v>92.884570161282</v>
+        <v>22.484559348</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.08375246774958603</v>
+        <v>0.134993648458144</v>
       </c>
       <c r="T40">
-        <v>1.060876988484761</v>
+        <v>0.9398390504707833</v>
       </c>
       <c r="U40">
-        <v>0.0279639358055895</v>
+        <v>0.1966</v>
       </c>
       <c r="V40">
-        <v>0.31</v>
+        <v>0.2546860504943609</v>
       </c>
       <c r="W40">
-        <v>0.01929511570585675</v>
+        <v>0.1465287224728087</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.569172292674102</v>
+        <v>0.821567904820519</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4556,25 +4556,25 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.05997092877667096</v>
+        <v>0.1409549765837166</v>
       </c>
       <c r="C41">
-        <v>1439.970933282756</v>
+        <v>441.3110680245961</v>
       </c>
       <c r="D41">
-        <v>2200.281933282756</v>
+        <v>1030.100068024596</v>
       </c>
       <c r="E41">
-        <v>685.711</v>
+        <v>514.1890000000001</v>
       </c>
       <c r="F41">
-        <v>820.9110000000001</v>
+        <v>649.3890000000001</v>
       </c>
       <c r="G41">
         <v>60.6</v>
       </c>
       <c r="H41">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -4589,45 +4589,45 @@
         <v>102.2</v>
       </c>
       <c r="M41">
-        <v>25.45699030469531</v>
+        <v>127.6698774</v>
       </c>
       <c r="N41">
-        <v>76.74300969530469</v>
+        <v>-25.46987740000002</v>
       </c>
       <c r="O41">
-        <v>23.79033300554445</v>
+        <v>-7.895661994000006</v>
       </c>
       <c r="P41">
-        <v>52.95267668976024</v>
+        <v>-17.57421540600001</v>
       </c>
       <c r="Q41">
-        <v>90.75267668976024</v>
+        <v>20.22578459399999</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.08463272245461211</v>
+        <v>0.136570593514835</v>
       </c>
       <c r="T41">
-        <v>1.074479441407121</v>
+        <v>0.9552462480194848</v>
       </c>
       <c r="U41">
-        <v>0.031010658042949</v>
+        <v>0.1966</v>
       </c>
       <c r="V41">
-        <v>0.31</v>
+        <v>0.2481556389432235</v>
       </c>
       <c r="W41">
-        <v>0.02139735404963481</v>
+        <v>0.1478126013837623</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.01461440558235</v>
+        <v>0.8005020611071723</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4638,25 +4638,25 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.06083122142745018</v>
+        <v>0.1499270846033419</v>
       </c>
       <c r="C42">
-        <v>1377.530378065968</v>
+        <v>341.4925025806801</v>
       </c>
       <c r="D42">
-        <v>2158.890378065968</v>
+        <v>946.9325025806802</v>
       </c>
       <c r="E42">
-        <v>706.76</v>
+        <v>530.8400000000001</v>
       </c>
       <c r="F42">
-        <v>841.96</v>
+        <v>666.0400000000001</v>
       </c>
       <c r="G42">
         <v>60.6</v>
       </c>
       <c r="H42">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -4671,45 +4671,45 @@
         <v>102.2</v>
       </c>
       <c r="M42">
-        <v>28.99829224068734</v>
+        <v>142.399352</v>
       </c>
       <c r="N42">
-        <v>73.20170775931265</v>
+        <v>-40.19935200000002</v>
       </c>
       <c r="O42">
-        <v>22.69252940538692</v>
+        <v>-12.46179912000001</v>
       </c>
       <c r="P42">
-        <v>50.50917835392573</v>
+        <v>-27.73755288000001</v>
       </c>
       <c r="Q42">
-        <v>88.30917835392573</v>
+        <v>10.06244711999999</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08554231898313905</v>
+        <v>0.1390569501061244</v>
       </c>
       <c r="T42">
-        <v>1.088535309426893</v>
+        <v>0.9795386525113053</v>
       </c>
       <c r="U42">
-        <v>0.0344414131795897</v>
+        <v>0.2138</v>
       </c>
       <c r="V42">
-        <v>0.31</v>
+        <v>0.2224869674968745</v>
       </c>
       <c r="W42">
-        <v>0.02376457509391689</v>
+        <v>0.1662322863491682</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.524345473579432</v>
+        <v>0.7176998951512081</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4720,25 +4720,25 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.06138636682613336</v>
+        <v>0.1516770846033419</v>
       </c>
       <c r="C43">
-        <v>1330.588266512264</v>
+        <v>310.1606496392753</v>
       </c>
       <c r="D43">
-        <v>2132.997266512265</v>
+        <v>932.2516496392755</v>
       </c>
       <c r="E43">
-        <v>727.8090000000002</v>
+        <v>547.4910000000002</v>
       </c>
       <c r="F43">
-        <v>863.0090000000001</v>
+        <v>682.6910000000001</v>
       </c>
       <c r="G43">
         <v>60.6</v>
       </c>
       <c r="H43">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -4753,45 +4753,45 @@
         <v>102.2</v>
       </c>
       <c r="M43">
-        <v>31.60871816082867</v>
+        <v>145.9593358</v>
       </c>
       <c r="N43">
-        <v>70.59128183917133</v>
+        <v>-43.75933580000002</v>
       </c>
       <c r="O43">
-        <v>21.88329737014311</v>
+        <v>-13.56539409800001</v>
       </c>
       <c r="P43">
-        <v>48.70798446902822</v>
+        <v>-30.19394170200001</v>
       </c>
       <c r="Q43">
-        <v>86.50798446902822</v>
+        <v>7.606058297999986</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.08648274929229403</v>
+        <v>0.1407562204469061</v>
       </c>
       <c r="T43">
-        <v>1.103067647549031</v>
+        <v>0.9961410025538697</v>
       </c>
       <c r="U43">
-        <v>0.0366261744209257</v>
+        <v>0.2138</v>
       </c>
       <c r="V43">
-        <v>0.31</v>
+        <v>0.2170604560945118</v>
       </c>
       <c r="W43">
-        <v>0.02527206035043873</v>
+        <v>0.1673924744869934</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y43">
-        <v>3.233285180373182</v>
+        <v>0.7001950196597153</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4802,25 +4802,25 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.06133851812220779</v>
+        <v>0.1534270846033419</v>
       </c>
       <c r="C44">
-        <v>1311.746542152233</v>
+        <v>279.2770588644668</v>
       </c>
       <c r="D44">
-        <v>2135.204542152233</v>
+        <v>918.0190588644667</v>
       </c>
       <c r="E44">
-        <v>748.8579999999999</v>
+        <v>564.1420000000001</v>
       </c>
       <c r="F44">
-        <v>884.058</v>
+        <v>699.342</v>
       </c>
       <c r="G44">
         <v>60.6</v>
       </c>
       <c r="H44">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -4835,45 +4835,45 @@
         <v>102.2</v>
       </c>
       <c r="M44">
-        <v>32.37966250621474</v>
+        <v>149.5193196</v>
       </c>
       <c r="N44">
-        <v>69.82033749378527</v>
+        <v>-47.31931959999999</v>
       </c>
       <c r="O44">
-        <v>21.64430462307343</v>
+        <v>-14.668989076</v>
       </c>
       <c r="P44">
-        <v>48.17603287071184</v>
+        <v>-32.65033052399999</v>
       </c>
       <c r="Q44">
-        <v>85.97603287071183</v>
+        <v>5.149669476000007</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.08745560823279917</v>
+        <v>0.1425140863166804</v>
       </c>
       <c r="T44">
-        <v>1.118101100778828</v>
+        <v>1.013315847425488</v>
       </c>
       <c r="U44">
-        <v>0.0366261744209257</v>
+        <v>0.2138</v>
       </c>
       <c r="V44">
-        <v>0.31</v>
+        <v>0.2118923499970235</v>
       </c>
       <c r="W44">
-        <v>0.02527206035043873</v>
+        <v>0.1684974155706364</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.156302199888107</v>
+        <v>0.6835237096678175</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4884,25 +4884,25 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.06129066941828223</v>
+        <v>0.1551770846033419</v>
       </c>
       <c r="C45">
-        <v>1292.909390805752</v>
+        <v>248.8215082651068</v>
       </c>
       <c r="D45">
-        <v>2137.416390805752</v>
+        <v>904.2145082651068</v>
       </c>
       <c r="E45">
-        <v>769.9069999999999</v>
+        <v>580.7930000000001</v>
       </c>
       <c r="F45">
-        <v>905.107</v>
+        <v>715.9930000000001</v>
       </c>
       <c r="G45">
         <v>60.6</v>
       </c>
       <c r="H45">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -4917,45 +4917,45 @@
         <v>102.2</v>
       </c>
       <c r="M45">
-        <v>33.1506068516008</v>
+        <v>153.0793034</v>
       </c>
       <c r="N45">
-        <v>69.0493931483992</v>
+        <v>-50.87930340000001</v>
       </c>
       <c r="O45">
-        <v>21.40531187600375</v>
+        <v>-15.77258405400001</v>
       </c>
       <c r="P45">
-        <v>47.64408127239545</v>
+        <v>-35.10671934600001</v>
       </c>
       <c r="Q45">
-        <v>85.44408127239545</v>
+        <v>2.693280653999992</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.08846260257472556</v>
+        <v>0.1443336316906572</v>
       </c>
       <c r="T45">
-        <v>1.133662043595636</v>
+        <v>1.031093318432953</v>
       </c>
       <c r="U45">
-        <v>0.0366261744209257</v>
+        <v>0.2138</v>
       </c>
       <c r="V45">
-        <v>0.31</v>
+        <v>0.2069646209273252</v>
       </c>
       <c r="W45">
-        <v>0.02527206035043873</v>
+        <v>0.1695509640457379</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.082899823146523</v>
+        <v>0.6676278094429844</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -4966,25 +4966,25 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.06124282071435666</v>
+        <v>0.1569270846033419</v>
       </c>
       <c r="C46">
-        <v>1274.07682669905</v>
+        <v>218.7749741691169</v>
       </c>
       <c r="D46">
-        <v>2139.63282669905</v>
+        <v>890.818974169117</v>
       </c>
       <c r="E46">
-        <v>790.9560000000001</v>
+        <v>597.4440000000002</v>
       </c>
       <c r="F46">
-        <v>926.1560000000001</v>
+        <v>732.6440000000001</v>
       </c>
       <c r="G46">
         <v>60.6</v>
       </c>
       <c r="H46">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -4999,45 +4999,45 @@
         <v>102.2</v>
       </c>
       <c r="M46">
-        <v>33.92155119698687</v>
+        <v>156.6392872</v>
       </c>
       <c r="N46">
-        <v>68.27844880301313</v>
+        <v>-54.43928720000001</v>
       </c>
       <c r="O46">
-        <v>21.16631912893407</v>
+        <v>-16.87617903200001</v>
       </c>
       <c r="P46">
-        <v>47.11212967407906</v>
+        <v>-37.563108168</v>
       </c>
       <c r="Q46">
-        <v>84.91212967407907</v>
+        <v>0.2368918319999977</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.08950556100029217</v>
+        <v>0.1462181608279904</v>
       </c>
       <c r="T46">
-        <v>1.149778734370187</v>
+        <v>1.049505699119256</v>
       </c>
       <c r="U46">
-        <v>0.0366261744209257</v>
+        <v>0.2138</v>
       </c>
       <c r="V46">
-        <v>0.31</v>
+        <v>0.2022608795426133</v>
       </c>
       <c r="W46">
-        <v>0.02527206035043873</v>
+        <v>0.1705566239537893</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.01283391807501</v>
+        <v>0.6524544501374621</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5048,25 +5048,25 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.06623780997316825</v>
+        <v>0.1586770846033419</v>
       </c>
       <c r="C47">
-        <v>1044.034852757263</v>
+        <v>189.1195437564633</v>
       </c>
       <c r="D47">
-        <v>1930.639852757263</v>
+        <v>877.8145437564633</v>
       </c>
       <c r="E47">
-        <v>812.0050000000001</v>
+        <v>614.095</v>
       </c>
       <c r="F47">
-        <v>947.205</v>
+        <v>749.2950000000001</v>
       </c>
       <c r="G47">
         <v>60.6</v>
       </c>
       <c r="H47">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -5081,45 +5081,45 @@
         <v>102.2</v>
       </c>
       <c r="M47">
-        <v>50.07607471304747</v>
+        <v>160.199271</v>
       </c>
       <c r="N47">
-        <v>52.12392528695253</v>
+        <v>-57.99927100000001</v>
       </c>
       <c r="O47">
-        <v>16.15841683895529</v>
+        <v>-17.97977401000001</v>
       </c>
       <c r="P47">
-        <v>35.96550844799725</v>
+        <v>-40.01949699</v>
       </c>
       <c r="Q47">
-        <v>73.76550844799725</v>
+        <v>-2.219496990000003</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.09058644518678848</v>
+        <v>0.1481712182975902</v>
       </c>
       <c r="T47">
-        <v>1.166481486627449</v>
+        <v>1.068587620921424</v>
       </c>
       <c r="U47">
-        <v>0.0528671984555059</v>
+        <v>0.2138</v>
       </c>
       <c r="V47">
-        <v>0.31</v>
+        <v>0.1977661933305552</v>
       </c>
       <c r="W47">
-        <v>0.03647836693429907</v>
+        <v>0.1715175878659273</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.040894790289373</v>
+        <v>0.6379554623566295</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5130,25 +5130,25 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.06896587073280966</v>
+        <v>0.1604270846033419</v>
       </c>
       <c r="C48">
-        <v>925.2077466642165</v>
+        <v>159.8383351431129</v>
       </c>
       <c r="D48">
-        <v>1832.861746664217</v>
+        <v>865.184335143113</v>
       </c>
       <c r="E48">
-        <v>833.0540000000001</v>
+        <v>630.7460000000001</v>
       </c>
       <c r="F48">
-        <v>968.2540000000001</v>
+        <v>765.9460000000001</v>
       </c>
       <c r="G48">
         <v>60.6</v>
       </c>
       <c r="H48">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -5163,45 +5163,45 @@
         <v>102.2</v>
       </c>
       <c r="M48">
-        <v>59.31515214519028</v>
+        <v>163.7592548</v>
       </c>
       <c r="N48">
-        <v>42.88484785480973</v>
+        <v>-61.55925480000003</v>
       </c>
       <c r="O48">
-        <v>13.29430283499102</v>
+        <v>-19.08336898800001</v>
       </c>
       <c r="P48">
-        <v>29.59054501981871</v>
+        <v>-42.47588581200002</v>
       </c>
       <c r="Q48">
-        <v>67.39054501981872</v>
+        <v>-4.675885812000018</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.09170736212093279</v>
+        <v>0.1501966112290271</v>
       </c>
       <c r="T48">
-        <v>1.183802859338684</v>
+        <v>1.088376280568117</v>
       </c>
       <c r="U48">
-        <v>0.06125990922339621</v>
+        <v>0.2138</v>
       </c>
       <c r="V48">
-        <v>0.31</v>
+        <v>0.1934669282581518</v>
       </c>
       <c r="W48">
-        <v>0.04226933736414338</v>
+        <v>0.1724367707384071</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y48">
-        <v>1.722999879522136</v>
+        <v>0.6240868653488767</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5212,25 +5212,25 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.06908799479902115</v>
+        <v>0.1621770846033419</v>
       </c>
       <c r="C49">
-        <v>900.012704009004</v>
+        <v>130.9154242662416</v>
       </c>
       <c r="D49">
-        <v>1828.715704009004</v>
+        <v>852.9124242662417</v>
       </c>
       <c r="E49">
-        <v>854.1030000000001</v>
+        <v>647.3970000000002</v>
       </c>
       <c r="F49">
-        <v>989.3030000000001</v>
+        <v>782.5970000000001</v>
       </c>
       <c r="G49">
         <v>60.6</v>
       </c>
       <c r="H49">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -5245,45 +5245,45 @@
         <v>102.2</v>
       </c>
       <c r="M49">
-        <v>60.60461197443355</v>
+        <v>167.3192386</v>
       </c>
       <c r="N49">
-        <v>41.59538802556646</v>
+        <v>-65.1192386</v>
       </c>
       <c r="O49">
-        <v>12.8945702879256</v>
+        <v>-20.186963966</v>
       </c>
       <c r="P49">
-        <v>28.70081773764085</v>
+        <v>-44.932274634</v>
       </c>
       <c r="Q49">
-        <v>66.50081773764086</v>
+        <v>-7.132274633999998</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.09287057780730898</v>
+        <v>0.152298434082405</v>
       </c>
       <c r="T49">
-        <v>1.201777868756003</v>
+        <v>1.10891168208827</v>
       </c>
       <c r="U49">
-        <v>0.06125990922339621</v>
+        <v>0.2138</v>
       </c>
       <c r="V49">
-        <v>0.31</v>
+        <v>0.189350610635638</v>
       </c>
       <c r="W49">
-        <v>0.04226933736414338</v>
+        <v>0.1733168394461006</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.686340307617409</v>
+        <v>0.6108084214052836</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5294,25 +5294,25 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.06921011886523262</v>
+        <v>0.1639270846033419</v>
       </c>
       <c r="C50">
-        <v>874.8363762115072</v>
+        <v>102.3357779048442</v>
       </c>
       <c r="D50">
-        <v>1824.588376211507</v>
+        <v>840.9837779048443</v>
       </c>
       <c r="E50">
-        <v>875.152</v>
+        <v>664.048</v>
       </c>
       <c r="F50">
-        <v>1010.352</v>
+        <v>799.248</v>
       </c>
       <c r="G50">
         <v>60.6</v>
       </c>
       <c r="H50">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -5327,45 +5327,45 @@
         <v>102.2</v>
       </c>
       <c r="M50">
-        <v>61.8940718036768</v>
+        <v>170.8792224</v>
       </c>
       <c r="N50">
-        <v>40.3059281963232</v>
+        <v>-68.6792224</v>
       </c>
       <c r="O50">
-        <v>12.49483774086019</v>
+        <v>-21.290558944</v>
       </c>
       <c r="P50">
-        <v>27.81109045546301</v>
+        <v>-47.388663456</v>
       </c>
       <c r="Q50">
-        <v>65.611090455463</v>
+        <v>-9.588663455999999</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.09407853255854577</v>
+        <v>0.1544810962762974</v>
       </c>
       <c r="T50">
-        <v>1.220444224689373</v>
+        <v>1.130236906743814</v>
       </c>
       <c r="U50">
-        <v>0.06125990922339621</v>
+        <v>0.2138</v>
       </c>
       <c r="V50">
-        <v>0.31</v>
+        <v>0.1854058062473955</v>
       </c>
       <c r="W50">
-        <v>0.04226933736414338</v>
+        <v>0.1741602386243068</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.65120821787538</v>
+        <v>0.5980832459593403</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5376,25 +5376,25 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.0693322429314441</v>
+        <v>0.1656770846033419</v>
       </c>
       <c r="C51">
-        <v>849.678636841335</v>
+        <v>74.08519224337863</v>
       </c>
       <c r="D51">
-        <v>1820.479636841335</v>
+        <v>829.3841922433786</v>
       </c>
       <c r="E51">
-        <v>896.201</v>
+        <v>680.6990000000001</v>
       </c>
       <c r="F51">
-        <v>1031.401</v>
+        <v>815.899</v>
       </c>
       <c r="G51">
         <v>60.6</v>
       </c>
       <c r="H51">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -5409,45 +5409,45 @@
         <v>102.2</v>
       </c>
       <c r="M51">
-        <v>63.18353163292007</v>
+        <v>174.4392062</v>
       </c>
       <c r="N51">
-        <v>39.01646836707993</v>
+        <v>-72.2392062</v>
       </c>
       <c r="O51">
-        <v>12.09510519379478</v>
+        <v>-22.394153922</v>
       </c>
       <c r="P51">
-        <v>26.92136317328515</v>
+        <v>-49.845052278</v>
       </c>
       <c r="Q51">
-        <v>64.72136317328514</v>
+        <v>-12.045052278</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.09533385808434089</v>
+        <v>0.1567493530660287</v>
       </c>
       <c r="T51">
-        <v>1.239842594580914</v>
+        <v>1.152398414719183</v>
       </c>
       <c r="U51">
-        <v>0.06125990922339621</v>
+        <v>0.2138</v>
       </c>
       <c r="V51">
-        <v>0.31</v>
+        <v>0.1816220142831629</v>
       </c>
       <c r="W51">
-        <v>0.04226933736414338</v>
+        <v>0.1749692133462598</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.617510090979964</v>
+        <v>0.5858774654295578</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5458,25 +5458,25 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.06945436699765559</v>
+        <v>0.1674270846033419</v>
       </c>
       <c r="C52">
-        <v>824.539360604361</v>
+        <v>46.1502364505393</v>
       </c>
       <c r="D52">
-        <v>1816.389360604361</v>
+        <v>818.1002364505393</v>
       </c>
       <c r="E52">
-        <v>917.25</v>
+        <v>697.3500000000001</v>
       </c>
       <c r="F52">
-        <v>1052.45</v>
+        <v>832.5500000000001</v>
       </c>
       <c r="G52">
         <v>60.6</v>
       </c>
       <c r="H52">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -5491,45 +5491,45 @@
         <v>102.2</v>
       </c>
       <c r="M52">
-        <v>64.47299146216334</v>
+        <v>177.99919</v>
       </c>
       <c r="N52">
-        <v>37.72700853783667</v>
+        <v>-75.79919</v>
       </c>
       <c r="O52">
-        <v>11.69537264672937</v>
+        <v>-23.4977489</v>
       </c>
       <c r="P52">
-        <v>26.0316358911073</v>
+        <v>-52.30144109999999</v>
       </c>
       <c r="Q52">
-        <v>63.8316358911073</v>
+        <v>-14.50144109999999</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.0966393966311678</v>
+        <v>0.1591083401273492</v>
       </c>
       <c r="T52">
-        <v>1.260016899268116</v>
+        <v>1.175446383013566</v>
       </c>
       <c r="U52">
-        <v>0.06125990922339621</v>
+        <v>0.2138</v>
       </c>
       <c r="V52">
-        <v>0.31</v>
+        <v>0.1779895739974997</v>
       </c>
       <c r="W52">
-        <v>0.04226933736414338</v>
+        <v>0.1757458290793346</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y52">
-        <v>1.585159889160365</v>
+        <v>0.5741599161209666</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5540,25 +5540,25 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.06957649106386708</v>
+        <v>0.1691770846033419</v>
       </c>
       <c r="C53">
-        <v>799.4184233299827</v>
+        <v>18.51820080194989</v>
       </c>
       <c r="D53">
-        <v>1812.317423329983</v>
+        <v>807.11920080195</v>
       </c>
       <c r="E53">
-        <v>938.299</v>
+        <v>714.0010000000002</v>
       </c>
       <c r="F53">
-        <v>1073.499</v>
+        <v>849.2010000000001</v>
       </c>
       <c r="G53">
         <v>60.6</v>
       </c>
       <c r="H53">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -5573,45 +5573,45 @@
         <v>102.2</v>
       </c>
       <c r="M53">
-        <v>65.76245129140661</v>
+        <v>181.5591738</v>
       </c>
       <c r="N53">
-        <v>36.4375487085934</v>
+        <v>-79.35917380000002</v>
       </c>
       <c r="O53">
-        <v>11.29564009966395</v>
+        <v>-24.60134387800001</v>
       </c>
       <c r="P53">
-        <v>25.14190860892944</v>
+        <v>-54.75782992200001</v>
       </c>
       <c r="Q53">
-        <v>62.94190860892944</v>
+        <v>-16.95782992200002</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.09799822246562032</v>
+        <v>0.1615636123748462</v>
       </c>
       <c r="T53">
-        <v>1.28101464496296</v>
+        <v>1.199435084707721</v>
       </c>
       <c r="U53">
-        <v>0.06125990922339621</v>
+        <v>0.2138</v>
       </c>
       <c r="V53">
-        <v>0.31</v>
+        <v>0.1744995823504899</v>
       </c>
       <c r="W53">
-        <v>0.04226933736414338</v>
+        <v>0.1764919892934652</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.55407832270624</v>
+        <v>0.5629018785499672</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5622,25 +5622,25 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.06969861513007855</v>
+        <v>0.1709270846033419</v>
       </c>
       <c r="C54">
-        <v>774.315701958559</v>
+        <v>-8.822951074508524</v>
       </c>
       <c r="D54">
-        <v>1808.263701958559</v>
+        <v>796.4290489254915</v>
       </c>
       <c r="E54">
-        <v>959.348</v>
+        <v>730.652</v>
       </c>
       <c r="F54">
-        <v>1094.548</v>
+        <v>865.8520000000001</v>
       </c>
       <c r="G54">
         <v>60.6</v>
       </c>
       <c r="H54">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -5655,45 +5655,45 @@
         <v>102.2</v>
       </c>
       <c r="M54">
-        <v>67.05191112064988</v>
+        <v>185.1191576</v>
       </c>
       <c r="N54">
-        <v>35.14808887935013</v>
+        <v>-82.91915760000002</v>
       </c>
       <c r="O54">
-        <v>10.89590755259854</v>
+        <v>-25.70493885600001</v>
       </c>
       <c r="P54">
-        <v>24.25218132675159</v>
+        <v>-57.21421874400001</v>
       </c>
       <c r="Q54">
-        <v>62.05218132675159</v>
+        <v>-19.41421874400001</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.099413666043175</v>
+        <v>0.1641211876326555</v>
       </c>
       <c r="T54">
-        <v>1.302887296728422</v>
+        <v>1.224423315639132</v>
       </c>
       <c r="U54">
-        <v>0.06125990922339621</v>
+        <v>0.2138</v>
       </c>
       <c r="V54">
-        <v>0.31</v>
+        <v>0.171143821151442</v>
       </c>
       <c r="W54">
-        <v>0.04226933736414338</v>
+        <v>0.1772094510378217</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.524192201115736</v>
+        <v>0.5520768424240063</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5704,25 +5704,25 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.08789287845873363</v>
+        <v>0.1726770846033419</v>
       </c>
       <c r="C55">
-        <v>301.2990554293208</v>
+        <v>-35.88462620796486</v>
       </c>
       <c r="D55">
-        <v>1356.296055429321</v>
+        <v>786.0183737920353</v>
       </c>
       <c r="E55">
-        <v>980.3970000000002</v>
+        <v>747.3030000000001</v>
       </c>
       <c r="F55">
-        <v>1115.597</v>
+        <v>882.5030000000002</v>
       </c>
       <c r="G55">
         <v>60.6</v>
       </c>
       <c r="H55">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -5737,45 +5737,45 @@
         <v>102.2</v>
       </c>
       <c r="M55">
-        <v>115.0180507</v>
+        <v>188.6791414</v>
       </c>
       <c r="N55">
-        <v>-12.81805070000001</v>
+        <v>-86.47914140000002</v>
       </c>
       <c r="O55">
-        <v>-3.973595717000005</v>
+        <v>-26.80853383400001</v>
       </c>
       <c r="P55">
-        <v>-8.844454983000009</v>
+        <v>-59.67060756600001</v>
       </c>
       <c r="Q55">
-        <v>28.95554501699999</v>
+        <v>-21.87060756600001</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1027689890435877</v>
+        <v>0.1667875958801588</v>
       </c>
       <c r="T55">
-        <v>1.354736634075701</v>
+        <v>1.250474875546347</v>
       </c>
       <c r="U55">
-        <v>0.1031</v>
+        <v>0.2138</v>
       </c>
       <c r="V55">
-        <v>0.2754524164440564</v>
+        <v>0.1679146924504714</v>
       </c>
       <c r="W55">
-        <v>0.07470085586461779</v>
+        <v>0.1778998387540892</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.8885561820776013</v>
+        <v>0.541660298227327</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5786,25 +5786,25 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.08877287845873363</v>
+        <v>0.1744270846033419</v>
       </c>
       <c r="C56">
-        <v>264.0495138766198</v>
+        <v>-62.67764288670537</v>
       </c>
       <c r="D56">
-        <v>1340.09551387662</v>
+        <v>775.8763571132947</v>
       </c>
       <c r="E56">
-        <v>1001.446</v>
+        <v>763.9540000000002</v>
       </c>
       <c r="F56">
-        <v>1136.646</v>
+        <v>899.1540000000001</v>
       </c>
       <c r="G56">
         <v>60.6</v>
       </c>
       <c r="H56">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -5819,45 +5819,45 @@
         <v>102.2</v>
       </c>
       <c r="M56">
-        <v>117.1882026</v>
+        <v>192.2391252</v>
       </c>
       <c r="N56">
-        <v>-14.98820260000001</v>
+        <v>-90.03912520000002</v>
       </c>
       <c r="O56">
-        <v>-4.646342806000002</v>
+        <v>-27.91212881200001</v>
       </c>
       <c r="P56">
-        <v>-10.341859794</v>
+        <v>-62.12699638800001</v>
       </c>
       <c r="Q56">
-        <v>27.45814020599999</v>
+        <v>-24.32699638800001</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1046748366314917</v>
+        <v>0.1695699349210318</v>
       </c>
       <c r="T56">
-        <v>1.384187430468651</v>
+        <v>1.277659111971268</v>
       </c>
       <c r="U56">
-        <v>0.1031</v>
+        <v>0.2138</v>
       </c>
       <c r="V56">
-        <v>0.2703514457691665</v>
+        <v>0.164805161108796</v>
       </c>
       <c r="W56">
-        <v>0.07522676594119894</v>
+        <v>0.1785646565549394</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.8721014379650532</v>
+        <v>0.531629551963858</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5868,25 +5868,25 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.08965287845873363</v>
+        <v>0.1761770846033419</v>
       </c>
       <c r="C57">
-        <v>227.1824250705092</v>
+        <v>-89.21226815702403</v>
       </c>
       <c r="D57">
-        <v>1324.277425070509</v>
+        <v>765.9927318429761</v>
       </c>
       <c r="E57">
-        <v>1022.495</v>
+        <v>780.6050000000002</v>
       </c>
       <c r="F57">
-        <v>1157.695</v>
+        <v>915.8050000000002</v>
       </c>
       <c r="G57">
         <v>60.6</v>
       </c>
       <c r="H57">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -5901,45 +5901,45 @@
         <v>102.2</v>
       </c>
       <c r="M57">
-        <v>119.3583545</v>
+        <v>195.799109</v>
       </c>
       <c r="N57">
-        <v>-17.15835450000002</v>
+        <v>-93.59910900000001</v>
       </c>
       <c r="O57">
-        <v>-5.319089895000005</v>
+        <v>-29.01572379000001</v>
       </c>
       <c r="P57">
-        <v>-11.83926460500001</v>
+        <v>-64.58338521</v>
       </c>
       <c r="Q57">
-        <v>25.96073539499999</v>
+        <v>-26.78338521000001</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.106665388556636</v>
+        <v>0.1724759334748325</v>
       </c>
       <c r="T57">
-        <v>1.414947151145732</v>
+        <v>1.306051536681741</v>
       </c>
       <c r="U57">
-        <v>0.1031</v>
+        <v>0.2138</v>
       </c>
       <c r="V57">
-        <v>0.2654359649369998</v>
+        <v>0.1618087036340906</v>
       </c>
       <c r="W57">
-        <v>0.07573355201499532</v>
+        <v>0.1792052991630314</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.8562450481838704</v>
+        <v>0.5219635601099697</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5950,25 +5950,25 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09053287845873363</v>
+        <v>0.1779270846033419</v>
       </c>
       <c r="C58">
-        <v>190.6844039291566</v>
+        <v>-115.498252492008</v>
       </c>
       <c r="D58">
-        <v>1308.828403929157</v>
+        <v>756.3577475079921</v>
       </c>
       <c r="E58">
-        <v>1043.544</v>
+        <v>797.2560000000001</v>
       </c>
       <c r="F58">
-        <v>1178.744</v>
+        <v>932.4560000000001</v>
       </c>
       <c r="G58">
         <v>60.6</v>
       </c>
       <c r="H58">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -5983,45 +5983,45 @@
         <v>102.2</v>
       </c>
       <c r="M58">
-        <v>121.5285064</v>
+        <v>199.3590928</v>
       </c>
       <c r="N58">
-        <v>-19.32850640000001</v>
+        <v>-97.15909280000001</v>
       </c>
       <c r="O58">
-        <v>-5.991836984000003</v>
+        <v>-30.11931876800001</v>
       </c>
       <c r="P58">
-        <v>-13.33666941600001</v>
+        <v>-67.039774032</v>
       </c>
       <c r="Q58">
-        <v>24.46333058399999</v>
+        <v>-29.239774032</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1087464201147414</v>
+        <v>0.1755140228719878</v>
       </c>
       <c r="T58">
-        <v>1.447105040944499</v>
+        <v>1.33573452615178</v>
       </c>
       <c r="U58">
-        <v>0.1031</v>
+        <v>0.2138</v>
       </c>
       <c r="V58">
-        <v>0.2606960369916962</v>
+        <v>0.1589192624977676</v>
       </c>
       <c r="W58">
-        <v>0.07622223858615612</v>
+        <v>0.1798230616779773</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.8409549580377299</v>
+        <v>0.512642782250863</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6032,25 +6032,25 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09141287845873361</v>
+        <v>0.1796770846033419</v>
       </c>
       <c r="C59">
-        <v>154.5426827696417</v>
+        <v>-141.5448618763576</v>
       </c>
       <c r="D59">
-        <v>1293.735682769642</v>
+        <v>746.9621381236426</v>
       </c>
       <c r="E59">
-        <v>1064.593</v>
+        <v>813.9070000000002</v>
       </c>
       <c r="F59">
-        <v>1199.793</v>
+        <v>949.1070000000002</v>
       </c>
       <c r="G59">
         <v>60.6</v>
       </c>
       <c r="H59">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -6065,45 +6065,45 @@
         <v>102.2</v>
       </c>
       <c r="M59">
-        <v>123.6986583</v>
+        <v>202.9190766</v>
       </c>
       <c r="N59">
-        <v>-21.4986583</v>
+        <v>-100.7190766</v>
       </c>
       <c r="O59">
-        <v>-6.664584073</v>
+        <v>-31.22291374600002</v>
       </c>
       <c r="P59">
-        <v>-14.834074227</v>
+        <v>-69.49616285400002</v>
       </c>
       <c r="Q59">
-        <v>22.965925773</v>
+        <v>-31.69616285400002</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.11092424383834</v>
+        <v>0.1786934187527317</v>
       </c>
       <c r="T59">
-        <v>1.480758646547859</v>
+        <v>1.366798119783217</v>
       </c>
       <c r="U59">
-        <v>0.1031</v>
+        <v>0.2138</v>
       </c>
       <c r="V59">
-        <v>0.2561224223076314</v>
+        <v>0.1561312052609646</v>
       </c>
       <c r="W59">
-        <v>0.0766937782600832</v>
+        <v>0.1804191483152058</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.826201362282682</v>
+        <v>0.5036490492289181</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6114,25 +6114,25 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.0922928784587336</v>
+        <v>0.1965422829099082</v>
       </c>
       <c r="C60">
-        <v>118.7450761161681</v>
+        <v>-238.058181316396</v>
       </c>
       <c r="D60">
-        <v>1278.987076116168</v>
+        <v>667.099818683604</v>
       </c>
       <c r="E60">
-        <v>1085.642</v>
+        <v>830.558</v>
       </c>
       <c r="F60">
-        <v>1220.842</v>
+        <v>965.758</v>
       </c>
       <c r="G60">
         <v>60.6</v>
       </c>
       <c r="H60">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -6147,45 +6147,45 @@
         <v>102.2</v>
       </c>
       <c r="M60">
-        <v>125.8688102</v>
+        <v>230.6230104</v>
       </c>
       <c r="N60">
-        <v>-23.66881019999998</v>
+        <v>-128.4230104</v>
       </c>
       <c r="O60">
-        <v>-7.337331161999995</v>
+        <v>-39.81113322400001</v>
       </c>
       <c r="P60">
-        <v>-16.33147903799999</v>
+        <v>-88.61187717600001</v>
       </c>
       <c r="Q60">
-        <v>21.46852096200001</v>
+        <v>-50.81187717600001</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1132057734535385</v>
+        <v>0.1834889723100975</v>
       </c>
       <c r="T60">
-        <v>1.516014804798998</v>
+        <v>1.413652029309245</v>
       </c>
       <c r="U60">
-        <v>0.1031</v>
+        <v>0.2388</v>
       </c>
       <c r="V60">
-        <v>0.2517065184747413</v>
+        <v>0.1373757108843984</v>
       </c>
       <c r="W60">
-        <v>0.07714905794525416</v>
+        <v>0.2059946802408057</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.8119565112088429</v>
+        <v>0.4431474544658013</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6196,25 +6196,25 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1058327044409004</v>
+        <v>0.1985422829099082</v>
       </c>
       <c r="C61">
-        <v>-93.16412749798747</v>
+        <v>-263.0613822056225</v>
       </c>
       <c r="D61">
-        <v>1088.126872502013</v>
+        <v>658.7476177943774</v>
       </c>
       <c r="E61">
-        <v>1106.691</v>
+        <v>847.2090000000001</v>
       </c>
       <c r="F61">
-        <v>1241.891</v>
+        <v>982.409</v>
       </c>
       <c r="G61">
         <v>60.6</v>
       </c>
       <c r="H61">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -6229,45 +6229,45 @@
         <v>102.2</v>
       </c>
       <c r="M61">
-        <v>152.3229463099458</v>
+        <v>234.5992692</v>
       </c>
       <c r="N61">
-        <v>-50.12294630994576</v>
+        <v>-132.3992692</v>
       </c>
       <c r="O61">
-        <v>-15.53811335608319</v>
+        <v>-41.043773452</v>
       </c>
       <c r="P61">
-        <v>-34.58483295386257</v>
+        <v>-91.35549574799998</v>
       </c>
       <c r="Q61">
-        <v>3.215167046137424</v>
+        <v>-53.55549574799998</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1183374834650687</v>
+        <v>0.187017971634734</v>
       </c>
       <c r="T61">
-        <v>1.595314402341026</v>
+        <v>1.448131347097276</v>
       </c>
       <c r="U61">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V61">
-        <v>0.2079923003559403</v>
+        <v>0.1350473090050018</v>
       </c>
       <c r="W61">
-        <v>0.09714294274613935</v>
+        <v>0.2065507026096056</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.6709429043740008</v>
+        <v>0.4356364806612961</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6278,25 +6278,25 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1069082448241542</v>
+        <v>0.2005422829099083</v>
       </c>
       <c r="C62">
-        <v>-126.9606143464855</v>
+        <v>-287.8580273139128</v>
       </c>
       <c r="D62">
-        <v>1075.379385653515</v>
+        <v>650.6019726860873</v>
       </c>
       <c r="E62">
-        <v>1127.74</v>
+        <v>863.8600000000001</v>
       </c>
       <c r="F62">
-        <v>1262.94</v>
+        <v>999.0600000000001</v>
       </c>
       <c r="G62">
         <v>60.6</v>
       </c>
       <c r="H62">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -6311,45 +6311,45 @@
         <v>102.2</v>
       </c>
       <c r="M62">
-        <v>154.9046911626567</v>
+        <v>238.575528</v>
       </c>
       <c r="N62">
-        <v>-52.70469116265669</v>
+        <v>-136.375528</v>
       </c>
       <c r="O62">
-        <v>-16.33845426042357</v>
+        <v>-42.27641368000002</v>
       </c>
       <c r="P62">
-        <v>-36.36623690223311</v>
+        <v>-94.09911432000001</v>
       </c>
       <c r="Q62">
-        <v>1.433763097766885</v>
+        <v>-56.29911432000002</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1209184205516955</v>
+        <v>0.1907234209256024</v>
       </c>
       <c r="T62">
-        <v>1.635197262399552</v>
+        <v>1.484334630774708</v>
       </c>
       <c r="U62">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V62">
-        <v>0.2045257620166746</v>
+        <v>0.1327965205215851</v>
       </c>
       <c r="W62">
-        <v>0.09756812767246005</v>
+        <v>0.2070881908994455</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.6597605226344343</v>
+        <v>0.4283758726502744</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6360,25 +6360,25 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.107983785207408</v>
+        <v>0.2025422829099083</v>
       </c>
       <c r="C63">
-        <v>-160.4618841803035</v>
+        <v>-312.4556854540591</v>
       </c>
       <c r="D63">
-        <v>1062.927115819697</v>
+        <v>642.6553145459409</v>
       </c>
       <c r="E63">
-        <v>1148.789</v>
+        <v>880.511</v>
       </c>
       <c r="F63">
-        <v>1283.989</v>
+        <v>1015.711</v>
       </c>
       <c r="G63">
         <v>60.6</v>
       </c>
       <c r="H63">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -6393,45 +6393,45 @@
         <v>102.2</v>
       </c>
       <c r="M63">
-        <v>157.4864360153676</v>
+        <v>242.5517868</v>
       </c>
       <c r="N63">
-        <v>-55.28643601536764</v>
+        <v>-140.3517868</v>
       </c>
       <c r="O63">
-        <v>-17.13879516476397</v>
+        <v>-43.50905390800001</v>
       </c>
       <c r="P63">
-        <v>-38.14764085060367</v>
+        <v>-96.842732892</v>
       </c>
       <c r="Q63">
-        <v>-0.3476408506036748</v>
+        <v>-59.042732892</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1236317133863543</v>
+        <v>0.1946188932570281</v>
       </c>
       <c r="T63">
-        <v>1.677125397332874</v>
+        <v>1.522394493102264</v>
       </c>
       <c r="U63">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V63">
-        <v>0.201172880672139</v>
+        <v>0.130619528381887</v>
       </c>
       <c r="W63">
-        <v>0.09797937210939318</v>
+        <v>0.2076080566224054</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.6489447763617385</v>
+        <v>0.4213533173609257</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6442,25 +6442,25 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1090593255906618</v>
+        <v>0.2045422829099083</v>
       </c>
       <c r="C64">
-        <v>-193.6780749336733</v>
+        <v>-336.8615601096143</v>
       </c>
       <c r="D64">
-        <v>1050.759925066327</v>
+        <v>634.9004398903858</v>
       </c>
       <c r="E64">
-        <v>1169.838</v>
+        <v>897.162</v>
       </c>
       <c r="F64">
-        <v>1305.038</v>
+        <v>1032.362</v>
       </c>
       <c r="G64">
         <v>60.6</v>
       </c>
       <c r="H64">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -6475,45 +6475,45 @@
         <v>102.2</v>
       </c>
       <c r="M64">
-        <v>160.0681808680786</v>
+        <v>246.5280456</v>
       </c>
       <c r="N64">
-        <v>-57.86818086807857</v>
+        <v>-144.3280456000001</v>
       </c>
       <c r="O64">
-        <v>-17.93913606910436</v>
+        <v>-44.74169413600002</v>
       </c>
       <c r="P64">
-        <v>-39.92904479897421</v>
+        <v>-99.58635146400003</v>
       </c>
       <c r="Q64">
-        <v>-2.129044798974213</v>
+        <v>-61.78635146400003</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1264878111070478</v>
+        <v>0.1987193904480025</v>
       </c>
       <c r="T64">
-        <v>1.721260276210055</v>
+        <v>1.56245750607864</v>
       </c>
       <c r="U64">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V64">
-        <v>0.1979281567903303</v>
+        <v>0.1285127617950824</v>
       </c>
       <c r="W64">
-        <v>0.09837735059674782</v>
+        <v>0.2081111524833344</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.6384779251300976</v>
+        <v>0.4145572961131687</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6524,25 +6524,25 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1101348659739156</v>
+        <v>0.2065422829099083</v>
       </c>
       <c r="C65">
-        <v>-226.6188656036763</v>
+        <v>-361.0825112140878</v>
       </c>
       <c r="D65">
-        <v>1038.868134396324</v>
+        <v>627.3304887859123</v>
       </c>
       <c r="E65">
-        <v>1190.887</v>
+        <v>913.8130000000001</v>
       </c>
       <c r="F65">
-        <v>1326.087</v>
+        <v>1049.013</v>
       </c>
       <c r="G65">
         <v>60.6</v>
       </c>
       <c r="H65">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -6557,45 +6557,45 @@
         <v>102.2</v>
       </c>
       <c r="M65">
-        <v>162.6499257207895</v>
+        <v>250.5043044000001</v>
       </c>
       <c r="N65">
-        <v>-60.44992572078952</v>
+        <v>-148.3043044</v>
       </c>
       <c r="O65">
-        <v>-18.73947697344475</v>
+        <v>-45.97433436400002</v>
       </c>
       <c r="P65">
-        <v>-41.71044874734477</v>
+        <v>-102.329970036</v>
       </c>
       <c r="Q65">
-        <v>-3.910448747344773</v>
+        <v>-64.52997003600002</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1294982924883194</v>
+        <v>0.2030415361357864</v>
       </c>
       <c r="T65">
-        <v>1.767780824215732</v>
+        <v>1.604686087324009</v>
       </c>
       <c r="U65">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V65">
-        <v>0.1947864400158806</v>
+        <v>0.1264728766872239</v>
       </c>
       <c r="W65">
-        <v>0.09876269484640866</v>
+        <v>0.208598277047091</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.6283433548899373</v>
+        <v>0.40797702157169</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6606,25 +6606,25 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1112104063571694</v>
+        <v>0.2085422829099082</v>
       </c>
       <c r="C66">
-        <v>-259.2935019293252</v>
+        <v>-385.1250753904559</v>
       </c>
       <c r="D66">
-        <v>1027.242498070675</v>
+        <v>619.9389246095443</v>
       </c>
       <c r="E66">
-        <v>1211.936</v>
+        <v>930.4640000000002</v>
       </c>
       <c r="F66">
-        <v>1347.136</v>
+        <v>1065.664</v>
       </c>
       <c r="G66">
         <v>60.6</v>
       </c>
       <c r="H66">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -6639,45 +6639,45 @@
         <v>102.2</v>
       </c>
       <c r="M66">
-        <v>165.2316705735005</v>
+        <v>254.4805632000001</v>
       </c>
       <c r="N66">
-        <v>-63.03167057350048</v>
+        <v>-152.2805632000001</v>
       </c>
       <c r="O66">
-        <v>-19.53981787778515</v>
+        <v>-47.20697459200003</v>
       </c>
       <c r="P66">
-        <v>-43.49185269571533</v>
+        <v>-105.0735886080001</v>
       </c>
       <c r="Q66">
-        <v>-5.691852695715333</v>
+        <v>-67.27358860800005</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1326760228352172</v>
+        <v>0.2076038010284471</v>
       </c>
       <c r="T66">
-        <v>1.816885847110613</v>
+        <v>1.649260700860786</v>
       </c>
       <c r="U66">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V66">
-        <v>0.1917429018906325</v>
+        <v>0.124496737988986</v>
       </c>
       <c r="W66">
-        <v>0.09913599708826761</v>
+        <v>0.2090701789682301</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.6185254899697821</v>
+        <v>0.4016023806096322</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6688,25 +6688,25 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1122859467404232</v>
+        <v>0.2105422829099083</v>
       </c>
       <c r="C67">
-        <v>-291.7108203655337</v>
+        <v>-408.9954847764922</v>
       </c>
       <c r="D67">
-        <v>1015.874179634466</v>
+        <v>612.7195152235079</v>
       </c>
       <c r="E67">
-        <v>1232.985</v>
+        <v>947.115</v>
       </c>
       <c r="F67">
-        <v>1368.185</v>
+        <v>1082.315</v>
       </c>
       <c r="G67">
         <v>60.6</v>
       </c>
       <c r="H67">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -6721,45 +6721,45 @@
         <v>102.2</v>
       </c>
       <c r="M67">
-        <v>167.8134154262114</v>
+        <v>258.456822</v>
       </c>
       <c r="N67">
-        <v>-65.61341542621143</v>
+        <v>-156.2568220000001</v>
       </c>
       <c r="O67">
-        <v>-20.34015878212555</v>
+        <v>-48.43961482000002</v>
       </c>
       <c r="P67">
-        <v>-45.27325664408589</v>
+        <v>-107.81720718</v>
       </c>
       <c r="Q67">
-        <v>-7.473256644085893</v>
+        <v>-70.01720718000003</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1360353377733662</v>
+        <v>0.2124267667721171</v>
       </c>
       <c r="T67">
-        <v>1.868796871313773</v>
+        <v>1.696382435171095</v>
       </c>
       <c r="U67">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V67">
-        <v>0.188793011092315</v>
+        <v>0.1225814035583862</v>
       </c>
       <c r="W67">
-        <v>0.09949781310730012</v>
+        <v>0.2095275608302574</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.6090097132010162</v>
+        <v>0.3954238824464071</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6770,25 +6770,25 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1133614871236771</v>
+        <v>0.2125422829099083</v>
       </c>
       <c r="C68">
-        <v>-323.8792704826126</v>
+        <v>-432.6996845498741</v>
       </c>
       <c r="D68">
-        <v>1004.754729517388</v>
+        <v>605.666315450126</v>
       </c>
       <c r="E68">
-        <v>1254.034</v>
+        <v>963.7660000000001</v>
       </c>
       <c r="F68">
-        <v>1389.234</v>
+        <v>1098.966</v>
       </c>
       <c r="G68">
         <v>60.6</v>
       </c>
       <c r="H68">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -6803,45 +6803,45 @@
         <v>102.2</v>
       </c>
       <c r="M68">
-        <v>170.3951602789224</v>
+        <v>262.4330808</v>
       </c>
       <c r="N68">
-        <v>-68.19516027892239</v>
+        <v>-160.2330808</v>
       </c>
       <c r="O68">
-        <v>-21.14049968646594</v>
+        <v>-49.67225504800002</v>
       </c>
       <c r="P68">
-        <v>-47.05466059245644</v>
+        <v>-110.560825752</v>
       </c>
       <c r="Q68">
-        <v>-9.254660592456446</v>
+        <v>-72.76082575200003</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1395922594725829</v>
+        <v>0.2175334363830617</v>
       </c>
       <c r="T68">
-        <v>1.923761485175944</v>
+        <v>1.746276036205539</v>
       </c>
       <c r="U68">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V68">
-        <v>0.1859325109242496</v>
+        <v>0.1207241095650774</v>
       </c>
       <c r="W68">
-        <v>0.09984866500454379</v>
+        <v>0.2099710826358595</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.599782293304031</v>
+        <v>0.3894326115002494</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6852,25 +6852,25 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1144370275069309</v>
+        <v>0.2145422829099083</v>
       </c>
       <c r="C69">
-        <v>-355.8069359106253</v>
+        <v>-456.2433492566439</v>
       </c>
       <c r="D69">
-        <v>993.8760640893748</v>
+        <v>598.7736507433563</v>
       </c>
       <c r="E69">
-        <v>1275.083</v>
+        <v>980.4170000000001</v>
       </c>
       <c r="F69">
-        <v>1410.283</v>
+        <v>1115.617</v>
       </c>
       <c r="G69">
         <v>60.6</v>
       </c>
       <c r="H69">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -6885,45 +6885,45 @@
         <v>102.2</v>
       </c>
       <c r="M69">
-        <v>172.9769051316333</v>
+        <v>266.4093396000001</v>
       </c>
       <c r="N69">
-        <v>-70.77690513163331</v>
+        <v>-164.2093396000001</v>
       </c>
       <c r="O69">
-        <v>-21.94084059080633</v>
+        <v>-50.90489527600003</v>
       </c>
       <c r="P69">
-        <v>-48.83606454082698</v>
+        <v>-113.304444324</v>
       </c>
       <c r="Q69">
-        <v>-11.03606454082698</v>
+        <v>-75.50444432400005</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1433647521838733</v>
+        <v>0.2229496011219424</v>
       </c>
       <c r="T69">
-        <v>1.982057287757033</v>
+        <v>1.799193491848131</v>
       </c>
       <c r="U69">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V69">
-        <v>0.1831573988209026</v>
+        <v>0.118922257183509</v>
       </c>
       <c r="W69">
-        <v>0.1001890437108249</v>
+        <v>0.2104013649845781</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.5908303187771052</v>
+        <v>0.3836201844629322</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6934,25 +6934,25 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1155125678901847</v>
+        <v>0.2165422829099083</v>
       </c>
       <c r="C70">
-        <v>-387.5015539377089</v>
+        <v>-479.6318980372778</v>
       </c>
       <c r="D70">
-        <v>983.2304460622913</v>
+        <v>592.0361019627225</v>
       </c>
       <c r="E70">
-        <v>1296.132</v>
+        <v>997.0680000000002</v>
       </c>
       <c r="F70">
-        <v>1431.332</v>
+        <v>1132.268</v>
       </c>
       <c r="G70">
         <v>60.6</v>
       </c>
       <c r="H70">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -6967,45 +6967,45 @@
         <v>102.2</v>
       </c>
       <c r="M70">
-        <v>175.5586499843443</v>
+        <v>270.3855984</v>
       </c>
       <c r="N70">
-        <v>-73.35864998434427</v>
+        <v>-168.1855984000001</v>
       </c>
       <c r="O70">
-        <v>-22.74118149514672</v>
+        <v>-52.13753550400003</v>
       </c>
       <c r="P70">
-        <v>-50.61746848919755</v>
+        <v>-116.048062896</v>
       </c>
       <c r="Q70">
-        <v>-12.81746848919755</v>
+        <v>-78.24806289600004</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1473730256896193</v>
+        <v>0.2287042761570031</v>
       </c>
       <c r="T70">
-        <v>2.04399657799944</v>
+        <v>1.855418288468385</v>
       </c>
       <c r="U70">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V70">
-        <v>0.1804639076617717</v>
+        <v>0.1171734004602221</v>
       </c>
       <c r="W70">
-        <v>0.100519411278686</v>
+        <v>0.210818991970099</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.5821416376186184</v>
+        <v>0.3779787111620068</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7016,25 +7016,25 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1165881082734385</v>
+        <v>0.2185422829099083</v>
       </c>
       <c r="C71">
-        <v>-418.9705338622082</v>
+        <v>-502.8705088362286</v>
       </c>
       <c r="D71">
-        <v>972.8104661377919</v>
+        <v>585.4484911637715</v>
       </c>
       <c r="E71">
-        <v>1317.181</v>
+        <v>1013.719</v>
       </c>
       <c r="F71">
-        <v>1452.381</v>
+        <v>1148.919</v>
       </c>
       <c r="G71">
         <v>60.6</v>
       </c>
       <c r="H71">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -7049,45 +7049,45 @@
         <v>102.2</v>
       </c>
       <c r="M71">
-        <v>178.1403948370552</v>
+        <v>274.3618572</v>
       </c>
       <c r="N71">
-        <v>-75.94039483705519</v>
+        <v>-172.1618572</v>
       </c>
       <c r="O71">
-        <v>-23.54152239948711</v>
+        <v>-53.37017573200002</v>
       </c>
       <c r="P71">
-        <v>-52.39887243756809</v>
+        <v>-118.791681468</v>
       </c>
       <c r="Q71">
-        <v>-14.59887243756809</v>
+        <v>-80.99168146800002</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1516398974860587</v>
+        <v>0.2348302205491645</v>
       </c>
       <c r="T71">
-        <v>2.109931951483293</v>
+        <v>1.915270491322204</v>
       </c>
       <c r="U71">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V71">
-        <v>0.1778484887101518</v>
+        <v>0.115475235236161</v>
       </c>
       <c r="W71">
-        <v>0.100840202975015</v>
+        <v>0.2112245138256048</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.5737048022908123</v>
+        <v>0.3725007588263256</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7098,25 +7098,25 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1176636486566923</v>
+        <v>0.2205422829099083</v>
       </c>
       <c r="C72">
-        <v>-450.2209741901103</v>
+        <v>-525.9641316732489</v>
       </c>
       <c r="D72">
-        <v>962.60902580989</v>
+        <v>579.0058683267513</v>
       </c>
       <c r="E72">
-        <v>1338.23</v>
+        <v>1030.37</v>
       </c>
       <c r="F72">
-        <v>1473.43</v>
+        <v>1165.57</v>
       </c>
       <c r="G72">
         <v>60.6</v>
       </c>
       <c r="H72">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -7131,45 +7131,45 @@
         <v>102.2</v>
       </c>
       <c r="M72">
-        <v>180.7221396897662</v>
+        <v>278.3381160000001</v>
       </c>
       <c r="N72">
-        <v>-78.52213968976618</v>
+        <v>-176.1381160000001</v>
       </c>
       <c r="O72">
-        <v>-24.34186330382752</v>
+        <v>-54.60281596000004</v>
       </c>
       <c r="P72">
-        <v>-54.18027638593866</v>
+        <v>-121.53530004</v>
       </c>
       <c r="Q72">
-        <v>-16.38027638593866</v>
+        <v>-83.73530004000004</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1561912274022607</v>
+        <v>0.2413645612341366</v>
       </c>
       <c r="T72">
-        <v>2.180263016532737</v>
+        <v>1.979112841032944</v>
       </c>
       <c r="U72">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V72">
-        <v>0.1753077960142925</v>
+        <v>0.1138255890185015</v>
       </c>
       <c r="W72">
-        <v>0.1011518291943059</v>
+        <v>0.2116184493423819</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.5655090194009436</v>
+        <v>0.3671793194145209</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7180,25 +7180,25 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1187391890399461</v>
+        <v>0.2225422829099082</v>
       </c>
       <c r="C73">
-        <v>-481.2596787616509</v>
+        <v>-548.9175010479738</v>
       </c>
       <c r="D73">
-        <v>952.6193212383491</v>
+        <v>572.7034989520262</v>
       </c>
       <c r="E73">
-        <v>1359.279</v>
+        <v>1047.021</v>
       </c>
       <c r="F73">
-        <v>1494.479</v>
+        <v>1182.221</v>
       </c>
       <c r="G73">
         <v>60.6</v>
       </c>
       <c r="H73">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -7213,45 +7213,45 @@
         <v>102.2</v>
       </c>
       <c r="M73">
-        <v>183.3038845424771</v>
+        <v>282.3143748</v>
       </c>
       <c r="N73">
-        <v>-81.10388454247708</v>
+        <v>-180.1143748</v>
       </c>
       <c r="O73">
-        <v>-25.14220420816789</v>
+        <v>-55.83545618800001</v>
       </c>
       <c r="P73">
-        <v>-55.96168033430918</v>
+        <v>-124.278918612</v>
       </c>
       <c r="Q73">
-        <v>-18.16168033430918</v>
+        <v>-86.478918612</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1610564421402696</v>
+        <v>0.2483495461042792</v>
       </c>
       <c r="T73">
-        <v>2.255444499861451</v>
+        <v>2.04735811141339</v>
       </c>
       <c r="U73">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V73">
-        <v>0.1728386721267673</v>
+        <v>0.1122224117083818</v>
       </c>
       <c r="W73">
-        <v>0.1014546772102365</v>
+        <v>0.2120012880840385</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.5575441036347332</v>
+        <v>0.3620077797044573</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7262,25 +7262,25 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1198147294231999</v>
+        <v>0.2245422829099082</v>
       </c>
       <c r="C74">
-        <v>-512.0931718840928</v>
+        <v>-571.735147543105</v>
       </c>
       <c r="D74">
-        <v>942.8348281159072</v>
+        <v>566.5368524568951</v>
       </c>
       <c r="E74">
-        <v>1380.328</v>
+        <v>1063.672</v>
       </c>
       <c r="F74">
-        <v>1515.528</v>
+        <v>1198.872</v>
       </c>
       <c r="G74">
         <v>60.6</v>
       </c>
       <c r="H74">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -7295,45 +7295,45 @@
         <v>102.2</v>
       </c>
       <c r="M74">
-        <v>185.885629395188</v>
+        <v>286.2906336</v>
       </c>
       <c r="N74">
-        <v>-83.68562939518803</v>
+        <v>-184.0906336</v>
       </c>
       <c r="O74">
-        <v>-25.94254511250829</v>
+        <v>-57.06809641600002</v>
       </c>
       <c r="P74">
-        <v>-57.74308428267975</v>
+        <v>-127.022537184</v>
       </c>
       <c r="Q74">
-        <v>-19.94308428267975</v>
+        <v>-89.22253718400002</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1662691722167078</v>
+        <v>0.2558334584651463</v>
       </c>
       <c r="T74">
-        <v>2.335996089142217</v>
+        <v>2.120478043963868</v>
       </c>
       <c r="U74">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V74">
-        <v>0.1704381350138955</v>
+        <v>0.1106637671013209</v>
       </c>
       <c r="W74">
-        <v>0.1017491127812802</v>
+        <v>0.2123734924162046</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.5498004355286952</v>
+        <v>0.3569798938752287</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7344,25 +7344,25 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1208902698064537</v>
+        <v>0.2265422829099082</v>
       </c>
       <c r="C75">
-        <v>-542.7277125413959</v>
+        <v>-594.4214086859428</v>
       </c>
       <c r="D75">
-        <v>933.249287458604</v>
+        <v>560.5015913140574</v>
       </c>
       <c r="E75">
-        <v>1401.377</v>
+        <v>1080.323</v>
       </c>
       <c r="F75">
-        <v>1536.577</v>
+        <v>1215.523</v>
       </c>
       <c r="G75">
         <v>60.6</v>
       </c>
       <c r="H75">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -7377,45 +7377,45 @@
         <v>102.2</v>
       </c>
       <c r="M75">
-        <v>188.467374247899</v>
+        <v>290.2668924000001</v>
       </c>
       <c r="N75">
-        <v>-86.26737424789896</v>
+        <v>-188.0668924000001</v>
       </c>
       <c r="O75">
-        <v>-26.74288601684868</v>
+        <v>-58.30073664400004</v>
       </c>
       <c r="P75">
-        <v>-59.52448823105028</v>
+        <v>-129.766155756</v>
       </c>
       <c r="Q75">
-        <v>-21.72448823105029</v>
+        <v>-91.96615575600005</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1718680304469562</v>
+        <v>0.2638717347045961</v>
       </c>
       <c r="T75">
-        <v>2.422514462814151</v>
+        <v>2.199014267814382</v>
       </c>
       <c r="U75">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V75">
-        <v>0.1681033660411024</v>
+        <v>0.1091478250862343</v>
       </c>
       <c r="W75">
-        <v>0.1020354816243501</v>
+        <v>0.2127354993694072</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.5422689227132336</v>
+        <v>0.3520897583426913</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7426,25 +7426,25 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1219658101897075</v>
+        <v>0.2285422829099082</v>
       </c>
       <c r="C76">
-        <v>-573.1693077458184</v>
+        <v>-616.980439122998</v>
       </c>
       <c r="D76">
-        <v>923.8566922541816</v>
+        <v>554.593560877002</v>
       </c>
       <c r="E76">
-        <v>1422.426</v>
+        <v>1096.974</v>
       </c>
       <c r="F76">
-        <v>1557.626</v>
+        <v>1232.174</v>
       </c>
       <c r="G76">
         <v>60.6</v>
       </c>
       <c r="H76">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -7459,45 +7459,45 @@
         <v>102.2</v>
       </c>
       <c r="M76">
-        <v>191.0491191006099</v>
+        <v>294.2431512</v>
       </c>
       <c r="N76">
-        <v>-88.84911910060991</v>
+        <v>-192.0431512</v>
       </c>
       <c r="O76">
-        <v>-27.54322692118907</v>
+        <v>-59.53337687200001</v>
       </c>
       <c r="P76">
-        <v>-61.30589217942084</v>
+        <v>-132.509774328</v>
       </c>
       <c r="Q76">
-        <v>-23.50589217942084</v>
+        <v>-94.70977432799999</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1778975700795314</v>
+        <v>0.2725283398855421</v>
       </c>
       <c r="T76">
-        <v>2.51568809599931</v>
+        <v>2.283591739653397</v>
       </c>
       <c r="U76">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V76">
-        <v>0.1658316989324389</v>
+        <v>0.1076728544769609</v>
       </c>
       <c r="W76">
-        <v>0.1023141107689586</v>
+        <v>0.2130877223509017</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.5349409642981899</v>
+        <v>0.3473317886353576</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7508,25 +7508,25 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1230413505729614</v>
+        <v>0.2305422829099082</v>
       </c>
       <c r="C77">
-        <v>-603.4237250912968</v>
+        <v>-639.4162201578372</v>
       </c>
       <c r="D77">
-        <v>914.6512749087034</v>
+        <v>548.8087798421628</v>
       </c>
       <c r="E77">
-        <v>1443.475</v>
+        <v>1113.625</v>
       </c>
       <c r="F77">
-        <v>1578.675</v>
+        <v>1248.825</v>
       </c>
       <c r="G77">
         <v>60.6</v>
       </c>
       <c r="H77">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -7541,45 +7541,45 @@
         <v>102.2</v>
       </c>
       <c r="M77">
-        <v>193.6308639533209</v>
+        <v>298.21941</v>
       </c>
       <c r="N77">
-        <v>-91.43086395332087</v>
+        <v>-196.0194100000001</v>
       </c>
       <c r="O77">
-        <v>-28.34356782552947</v>
+        <v>-60.76601710000003</v>
       </c>
       <c r="P77">
-        <v>-63.0872961277914</v>
+        <v>-135.2533929</v>
       </c>
       <c r="Q77">
-        <v>-25.2872961277914</v>
+        <v>-97.45339290000003</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1844094728827127</v>
+        <v>0.2818774734809639</v>
       </c>
       <c r="T77">
-        <v>2.616315619839283</v>
+        <v>2.374935409239533</v>
       </c>
       <c r="U77">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V77">
-        <v>0.1636206096133397</v>
+        <v>0.1062372164172681</v>
       </c>
       <c r="W77">
-        <v>0.1025853098030442</v>
+        <v>0.2134305527195564</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.5278084181075473</v>
+        <v>0.3427006981202195</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7590,25 +7590,25 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1241168909562152</v>
+        <v>0.2325422829099082</v>
       </c>
       <c r="C78">
-        <v>-633.4965045637272</v>
+        <v>-661.7325686981696</v>
       </c>
       <c r="D78">
-        <v>905.627495436273</v>
+        <v>543.1434313018304</v>
       </c>
       <c r="E78">
-        <v>1464.524</v>
+        <v>1130.276</v>
       </c>
       <c r="F78">
-        <v>1599.724</v>
+        <v>1265.476</v>
       </c>
       <c r="G78">
         <v>60.6</v>
       </c>
       <c r="H78">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -7623,45 +7623,45 @@
         <v>102.2</v>
       </c>
       <c r="M78">
-        <v>196.2126088060318</v>
+        <v>302.1956688</v>
       </c>
       <c r="N78">
-        <v>-94.01260880603182</v>
+        <v>-199.9956688</v>
       </c>
       <c r="O78">
-        <v>-29.14390872986986</v>
+        <v>-61.99865732800002</v>
       </c>
       <c r="P78">
-        <v>-64.86870007616196</v>
+        <v>-137.997011472</v>
       </c>
       <c r="Q78">
-        <v>-27.06870007616196</v>
+        <v>-100.197011472</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1914640342528258</v>
+        <v>0.2920057015426707</v>
       </c>
       <c r="T78">
-        <v>2.72532877066592</v>
+        <v>2.47389105129118</v>
       </c>
       <c r="U78">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V78">
-        <v>0.1614677068552694</v>
+        <v>0.1048393583065146</v>
       </c>
       <c r="W78">
-        <v>0.1028493720204434</v>
+        <v>0.2137643612364043</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.5208635705008691</v>
+        <v>0.3381914784081114</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7672,25 +7672,25 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.125192431339469</v>
+        <v>0.2345422829099083</v>
       </c>
       <c r="C79">
-        <v>-663.3929696589729</v>
+        <v>-683.9331456544355</v>
       </c>
       <c r="D79">
-        <v>896.7800303410272</v>
+        <v>537.5938543455646</v>
       </c>
       <c r="E79">
-        <v>1485.573</v>
+        <v>1146.927</v>
       </c>
       <c r="F79">
-        <v>1620.773</v>
+        <v>1282.127</v>
       </c>
       <c r="G79">
         <v>60.6</v>
       </c>
       <c r="H79">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -7705,45 +7705,45 @@
         <v>102.2</v>
       </c>
       <c r="M79">
-        <v>198.7943536587428</v>
+        <v>306.1719276000001</v>
       </c>
       <c r="N79">
-        <v>-96.59435365874278</v>
+        <v>-203.9719276000001</v>
       </c>
       <c r="O79">
-        <v>-29.94424963421026</v>
+        <v>-63.23129755600003</v>
       </c>
       <c r="P79">
-        <v>-66.65010402453251</v>
+        <v>-140.7406300440001</v>
       </c>
       <c r="Q79">
-        <v>-28.85010402453251</v>
+        <v>-102.9406300440001</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.199132035742079</v>
+        <v>0.3030146450880043</v>
       </c>
       <c r="T79">
-        <v>2.843821325912264</v>
+        <v>2.581451531782101</v>
       </c>
       <c r="U79">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V79">
-        <v>0.1593707236493568</v>
+        <v>0.1034778081986377</v>
       </c>
       <c r="W79">
-        <v>0.1031065754789491</v>
+        <v>0.2140894994021653</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.5140991085463122</v>
+        <v>0.3337993812859281</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7754,25 +7754,25 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1262679717227228</v>
+        <v>0.2365422829099083</v>
       </c>
       <c r="C80">
-        <v>-693.1182378554739</v>
+        <v>-706.021463828723</v>
       </c>
       <c r="D80">
-        <v>888.1037621445262</v>
+        <v>532.1565361712773</v>
       </c>
       <c r="E80">
-        <v>1506.622</v>
+        <v>1163.578</v>
       </c>
       <c r="F80">
-        <v>1641.822</v>
+        <v>1298.778</v>
       </c>
       <c r="G80">
         <v>60.6</v>
       </c>
       <c r="H80">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -7787,45 +7787,45 @@
         <v>102.2</v>
       </c>
       <c r="M80">
-        <v>201.3760985114537</v>
+        <v>310.1481864000001</v>
       </c>
       <c r="N80">
-        <v>-99.1760985114537</v>
+        <v>-207.9481864000001</v>
       </c>
       <c r="O80">
-        <v>-30.74459053855065</v>
+        <v>-64.46393778400005</v>
       </c>
       <c r="P80">
-        <v>-68.43150797290306</v>
+        <v>-143.4842486160001</v>
       </c>
       <c r="Q80">
-        <v>-30.63150797290307</v>
+        <v>-105.6842486160001</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2074971282758099</v>
+        <v>0.3150244016829135</v>
       </c>
       <c r="T80">
-        <v>2.973085931635549</v>
+        <v>2.698790237772196</v>
       </c>
       <c r="U80">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V80">
-        <v>0.1573275092435959</v>
+        <v>0.1021511696319885</v>
       </c>
       <c r="W80">
-        <v>0.1033571839769803</v>
+        <v>0.2144063006918811</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.5075080943341801</v>
+        <v>0.3295199020386725</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7836,25 +7836,25 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1273435121059766</v>
+        <v>0.2385422829099083</v>
       </c>
       <c r="C81">
-        <v>-722.6772304847512</v>
+        <v>-728.0008953297415</v>
       </c>
       <c r="D81">
-        <v>879.5937695152488</v>
+        <v>526.8281046702585</v>
       </c>
       <c r="E81">
-        <v>1527.671</v>
+        <v>1180.229</v>
       </c>
       <c r="F81">
-        <v>1662.871</v>
+        <v>1315.429</v>
       </c>
       <c r="G81">
         <v>60.6</v>
       </c>
       <c r="H81">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -7869,45 +7869,45 @@
         <v>102.2</v>
       </c>
       <c r="M81">
-        <v>203.9578433641647</v>
+        <v>314.1244452</v>
       </c>
       <c r="N81">
-        <v>-101.7578433641647</v>
+        <v>-211.9244452</v>
       </c>
       <c r="O81">
-        <v>-31.54493144289104</v>
+        <v>-65.69657801200002</v>
       </c>
       <c r="P81">
-        <v>-70.21291192127362</v>
+        <v>-146.227867188</v>
       </c>
       <c r="Q81">
-        <v>-32.41291192127362</v>
+        <v>-108.427867188</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2166588962889437</v>
+        <v>0.3281779446201952</v>
       </c>
       <c r="T81">
-        <v>3.114661452189623</v>
+        <v>2.827304058618492</v>
       </c>
       <c r="U81">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V81">
-        <v>0.1553360217848161</v>
+        <v>0.1008581168518368</v>
       </c>
       <c r="W81">
-        <v>0.103601447956074</v>
+        <v>0.2147150816957814</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.5010839412413424</v>
+        <v>0.3253487640381831</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7918,25 +7918,25 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1583984400964488</v>
+        <v>0.2405422829099083</v>
       </c>
       <c r="C82">
-        <v>-934.3474344195524</v>
+        <v>-749.8746785467387</v>
       </c>
       <c r="D82">
-        <v>688.9725655804476</v>
+        <v>521.6053214532615</v>
       </c>
       <c r="E82">
-        <v>1548.72</v>
+        <v>1196.88</v>
       </c>
       <c r="F82">
-        <v>1683.92</v>
+        <v>1332.08</v>
       </c>
       <c r="G82">
         <v>60.6</v>
       </c>
       <c r="H82">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -7951,37 +7951,37 @@
         <v>102.2</v>
       </c>
       <c r="M82">
-        <v>266.8273459671972</v>
+        <v>318.1007040000001</v>
       </c>
       <c r="N82">
-        <v>-164.6273459671972</v>
+        <v>-215.9007040000001</v>
       </c>
       <c r="O82">
-        <v>-51.03447724983113</v>
+        <v>-66.92921824000004</v>
       </c>
       <c r="P82">
-        <v>-113.5928687173661</v>
+        <v>-148.97148576</v>
       </c>
       <c r="Q82">
-        <v>-75.79286871736606</v>
+        <v>-111.17148576</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.233425651080379</v>
+        <v>0.3426468418512049</v>
       </c>
       <c r="T82">
-        <v>3.373755770469356</v>
+        <v>2.968669261549416</v>
       </c>
       <c r="U82">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V82">
-        <v>0.1187359559611813</v>
+        <v>0.09959739039118883</v>
       </c>
       <c r="W82">
-        <v>0.1396416373504663</v>
+        <v>0.2150161431745841</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.383019212778004</v>
+        <v>0.3212819044877058</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8000,25 +8000,25 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1598320007998504</v>
+        <v>0.2425422829099083</v>
       </c>
       <c r="C83">
-        <v>-962.2206611992525</v>
+        <v>-771.645924712665</v>
       </c>
       <c r="D83">
-        <v>682.1483388007478</v>
+        <v>516.4850752873352</v>
       </c>
       <c r="E83">
-        <v>1569.769</v>
+        <v>1213.531</v>
       </c>
       <c r="F83">
-        <v>1704.969</v>
+        <v>1348.731</v>
       </c>
       <c r="G83">
         <v>60.6</v>
       </c>
       <c r="H83">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -8033,37 +8033,37 @@
         <v>102.2</v>
       </c>
       <c r="M83">
-        <v>270.1626877917872</v>
+        <v>322.0769628</v>
       </c>
       <c r="N83">
-        <v>-167.9626877917872</v>
+        <v>-219.8769628000001</v>
       </c>
       <c r="O83">
-        <v>-52.06843321545402</v>
+        <v>-68.16185846800003</v>
       </c>
       <c r="P83">
-        <v>-115.8942545763332</v>
+        <v>-151.715104332</v>
       </c>
       <c r="Q83">
-        <v>-78.09425457633316</v>
+        <v>-113.915104332</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2449164748214516</v>
+        <v>0.3586387808960051</v>
       </c>
       <c r="T83">
-        <v>3.551321863651953</v>
+        <v>3.124915012157281</v>
       </c>
       <c r="U83">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V83">
-        <v>0.1172700799616605</v>
+        <v>0.09836779297895193</v>
       </c>
       <c r="W83">
-        <v>0.1398739143009563</v>
+        <v>0.2153097710366263</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3782905805214855</v>
+        <v>0.3173154612224255</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8082,25 +8082,25 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1612655615032519</v>
+        <v>0.2445422829099083</v>
       </c>
       <c r="C84">
-        <v>-989.9600268526807</v>
+        <v>-793.3176240845436</v>
       </c>
       <c r="D84">
-        <v>675.4579731473195</v>
+        <v>511.4643759154567</v>
       </c>
       <c r="E84">
-        <v>1590.818</v>
+        <v>1230.182</v>
       </c>
       <c r="F84">
-        <v>1726.018</v>
+        <v>1365.382</v>
       </c>
       <c r="G84">
         <v>60.6</v>
       </c>
       <c r="H84">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -8115,37 +8115,37 @@
         <v>102.2</v>
       </c>
       <c r="M84">
-        <v>273.4980296163772</v>
+        <v>326.0532216000001</v>
       </c>
       <c r="N84">
-        <v>-171.2980296163772</v>
+        <v>-223.8532216000001</v>
       </c>
       <c r="O84">
-        <v>-53.10238918107692</v>
+        <v>-69.39449869600004</v>
       </c>
       <c r="P84">
-        <v>-118.1956404353002</v>
+        <v>-154.4587229040001</v>
       </c>
       <c r="Q84">
-        <v>-80.39564043530025</v>
+        <v>-116.6587229040001</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2576840567559767</v>
+        <v>0.3764076020568944</v>
       </c>
       <c r="T84">
-        <v>3.748617522743729</v>
+        <v>3.298521401721574</v>
       </c>
       <c r="U84">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V84">
-        <v>0.1158399570352988</v>
+        <v>0.09716818574750127</v>
       </c>
       <c r="W84">
-        <v>0.1401005259599709</v>
+        <v>0.2155962372434967</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3736772807590283</v>
+        <v>0.3134457604758105</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8164,25 +8164,25 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1626991222066535</v>
+        <v>0.2465422829099083</v>
       </c>
       <c r="C85">
-        <v>-1017.56943176991</v>
+        <v>-814.8926517668355</v>
       </c>
       <c r="D85">
-        <v>668.89756823009</v>
+        <v>506.5403482331647</v>
       </c>
       <c r="E85">
-        <v>1611.867</v>
+        <v>1246.833</v>
       </c>
       <c r="F85">
-        <v>1747.067</v>
+        <v>1382.033</v>
       </c>
       <c r="G85">
         <v>60.6</v>
       </c>
       <c r="H85">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -8197,37 +8197,37 @@
         <v>102.2</v>
       </c>
       <c r="M85">
-        <v>276.8333714409671</v>
+        <v>330.0294804000001</v>
       </c>
       <c r="N85">
-        <v>-174.6333714409671</v>
+        <v>-227.8294804000001</v>
       </c>
       <c r="O85">
-        <v>-54.1363451466998</v>
+        <v>-70.62713892400004</v>
       </c>
       <c r="P85">
-        <v>-120.4970262942673</v>
+        <v>-157.202341476</v>
       </c>
       <c r="Q85">
-        <v>-82.6970262942673</v>
+        <v>-119.402341476</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2719537071533871</v>
+        <v>0.3962668727661235</v>
       </c>
       <c r="T85">
-        <v>3.969124435846301</v>
+        <v>3.492552072411079</v>
       </c>
       <c r="U85">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V85">
-        <v>0.1144442949023434</v>
+        <v>0.09599748471439885</v>
       </c>
       <c r="W85">
-        <v>0.1403216770970816</v>
+        <v>0.2158758006502016</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3691751448462689</v>
+        <v>0.3096693055303188</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8246,25 +8246,25 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1641326829100551</v>
+        <v>0.2485422829099083</v>
       </c>
       <c r="C86">
-        <v>-1045.052626268</v>
+        <v>-836.373773201632</v>
       </c>
       <c r="D86">
-        <v>662.4633737319997</v>
+        <v>501.710226798368</v>
       </c>
       <c r="E86">
-        <v>1632.916</v>
+        <v>1263.484</v>
       </c>
       <c r="F86">
-        <v>1768.116</v>
+        <v>1398.684</v>
       </c>
       <c r="G86">
         <v>60.6</v>
       </c>
       <c r="H86">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -8279,37 +8279,37 @@
         <v>102.2</v>
       </c>
       <c r="M86">
-        <v>280.168713265557</v>
+        <v>334.0057392</v>
       </c>
       <c r="N86">
-        <v>-177.968713265557</v>
+        <v>-231.8057392</v>
       </c>
       <c r="O86">
-        <v>-55.17030111232268</v>
+        <v>-71.85977915200002</v>
       </c>
       <c r="P86">
-        <v>-122.7984121532344</v>
+        <v>-159.945960048</v>
       </c>
       <c r="Q86">
-        <v>-84.99841215323436</v>
+        <v>-122.145960048</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2880070638504737</v>
+        <v>0.418608552314006</v>
       </c>
       <c r="T86">
-        <v>4.217194713086693</v>
+        <v>3.710836576936769</v>
       </c>
       <c r="U86">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V86">
-        <v>0.1130818628201726</v>
+        <v>0.09485465751541795</v>
       </c>
       <c r="W86">
-        <v>0.1405375627309277</v>
+        <v>0.2161487077853182</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3647802026457181</v>
+        <v>0.3059827661787675</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8328,25 +8328,25 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1655662436134567</v>
+        <v>0.2505422829099083</v>
       </c>
       <c r="C87">
-        <v>-1072.41321774007</v>
+        <v>-857.7636493477047</v>
       </c>
       <c r="D87">
-        <v>656.1517822599302</v>
+        <v>496.9713506522954</v>
       </c>
       <c r="E87">
-        <v>1653.965</v>
+        <v>1280.135</v>
       </c>
       <c r="F87">
-        <v>1789.165</v>
+        <v>1415.335</v>
       </c>
       <c r="G87">
         <v>60.6</v>
       </c>
       <c r="H87">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -8361,37 +8361,37 @@
         <v>102.2</v>
       </c>
       <c r="M87">
-        <v>283.5040550901469</v>
+        <v>337.981998</v>
       </c>
       <c r="N87">
-        <v>-181.304055090147</v>
+        <v>-235.781998</v>
       </c>
       <c r="O87">
-        <v>-56.20425707794556</v>
+        <v>-73.09241938000002</v>
       </c>
       <c r="P87">
-        <v>-125.0997980122014</v>
+        <v>-162.68957862</v>
       </c>
       <c r="Q87">
-        <v>-87.29979801220141</v>
+        <v>-124.88957862</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.306200868107172</v>
+        <v>0.4439291224682731</v>
       </c>
       <c r="T87">
-        <v>4.498341027292473</v>
+        <v>3.958225682065887</v>
       </c>
       <c r="U87">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V87">
-        <v>0.1117514879634647</v>
+        <v>0.09373872036817774</v>
       </c>
       <c r="W87">
-        <v>0.140748368702801</v>
+        <v>0.2164151935760792</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3604886708498862</v>
+        <v>0.3023829689296055</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8410,25 +8410,25 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1669998043168582</v>
+        <v>0.2525422829099083</v>
       </c>
       <c r="C88">
-        <v>-1099.654677399548</v>
+        <v>-879.0648415687897</v>
       </c>
       <c r="D88">
-        <v>649.9593226004522</v>
+        <v>492.3211584312104</v>
       </c>
       <c r="E88">
-        <v>1675.014</v>
+        <v>1296.786</v>
       </c>
       <c r="F88">
-        <v>1810.214</v>
+        <v>1431.986</v>
       </c>
       <c r="G88">
         <v>60.6</v>
       </c>
       <c r="H88">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -8443,37 +8443,37 @@
         <v>102.2</v>
       </c>
       <c r="M88">
-        <v>286.8393969147369</v>
+        <v>341.9582568</v>
       </c>
       <c r="N88">
-        <v>-184.6393969147369</v>
+        <v>-239.7582568</v>
       </c>
       <c r="O88">
-        <v>-57.23821304356846</v>
+        <v>-74.32505960800002</v>
       </c>
       <c r="P88">
-        <v>-127.4011838711685</v>
+        <v>-165.433197192</v>
       </c>
       <c r="Q88">
-        <v>-89.60118387116849</v>
+        <v>-127.633197192</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3269937872576842</v>
+        <v>0.4728669169302926</v>
       </c>
       <c r="T88">
-        <v>4.819651100670507</v>
+        <v>4.240956087927737</v>
       </c>
       <c r="U88">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V88">
-        <v>0.1104520520569128</v>
+        <v>0.09264873524761752</v>
       </c>
       <c r="W88">
-        <v>0.1409542722102121</v>
+        <v>0.216675482022869</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3562969421190736</v>
+        <v>0.2988668878955403</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8492,25 +8492,25 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1684333650202598</v>
+        <v>0.2545422829099083</v>
       </c>
       <c r="C89">
-        <v>-1126.780346646104</v>
+        <v>-900.2798162499774</v>
       </c>
       <c r="D89">
-        <v>643.8826533538964</v>
+        <v>487.7571837500228</v>
       </c>
       <c r="E89">
-        <v>1696.063</v>
+        <v>1313.437</v>
       </c>
       <c r="F89">
-        <v>1831.263</v>
+        <v>1448.637</v>
       </c>
       <c r="G89">
         <v>60.6</v>
       </c>
       <c r="H89">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -8525,37 +8525,37 @@
         <v>102.2</v>
       </c>
       <c r="M89">
-        <v>290.1747387393269</v>
+        <v>345.9345156000001</v>
       </c>
       <c r="N89">
-        <v>-187.9747387393269</v>
+        <v>-243.7345156000001</v>
       </c>
       <c r="O89">
-        <v>-58.27216900919135</v>
+        <v>-75.55769983600004</v>
       </c>
       <c r="P89">
-        <v>-129.7025697301356</v>
+        <v>-168.176815764</v>
       </c>
       <c r="Q89">
-        <v>-91.9025697301356</v>
+        <v>-130.376815764</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3509856170467369</v>
+        <v>0.5062566797710844</v>
       </c>
       <c r="T89">
-        <v>5.190393493029776</v>
+        <v>4.567183479306793</v>
       </c>
       <c r="U89">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V89">
-        <v>0.1091824882401667</v>
+        <v>0.09158380725626558</v>
       </c>
       <c r="W89">
-        <v>0.1411554423036598</v>
+        <v>0.2169297868272038</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3522015749682795</v>
+        <v>0.295431636310534</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8574,25 +8574,25 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1698669257236614</v>
+        <v>0.2565422829099083</v>
       </c>
       <c r="C90">
-        <v>-1153.79344307778</v>
+        <v>-921.4109491596873</v>
       </c>
       <c r="D90">
-        <v>637.9185569222198</v>
+        <v>483.2770508403129</v>
       </c>
       <c r="E90">
-        <v>1717.112</v>
+        <v>1330.088</v>
       </c>
       <c r="F90">
-        <v>1852.312</v>
+        <v>1465.288</v>
       </c>
       <c r="G90">
         <v>60.6</v>
       </c>
       <c r="H90">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -8607,37 +8607,37 @@
         <v>102.2</v>
       </c>
       <c r="M90">
-        <v>293.5100805639169</v>
+        <v>349.9107744000001</v>
       </c>
       <c r="N90">
-        <v>-191.3100805639169</v>
+        <v>-247.7107744000001</v>
       </c>
       <c r="O90">
-        <v>-59.30612497481425</v>
+        <v>-76.79034006400005</v>
       </c>
       <c r="P90">
-        <v>-132.0039555891027</v>
+        <v>-170.9204343360001</v>
       </c>
       <c r="Q90">
-        <v>-94.20395558910268</v>
+        <v>-133.1204343360001</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.378976085133965</v>
+        <v>0.5452114030853414</v>
       </c>
       <c r="T90">
-        <v>5.622926284115592</v>
+        <v>4.947782102582361</v>
       </c>
       <c r="U90">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V90">
-        <v>0.1079417781465284</v>
+        <v>0.09054308217380802</v>
       </c>
       <c r="W90">
-        <v>0.1413520403495291</v>
+        <v>0.2171783119768947</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.34819928434364</v>
+        <v>0.2920744586251871</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8656,25 +8656,25 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1713004864270629</v>
+        <v>0.2585422829099083</v>
       </c>
       <c r="C91">
-        <v>-1180.697066172065</v>
+        <v>-942.4605295734389</v>
       </c>
       <c r="D91">
-        <v>632.0639338279353</v>
+        <v>478.8784704265612</v>
       </c>
       <c r="E91">
-        <v>1738.161</v>
+        <v>1346.739</v>
       </c>
       <c r="F91">
-        <v>1873.361</v>
+        <v>1481.939</v>
       </c>
       <c r="G91">
         <v>60.6</v>
       </c>
       <c r="H91">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -8689,37 +8689,37 @@
         <v>102.2</v>
       </c>
       <c r="M91">
-        <v>296.8454223885068</v>
+        <v>353.8870332</v>
       </c>
       <c r="N91">
-        <v>-194.6454223885069</v>
+        <v>-251.6870332</v>
       </c>
       <c r="O91">
-        <v>-60.34008094043713</v>
+        <v>-78.02298029200003</v>
       </c>
       <c r="P91">
-        <v>-134.3053414480697</v>
+        <v>-173.664052908</v>
       </c>
       <c r="Q91">
-        <v>-96.50534144806973</v>
+        <v>-135.864052908</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.4120557292370527</v>
+        <v>0.591248803365827</v>
       </c>
       <c r="T91">
-        <v>6.134101400853373</v>
+        <v>5.397580475544393</v>
       </c>
       <c r="U91">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V91">
-        <v>0.1067289491785899</v>
+        <v>0.08952574417185515</v>
       </c>
       <c r="W91">
-        <v>0.1415442204617833</v>
+        <v>0.217421252291761</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3442869328341609</v>
+        <v>0.2887927231350165</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8738,25 +8738,25 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1727340471304645</v>
+        <v>0.2605422829099083</v>
       </c>
       <c r="C92">
-        <v>-1207.494202656965</v>
+        <v>-963.4307641744567</v>
       </c>
       <c r="D92">
-        <v>626.3157973430348</v>
+        <v>474.5592358255434</v>
       </c>
       <c r="E92">
-        <v>1759.21</v>
+        <v>1363.39</v>
       </c>
       <c r="F92">
-        <v>1894.41</v>
+        <v>1498.59</v>
       </c>
       <c r="G92">
         <v>60.6</v>
       </c>
       <c r="H92">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -8771,37 +8771,37 @@
         <v>102.2</v>
       </c>
       <c r="M92">
-        <v>300.1807642130968</v>
+        <v>357.8632920000001</v>
       </c>
       <c r="N92">
-        <v>-197.9807642130968</v>
+        <v>-255.6632920000001</v>
       </c>
       <c r="O92">
-        <v>-61.37403690606002</v>
+        <v>-79.25562052000004</v>
       </c>
       <c r="P92">
-        <v>-136.6067273070368</v>
+        <v>-176.40767148</v>
       </c>
       <c r="Q92">
-        <v>-98.80672730703684</v>
+        <v>-138.60767148</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4517513021607581</v>
+        <v>0.6464936837024098</v>
       </c>
       <c r="T92">
-        <v>6.747511540938712</v>
+        <v>5.937338523098832</v>
       </c>
       <c r="U92">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V92">
-        <v>0.1055430719654945</v>
+        <v>0.08853101368105673</v>
       </c>
       <c r="W92">
-        <v>0.1417321299048764</v>
+        <v>0.2176587939329637</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3404615224693369</v>
+        <v>0.2855839151001829</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8820,25 +8820,25 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.1741676078338661</v>
+        <v>0.2625422829099083</v>
       </c>
       <c r="C93">
-        <v>-1234.187731591658</v>
+        <v>-984.3237807450719</v>
       </c>
       <c r="D93">
-        <v>620.6712684083423</v>
+        <v>470.3172192549284</v>
       </c>
       <c r="E93">
-        <v>1780.259</v>
+        <v>1380.041</v>
       </c>
       <c r="F93">
-        <v>1915.459</v>
+        <v>1515.241</v>
       </c>
       <c r="G93">
         <v>60.6</v>
       </c>
       <c r="H93">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -8853,37 +8853,37 @@
         <v>102.2</v>
       </c>
       <c r="M93">
-        <v>303.5161060376868</v>
+        <v>361.8395508000001</v>
       </c>
       <c r="N93">
-        <v>-201.3161060376868</v>
+        <v>-259.6395508000001</v>
       </c>
       <c r="O93">
-        <v>-62.4079928716829</v>
+        <v>-80.48826074800004</v>
       </c>
       <c r="P93">
-        <v>-138.9081131660039</v>
+        <v>-179.1512900520001</v>
       </c>
       <c r="Q93">
-        <v>-101.1081131660039</v>
+        <v>-141.3512900520001</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.5002681135119534</v>
+        <v>0.7140152041137888</v>
       </c>
       <c r="T93">
-        <v>7.497235045487457</v>
+        <v>6.597042803443149</v>
       </c>
       <c r="U93">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V93">
-        <v>0.1043832579878517</v>
+        <v>0.08755814539884731</v>
       </c>
       <c r="W93">
-        <v>0.1419159094700992</v>
+        <v>0.2178911148787553</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.336720187057586</v>
+        <v>0.2824456303188622</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8902,25 +8902,25 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.1756011685372676</v>
+        <v>0.2645422829099083</v>
       </c>
       <c r="C94">
-        <v>-1260.780429174857</v>
+        <v>-1005.141631661899</v>
       </c>
       <c r="D94">
-        <v>615.1275708251436</v>
+        <v>466.150368338101</v>
       </c>
       <c r="E94">
-        <v>1801.308</v>
+        <v>1396.692</v>
       </c>
       <c r="F94">
-        <v>1936.508</v>
+        <v>1531.892</v>
       </c>
       <c r="G94">
         <v>60.6</v>
       </c>
       <c r="H94">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -8935,37 +8935,37 @@
         <v>102.2</v>
       </c>
       <c r="M94">
-        <v>306.8514478622768</v>
+        <v>365.8158096000001</v>
       </c>
       <c r="N94">
-        <v>-204.6514478622768</v>
+        <v>-263.6158096000001</v>
       </c>
       <c r="O94">
-        <v>-63.44194883730579</v>
+        <v>-81.72090097600004</v>
       </c>
       <c r="P94">
-        <v>-141.209499024971</v>
+        <v>-181.894908624</v>
       </c>
       <c r="Q94">
-        <v>-103.409499024971</v>
+        <v>-144.094908624</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5609141277009477</v>
+        <v>0.7984171046280124</v>
       </c>
       <c r="T94">
-        <v>8.434389426173391</v>
+        <v>7.421673153873543</v>
       </c>
       <c r="U94">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V94">
-        <v>0.1032486573575489</v>
+        <v>0.08660642642712071</v>
       </c>
       <c r="W94">
-        <v>0.1420956938273824</v>
+        <v>0.2181183853692036</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3330601850243513</v>
+        <v>0.2793755691197441</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -8984,25 +8984,25 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.1770347292406692</v>
+        <v>0.2665422829099083</v>
       </c>
       <c r="C95">
-        <v>-1287.27497329778</v>
+        <v>-1025.886297206848</v>
       </c>
       <c r="D95">
-        <v>609.6820267022198</v>
+        <v>462.0567027931524</v>
       </c>
       <c r="E95">
-        <v>1822.357</v>
+        <v>1413.343</v>
       </c>
       <c r="F95">
-        <v>1957.557</v>
+        <v>1548.543</v>
       </c>
       <c r="G95">
         <v>60.6</v>
       </c>
       <c r="H95">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -9017,37 +9017,37 @@
         <v>102.2</v>
       </c>
       <c r="M95">
-        <v>310.1867896868667</v>
+        <v>369.7920684000001</v>
       </c>
       <c r="N95">
-        <v>-207.9867896868668</v>
+        <v>-267.5920684000001</v>
       </c>
       <c r="O95">
-        <v>-64.4759048029287</v>
+        <v>-82.95354120400003</v>
       </c>
       <c r="P95">
-        <v>-143.510884883938</v>
+        <v>-184.638527196</v>
       </c>
       <c r="Q95">
-        <v>-105.710884883938</v>
+        <v>-146.838527196</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.638887574515369</v>
+        <v>0.9069338338605857</v>
       </c>
       <c r="T95">
-        <v>9.639302201341021</v>
+        <v>8.481912175855479</v>
       </c>
       <c r="U95">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V95">
-        <v>0.1021384567408011</v>
+        <v>0.08567517453005491</v>
       </c>
       <c r="W95">
-        <v>0.1422716118544015</v>
+        <v>0.2183407683222229</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3294788927122615</v>
+        <v>0.2763715307421125</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9066,25 +9066,25 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1784682899440708</v>
+        <v>0.2685422829099083</v>
       </c>
       <c r="C96">
-        <v>-1313.673947857407</v>
+        <v>-1046.559688705189</v>
       </c>
       <c r="D96">
-        <v>604.3320521425929</v>
+        <v>458.0343112948112</v>
       </c>
       <c r="E96">
-        <v>1843.406</v>
+        <v>1429.994</v>
       </c>
       <c r="F96">
-        <v>1978.606</v>
+        <v>1565.194</v>
       </c>
       <c r="G96">
         <v>60.6</v>
       </c>
       <c r="H96">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -9099,37 +9099,37 @@
         <v>102.2</v>
       </c>
       <c r="M96">
-        <v>313.5221315114567</v>
+        <v>373.7683272</v>
       </c>
       <c r="N96">
-        <v>-211.3221315114567</v>
+        <v>-271.5683272000001</v>
       </c>
       <c r="O96">
-        <v>-65.50986076855158</v>
+        <v>-84.18618143200003</v>
       </c>
       <c r="P96">
-        <v>-145.8122707429051</v>
+        <v>-187.382145768</v>
       </c>
       <c r="Q96">
-        <v>-108.0122707429051</v>
+        <v>-149.582145768</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.7428521702679306</v>
+        <v>1.051622806170684</v>
       </c>
       <c r="T96">
-        <v>11.24585256823119</v>
+        <v>9.895564205164728</v>
       </c>
       <c r="U96">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V96">
-        <v>0.1010518774137713</v>
+        <v>0.08476373650313943</v>
       </c>
       <c r="W96">
-        <v>0.1424437869446755</v>
+        <v>0.2185584197230503</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3259737981089396</v>
+        <v>0.2734314080746433</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9148,25 +9148,25 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1799018506474724</v>
+        <v>0.2705422829099083</v>
       </c>
       <c r="C97">
-        <v>-1339.979846844609</v>
+        <v>-1067.163651501131</v>
       </c>
       <c r="D97">
-        <v>599.0751531553914</v>
+        <v>454.0813484988689</v>
       </c>
       <c r="E97">
-        <v>1864.455</v>
+        <v>1446.645</v>
       </c>
       <c r="F97">
-        <v>1999.655</v>
+        <v>1581.845</v>
       </c>
       <c r="G97">
         <v>60.6</v>
       </c>
       <c r="H97">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -9181,37 +9181,37 @@
         <v>102.2</v>
       </c>
       <c r="M97">
-        <v>316.8574733360467</v>
+        <v>377.7445860000001</v>
       </c>
       <c r="N97">
-        <v>-214.6574733360467</v>
+        <v>-275.5445860000001</v>
       </c>
       <c r="O97">
-        <v>-66.54381673417447</v>
+        <v>-85.41882166000005</v>
       </c>
       <c r="P97">
-        <v>-148.1136566018722</v>
+        <v>-190.12576434</v>
       </c>
       <c r="Q97">
-        <v>-110.3136566018722</v>
+        <v>-152.32576434</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.8884026043215173</v>
+        <v>1.254187367404821</v>
       </c>
       <c r="T97">
-        <v>13.49502308187744</v>
+        <v>11.87467704619768</v>
       </c>
       <c r="U97">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V97">
-        <v>0.09998817344099474</v>
+        <v>0.08387148664521163</v>
       </c>
       <c r="W97">
-        <v>0.1426123372962069</v>
+        <v>0.2187714889891235</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3225424949709508</v>
+        <v>0.2705531827264891</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9230,25 +9230,25 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.1813354113508739</v>
+        <v>0.2725422829099083</v>
       </c>
       <c r="C98">
-        <v>-1366.195078220757</v>
+        <v>-1087.699967780633</v>
       </c>
       <c r="D98">
-        <v>593.9089217792427</v>
+        <v>450.1960322193674</v>
       </c>
       <c r="E98">
-        <v>1885.504</v>
+        <v>1463.296</v>
       </c>
       <c r="F98">
-        <v>2020.704</v>
+        <v>1598.496</v>
       </c>
       <c r="G98">
         <v>60.6</v>
       </c>
       <c r="H98">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -9263,37 +9263,37 @@
         <v>102.2</v>
       </c>
       <c r="M98">
-        <v>320.1928151606366</v>
+        <v>381.7208448000001</v>
       </c>
       <c r="N98">
-        <v>-217.9928151606366</v>
+        <v>-279.5208448000001</v>
       </c>
       <c r="O98">
-        <v>-67.57777269979735</v>
+        <v>-86.65146188800004</v>
       </c>
       <c r="P98">
-        <v>-150.4150424608393</v>
+        <v>-192.869382912</v>
       </c>
       <c r="Q98">
-        <v>-112.6150424608393</v>
+        <v>-155.069382912</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.106728255401894</v>
+        <v>1.558034209256023</v>
       </c>
       <c r="T98">
-        <v>16.86877885234676</v>
+        <v>14.84334630774707</v>
       </c>
       <c r="U98">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V98">
-        <v>0.09894662996765105</v>
+        <v>0.08299782532599069</v>
       </c>
       <c r="W98">
-        <v>0.1427773761820814</v>
+        <v>0.2189801193121534</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3191826773150034</v>
+        <v>0.2677349204064214</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9312,25 +9312,25 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.1827689720542755</v>
+        <v>0.2745422829099083</v>
       </c>
       <c r="C99">
-        <v>-1392.321967595463</v>
+        <v>-1108.170359250524</v>
       </c>
       <c r="D99">
-        <v>588.8310324045366</v>
+        <v>446.3766407494763</v>
       </c>
       <c r="E99">
-        <v>1906.553</v>
+        <v>1479.947</v>
       </c>
       <c r="F99">
-        <v>2041.753</v>
+        <v>1615.147</v>
       </c>
       <c r="G99">
         <v>60.6</v>
       </c>
       <c r="H99">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -9345,37 +9345,37 @@
         <v>102.2</v>
       </c>
       <c r="M99">
-        <v>323.5281569852265</v>
+        <v>385.6971036</v>
       </c>
       <c r="N99">
-        <v>-221.3281569852265</v>
+        <v>-283.4971036000001</v>
       </c>
       <c r="O99">
-        <v>-68.61172866542023</v>
+        <v>-87.88410211600004</v>
       </c>
       <c r="P99">
-        <v>-152.7164283198063</v>
+        <v>-195.613001484</v>
       </c>
       <c r="Q99">
-        <v>-114.9164283198063</v>
+        <v>-157.813001484</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.470604340535859</v>
+        <v>2.064445612341364</v>
       </c>
       <c r="T99">
-        <v>22.49170513646235</v>
+        <v>19.79112841032942</v>
       </c>
       <c r="U99">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V99">
-        <v>0.0979265616174691</v>
+        <v>0.08214217764221758</v>
       </c>
       <c r="W99">
-        <v>0.1429390122043296</v>
+        <v>0.2191844479790385</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3158921342499003</v>
+        <v>0.2649747665877986</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9394,25 +9394,25 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.1842025327576771</v>
+        <v>0.2765422829099083</v>
       </c>
       <c r="C100">
-        <v>-1418.362761717247</v>
+        <v>-1128.576489682401</v>
       </c>
       <c r="D100">
-        <v>583.8392382827528</v>
+        <v>442.6215103175991</v>
       </c>
       <c r="E100">
-        <v>1927.602</v>
+        <v>1496.598</v>
       </c>
       <c r="F100">
-        <v>2062.802</v>
+        <v>1631.798</v>
       </c>
       <c r="G100">
         <v>60.6</v>
       </c>
       <c r="H100">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -9427,37 +9427,37 @@
         <v>102.2</v>
       </c>
       <c r="M100">
-        <v>326.8634988098165</v>
+        <v>389.6733624</v>
       </c>
       <c r="N100">
-        <v>-224.6634988098165</v>
+        <v>-287.4733624</v>
       </c>
       <c r="O100">
-        <v>-69.64568463104312</v>
+        <v>-89.11674234400003</v>
       </c>
       <c r="P100">
-        <v>-155.0178141787734</v>
+        <v>-198.356620056</v>
       </c>
       <c r="Q100">
-        <v>-117.2178141787734</v>
+        <v>-160.556620056</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.198356510803788</v>
+        <v>3.077268418512046</v>
       </c>
       <c r="T100">
-        <v>33.73755770469351</v>
+        <v>29.68669261549413</v>
       </c>
       <c r="U100">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V100">
-        <v>0.0969273109887194</v>
+        <v>0.08130399215607252</v>
       </c>
       <c r="W100">
-        <v>0.1430973495322462</v>
+        <v>0.2193846066731299</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3126687451249013</v>
+        <v>0.2622709424389436</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9476,25 +9476,25 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.1856360934610786</v>
+        <v>0.2785422829099083</v>
       </c>
       <c r="C101">
-        <v>-1444.319631788149</v>
+        <v>-1148.919967329191</v>
       </c>
       <c r="D101">
-        <v>578.9313682118513</v>
+        <v>438.9290326708093</v>
       </c>
       <c r="E101">
-        <v>1948.651</v>
+        <v>1513.249</v>
       </c>
       <c r="F101">
-        <v>2083.851</v>
+        <v>1648.449</v>
       </c>
       <c r="G101">
         <v>60.6</v>
       </c>
       <c r="H101">
-        <v>1969.7</v>
+        <v>1529.9</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -9509,37 +9509,37 @@
         <v>102.2</v>
       </c>
       <c r="M101">
-        <v>330.1988406344065</v>
+        <v>393.6496212</v>
       </c>
       <c r="N101">
-        <v>-227.9988406344065</v>
+        <v>-291.4496212</v>
       </c>
       <c r="O101">
-        <v>-70.67964059666602</v>
+        <v>-90.34938257200002</v>
       </c>
       <c r="P101">
-        <v>-157.3192000377405</v>
+        <v>-201.100238628</v>
       </c>
       <c r="Q101">
-        <v>-119.5192000377405</v>
+        <v>-163.300238628</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>4.381613021607576</v>
+        <v>6.115736837024092</v>
       </c>
       <c r="T101">
-        <v>67.47511540938703</v>
+        <v>59.37338523098827</v>
       </c>
       <c r="U101">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V101">
-        <v>0.0959482472413586</v>
+        <v>0.0804827397100516</v>
       </c>
       <c r="W101">
-        <v>0.1432524881262655</v>
+        <v>0.2195807217572397</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3095104749721245</v>
+        <v>0.2596217410001663</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/morocco/morocco_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_oil_gas_distribution.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08923564184996284</v>
+        <v>0.08898068779604296</v>
       </c>
       <c r="C2">
-        <v>1382.784593735525</v>
+        <v>1376.537792272688</v>
       </c>
       <c r="D2">
-        <v>1320.584593735525</v>
+        <v>1328.381792272688</v>
       </c>
       <c r="E2">
-        <v>-129</v>
+        <v>-114.956</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>14.044</v>
       </c>
       <c r="G2">
         <v>62.2</v>
@@ -1451,28 +1451,28 @@
         <v>76.7</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.7064132</v>
       </c>
       <c r="N2">
-        <v>76.7</v>
+        <v>75.9935868</v>
       </c>
       <c r="O2">
-        <v>24.544</v>
+        <v>24.317947776</v>
       </c>
       <c r="P2">
-        <v>52.15600000000001</v>
+        <v>51.67563902400001</v>
       </c>
       <c r="Q2">
-        <v>90.456</v>
+        <v>89.975639024</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08923564184996284</v>
+        <v>0.08953398767277067</v>
       </c>
       <c r="T2">
-        <v>0.5661120226706918</v>
+        <v>0.5700004688870158</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>108.5766800507125</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08898068779604296</v>
+        <v>0.08872573374212307</v>
       </c>
       <c r="C3">
-        <v>1376.537792272688</v>
+        <v>1370.383612517297</v>
       </c>
       <c r="D3">
-        <v>1328.381792272688</v>
+        <v>1336.271612517297</v>
       </c>
       <c r="E3">
-        <v>-114.956</v>
+        <v>-100.912</v>
       </c>
       <c r="F3">
-        <v>14.044</v>
+        <v>28.088</v>
       </c>
       <c r="G3">
         <v>62.2</v>
@@ -1533,28 +1533,28 @@
         <v>76.7</v>
       </c>
       <c r="M3">
-        <v>0.7064132</v>
+        <v>1.4128264</v>
       </c>
       <c r="N3">
-        <v>75.9935868</v>
+        <v>75.2871736</v>
       </c>
       <c r="O3">
-        <v>24.317947776</v>
+        <v>24.091895552</v>
       </c>
       <c r="P3">
-        <v>51.67563902400001</v>
+        <v>51.19527804800001</v>
       </c>
       <c r="Q3">
-        <v>89.975639024</v>
+        <v>89.495278048</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08953398767277067</v>
+        <v>0.08983842218583987</v>
       </c>
       <c r="T3">
-        <v>0.5700004688870158</v>
+        <v>0.5739682711485707</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>108.5766800507125</v>
+        <v>54.28834002535627</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08872573374212307</v>
+        <v>0.0884707796882032</v>
       </c>
       <c r="C4">
-        <v>1370.383612517297</v>
+        <v>1364.323714688355</v>
       </c>
       <c r="D4">
-        <v>1336.271612517297</v>
+        <v>1344.255714688355</v>
       </c>
       <c r="E4">
-        <v>-100.912</v>
+        <v>-86.86799999999999</v>
       </c>
       <c r="F4">
-        <v>28.088</v>
+        <v>42.132</v>
       </c>
       <c r="G4">
         <v>62.2</v>
@@ -1615,28 +1615,28 @@
         <v>76.7</v>
       </c>
       <c r="M4">
-        <v>1.4128264</v>
+        <v>2.1192396</v>
       </c>
       <c r="N4">
-        <v>75.2871736</v>
+        <v>74.5807604</v>
       </c>
       <c r="O4">
-        <v>24.091895552</v>
+        <v>23.865843328</v>
       </c>
       <c r="P4">
-        <v>51.19527804800001</v>
+        <v>50.71491707200001</v>
       </c>
       <c r="Q4">
-        <v>89.495278048</v>
+        <v>89.014917072</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08983842218583987</v>
+        <v>0.09014913369917855</v>
       </c>
       <c r="T4">
-        <v>0.5739682711485707</v>
+        <v>0.5780178837660342</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>54.28834002535627</v>
+        <v>36.19222668357085</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0884707796882032</v>
+        <v>0.0882158256342833</v>
       </c>
       <c r="C5">
-        <v>1364.323714688355</v>
+        <v>1358.359798922005</v>
       </c>
       <c r="D5">
-        <v>1344.255714688355</v>
+        <v>1352.335798922005</v>
       </c>
       <c r="E5">
-        <v>-86.86799999999999</v>
+        <v>-72.824</v>
       </c>
       <c r="F5">
-        <v>42.132</v>
+        <v>56.176</v>
       </c>
       <c r="G5">
         <v>62.2</v>
@@ -1697,28 +1697,28 @@
         <v>76.7</v>
       </c>
       <c r="M5">
-        <v>2.1192396</v>
+        <v>2.8256528</v>
       </c>
       <c r="N5">
-        <v>74.5807604</v>
+        <v>73.8743472</v>
       </c>
       <c r="O5">
-        <v>23.865843328</v>
+        <v>23.639791104</v>
       </c>
       <c r="P5">
-        <v>50.71491707200001</v>
+        <v>50.23455609600001</v>
       </c>
       <c r="Q5">
-        <v>89.014917072</v>
+        <v>88.534556096</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09014913369917855</v>
+        <v>0.09046631836904512</v>
       </c>
       <c r="T5">
-        <v>0.5780178837660342</v>
+        <v>0.582151863313028</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>36.19222668357085</v>
+        <v>27.14417001267813</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0882158256342833</v>
+        <v>0.08796087158036342</v>
       </c>
       <c r="C6">
-        <v>1358.359798922005</v>
+        <v>1352.493606478448</v>
       </c>
       <c r="D6">
-        <v>1352.335798922005</v>
+        <v>1360.513606478448</v>
       </c>
       <c r="E6">
-        <v>-72.824</v>
+        <v>-58.77999999999999</v>
       </c>
       <c r="F6">
-        <v>56.176</v>
+        <v>70.22000000000001</v>
       </c>
       <c r="G6">
         <v>62.2</v>
@@ -1779,28 +1779,28 @@
         <v>76.7</v>
       </c>
       <c r="M6">
-        <v>2.8256528</v>
+        <v>3.532066</v>
       </c>
       <c r="N6">
-        <v>73.8743472</v>
+        <v>73.167934</v>
       </c>
       <c r="O6">
-        <v>23.639791104</v>
+        <v>23.41373888</v>
       </c>
       <c r="P6">
-        <v>50.23455609600001</v>
+        <v>49.75419512000001</v>
       </c>
       <c r="Q6">
-        <v>88.534556096</v>
+        <v>88.05419512</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09046631836904512</v>
+        <v>0.09079018061090888</v>
       </c>
       <c r="T6">
-        <v>0.582151863313028</v>
+        <v>0.5863728740083798</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>27.14417001267813</v>
+        <v>21.7153360101425</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08796087158036342</v>
+        <v>0.08770591752644355</v>
       </c>
       <c r="C7">
-        <v>1352.493606478448</v>
+        <v>1346.726920992942</v>
       </c>
       <c r="D7">
-        <v>1360.513606478448</v>
+        <v>1368.790920992942</v>
       </c>
       <c r="E7">
-        <v>-58.77999999999999</v>
+        <v>-44.73599999999999</v>
       </c>
       <c r="F7">
-        <v>70.22000000000001</v>
+        <v>84.26400000000001</v>
       </c>
       <c r="G7">
         <v>62.2</v>
@@ -1861,28 +1861,28 @@
         <v>76.7</v>
       </c>
       <c r="M7">
-        <v>3.532066</v>
+        <v>4.2384792</v>
       </c>
       <c r="N7">
-        <v>73.167934</v>
+        <v>72.4615208</v>
       </c>
       <c r="O7">
-        <v>23.41373888</v>
+        <v>23.187686656</v>
       </c>
       <c r="P7">
-        <v>49.75419512000001</v>
+        <v>49.27383414400001</v>
       </c>
       <c r="Q7">
-        <v>88.05419512</v>
+        <v>87.573834144</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09079018061090888</v>
+        <v>0.09112093353876974</v>
       </c>
       <c r="T7">
-        <v>0.5863728740083798</v>
+        <v>0.5906836934419304</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>21.7153360101425</v>
+        <v>18.09611334178542</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08770591752644355</v>
+        <v>0.08745096347252367</v>
       </c>
       <c r="C8">
-        <v>1346.726920992942</v>
+        <v>1341.061569772726</v>
       </c>
       <c r="D8">
-        <v>1368.790920992942</v>
+        <v>1377.169569772726</v>
       </c>
       <c r="E8">
-        <v>-44.736</v>
+        <v>-30.69200000000001</v>
       </c>
       <c r="F8">
-        <v>84.264</v>
+        <v>98.30799999999999</v>
       </c>
       <c r="G8">
         <v>62.2</v>
@@ -1943,28 +1943,28 @@
         <v>76.7</v>
       </c>
       <c r="M8">
-        <v>4.2384792</v>
+        <v>4.9448924</v>
       </c>
       <c r="N8">
-        <v>72.4615208</v>
+        <v>71.7551076</v>
       </c>
       <c r="O8">
-        <v>23.187686656</v>
+        <v>22.961634432</v>
       </c>
       <c r="P8">
-        <v>49.27383414400001</v>
+        <v>48.79347316800001</v>
       </c>
       <c r="Q8">
-        <v>87.573834144</v>
+        <v>87.093473168</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09112093353876974</v>
+        <v>0.09145879943282115</v>
       </c>
       <c r="T8">
-        <v>0.5906836934419304</v>
+        <v>0.5950872186697509</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.09611334178543</v>
+        <v>15.51095429295893</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08745096347252367</v>
+        <v>0.0871960094186038</v>
       </c>
       <c r="C9">
-        <v>1341.061569772726</v>
+        <v>1335.499425141878</v>
       </c>
       <c r="D9">
-        <v>1377.169569772726</v>
+        <v>1385.651425141878</v>
       </c>
       <c r="E9">
-        <v>-30.69199999999998</v>
+        <v>-16.648</v>
       </c>
       <c r="F9">
-        <v>98.30800000000002</v>
+        <v>112.352</v>
       </c>
       <c r="G9">
         <v>62.2</v>
@@ -2025,28 +2025,28 @@
         <v>76.7</v>
       </c>
       <c r="M9">
-        <v>4.944892400000001</v>
+        <v>5.6513056</v>
       </c>
       <c r="N9">
-        <v>71.7551076</v>
+        <v>71.0486944</v>
       </c>
       <c r="O9">
-        <v>22.961634432</v>
+        <v>22.735582208</v>
       </c>
       <c r="P9">
-        <v>48.79347316800001</v>
+        <v>48.31311219200001</v>
       </c>
       <c r="Q9">
-        <v>87.093473168</v>
+        <v>86.613112192</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09145879943282115</v>
+        <v>0.09180401023761281</v>
       </c>
       <c r="T9">
-        <v>0.5950872186697509</v>
+        <v>0.5995864727068718</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.51095429295893</v>
+        <v>13.57208500633907</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0871960094186038</v>
+        <v>0.08703285536468393</v>
       </c>
       <c r="C10">
-        <v>1335.499425141878</v>
+        <v>1326.938301487264</v>
       </c>
       <c r="D10">
-        <v>1385.651425141878</v>
+        <v>1391.134301487264</v>
       </c>
       <c r="E10">
-        <v>-16.648</v>
+        <v>-2.603999999999999</v>
       </c>
       <c r="F10">
-        <v>112.352</v>
+        <v>126.396</v>
       </c>
       <c r="G10">
         <v>62.2</v>
@@ -2107,45 +2107,45 @@
         <v>76.7</v>
       </c>
       <c r="M10">
-        <v>5.6513056</v>
+        <v>6.5473128</v>
       </c>
       <c r="N10">
-        <v>71.0486944</v>
+        <v>70.1526872</v>
       </c>
       <c r="O10">
-        <v>22.735582208</v>
+        <v>22.448859904</v>
       </c>
       <c r="P10">
-        <v>48.31311219200001</v>
+        <v>47.703827296</v>
       </c>
       <c r="Q10">
-        <v>86.613112192</v>
+        <v>86.003827296</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09180401023761281</v>
+        <v>0.09215680809305925</v>
       </c>
       <c r="T10">
-        <v>0.5995864727068718</v>
+        <v>0.6041846114481054</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.32</v>
       </c>
       <c r="W10">
-        <v>0.034204</v>
+        <v>0.035224</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>13.57208500633907</v>
+        <v>11.7147297437813</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08703285536468393</v>
+        <v>0.08678810131076403</v>
       </c>
       <c r="C11">
-        <v>1326.938301487264</v>
+        <v>1321.201242988519</v>
       </c>
       <c r="D11">
-        <v>1391.134301487264</v>
+        <v>1399.441242988519</v>
       </c>
       <c r="E11">
-        <v>-2.603999999999999</v>
+        <v>11.44</v>
       </c>
       <c r="F11">
-        <v>126.396</v>
+        <v>140.44</v>
       </c>
       <c r="G11">
         <v>62.2</v>
@@ -2189,28 +2189,28 @@
         <v>76.7</v>
       </c>
       <c r="M11">
-        <v>6.5473128</v>
+        <v>7.274792</v>
       </c>
       <c r="N11">
-        <v>70.1526872</v>
+        <v>69.425208</v>
       </c>
       <c r="O11">
-        <v>22.448859904</v>
+        <v>22.21606656</v>
       </c>
       <c r="P11">
-        <v>47.703827296</v>
+        <v>47.20914144</v>
       </c>
       <c r="Q11">
-        <v>86.003827296</v>
+        <v>85.50914143999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09215680809305925</v>
+        <v>0.09251744590084893</v>
       </c>
       <c r="T11">
-        <v>0.6041846114481054</v>
+        <v>0.6088849310502552</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.7147297437813</v>
+        <v>10.54325676940317</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08678810131076403</v>
+        <v>0.08667050725684415</v>
       </c>
       <c r="C12">
-        <v>1321.201242988519</v>
+        <v>1311.183764312355</v>
       </c>
       <c r="D12">
-        <v>1399.441242988519</v>
+        <v>1403.467764312355</v>
       </c>
       <c r="E12">
-        <v>11.44000000000003</v>
+        <v>25.48400000000001</v>
       </c>
       <c r="F12">
-        <v>140.44</v>
+        <v>154.484</v>
       </c>
       <c r="G12">
         <v>62.2</v>
@@ -2271,45 +2271,45 @@
         <v>76.7</v>
       </c>
       <c r="M12">
-        <v>7.274792000000001</v>
+        <v>8.264894</v>
       </c>
       <c r="N12">
-        <v>69.425208</v>
+        <v>68.435106</v>
       </c>
       <c r="O12">
-        <v>22.21606656</v>
+        <v>21.89923392</v>
       </c>
       <c r="P12">
-        <v>47.20914144</v>
+        <v>46.53587208</v>
       </c>
       <c r="Q12">
-        <v>85.50914143999999</v>
+        <v>84.83587208</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09251744590084893</v>
+        <v>0.09288618792903837</v>
       </c>
       <c r="T12">
-        <v>0.6088849310502552</v>
+        <v>0.6136908758120039</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.32</v>
       </c>
       <c r="W12">
-        <v>0.035224</v>
+        <v>0.03638</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.54325676940316</v>
+        <v>9.280215814020121</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08667050725684415</v>
+        <v>0.08643731320292426</v>
       </c>
       <c r="C13">
-        <v>1311.183764312355</v>
+        <v>1305.193454670071</v>
       </c>
       <c r="D13">
-        <v>1403.467764312355</v>
+        <v>1411.521454670071</v>
       </c>
       <c r="E13">
-        <v>25.48400000000001</v>
+        <v>39.52799999999999</v>
       </c>
       <c r="F13">
-        <v>154.484</v>
+        <v>168.528</v>
       </c>
       <c r="G13">
         <v>62.2</v>
@@ -2353,28 +2353,28 @@
         <v>76.7</v>
       </c>
       <c r="M13">
-        <v>8.264894</v>
+        <v>9.016247999999999</v>
       </c>
       <c r="N13">
-        <v>68.435106</v>
+        <v>67.683752</v>
       </c>
       <c r="O13">
-        <v>21.89923392</v>
+        <v>21.65880064</v>
       </c>
       <c r="P13">
-        <v>46.53587208</v>
+        <v>46.02495136</v>
       </c>
       <c r="Q13">
-        <v>84.83587208</v>
+        <v>84.32495136</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09288618792903837</v>
+        <v>0.09326331045786848</v>
       </c>
       <c r="T13">
-        <v>0.6136908758120039</v>
+        <v>0.6186060465910651</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.280215814020121</v>
+        <v>8.506864496185109</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08643731320292426</v>
+        <v>0.08620411914900437</v>
       </c>
       <c r="C14">
-        <v>1305.193454670071</v>
+        <v>1299.29610944543</v>
       </c>
       <c r="D14">
-        <v>1411.521454670071</v>
+        <v>1419.66810944543</v>
       </c>
       <c r="E14">
-        <v>39.52799999999999</v>
+        <v>53.57200000000003</v>
       </c>
       <c r="F14">
-        <v>168.528</v>
+        <v>182.572</v>
       </c>
       <c r="G14">
         <v>62.2</v>
@@ -2435,28 +2435,28 @@
         <v>76.7</v>
       </c>
       <c r="M14">
-        <v>9.016247999999999</v>
+        <v>9.767602000000002</v>
       </c>
       <c r="N14">
-        <v>67.683752</v>
+        <v>66.93239800000001</v>
       </c>
       <c r="O14">
-        <v>21.65880064</v>
+        <v>21.41836736</v>
       </c>
       <c r="P14">
-        <v>46.02495136</v>
+        <v>45.51403064</v>
       </c>
       <c r="Q14">
-        <v>84.32495136</v>
+        <v>83.81403064</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09326331045786848</v>
+        <v>0.09364910247011998</v>
       </c>
       <c r="T14">
-        <v>0.6186060465910651</v>
+        <v>0.6236342098018288</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.506864496185109</v>
+        <v>7.852490304170869</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08620411914900437</v>
+        <v>0.08604708509508449</v>
       </c>
       <c r="C15">
-        <v>1299.29610944543</v>
+        <v>1290.79129912638</v>
       </c>
       <c r="D15">
-        <v>1419.66810944543</v>
+        <v>1425.20729912638</v>
       </c>
       <c r="E15">
-        <v>53.57200000000003</v>
+        <v>67.61600000000004</v>
       </c>
       <c r="F15">
-        <v>182.572</v>
+        <v>196.616</v>
       </c>
       <c r="G15">
         <v>62.2</v>
@@ -2517,45 +2517,45 @@
         <v>76.7</v>
       </c>
       <c r="M15">
-        <v>9.767602000000002</v>
+        <v>10.6762488</v>
       </c>
       <c r="N15">
-        <v>66.93239800000001</v>
+        <v>66.02375119999999</v>
       </c>
       <c r="O15">
-        <v>21.41836736</v>
+        <v>21.127600384</v>
       </c>
       <c r="P15">
-        <v>45.51403064</v>
+        <v>44.896150816</v>
       </c>
       <c r="Q15">
-        <v>83.81403064</v>
+        <v>83.196150816</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09364910247011998</v>
+        <v>0.09404386638963314</v>
       </c>
       <c r="T15">
-        <v>0.6236342098018288</v>
+        <v>0.6287793070407498</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.32</v>
       </c>
       <c r="W15">
-        <v>0.03638</v>
+        <v>0.036924</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>7.852490304170869</v>
+        <v>7.184171279335488</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08604708509508449</v>
+        <v>0.08581933104116463</v>
       </c>
       <c r="C16">
-        <v>1290.79129912638</v>
+        <v>1284.858297776466</v>
       </c>
       <c r="D16">
-        <v>1425.20729912638</v>
+        <v>1433.318297776466</v>
       </c>
       <c r="E16">
-        <v>67.61600000000004</v>
+        <v>81.66000000000005</v>
       </c>
       <c r="F16">
-        <v>196.616</v>
+        <v>210.6600000000001</v>
       </c>
       <c r="G16">
         <v>62.2</v>
@@ -2599,28 +2599,28 @@
         <v>76.7</v>
       </c>
       <c r="M16">
-        <v>10.6762488</v>
+        <v>11.438838</v>
       </c>
       <c r="N16">
-        <v>66.02375119999999</v>
+        <v>65.261162</v>
       </c>
       <c r="O16">
-        <v>21.127600384</v>
+        <v>20.88357184</v>
       </c>
       <c r="P16">
-        <v>44.896150816</v>
+        <v>44.37759016</v>
       </c>
       <c r="Q16">
-        <v>83.196150816</v>
+        <v>82.67759015999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09404386638963314</v>
+        <v>0.09444791887195839</v>
       </c>
       <c r="T16">
-        <v>0.6287793070407498</v>
+        <v>0.6340454653911749</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.184171279335488</v>
+        <v>6.70522652737979</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08581933104116463</v>
+        <v>0.08559157698724473</v>
       </c>
       <c r="C17">
-        <v>1284.858297776466</v>
+        <v>1279.018145866749</v>
       </c>
       <c r="D17">
-        <v>1433.318297776466</v>
+        <v>1441.522145866749</v>
       </c>
       <c r="E17">
-        <v>81.66</v>
+        <v>95.70400000000001</v>
       </c>
       <c r="F17">
-        <v>210.66</v>
+        <v>224.704</v>
       </c>
       <c r="G17">
         <v>62.2</v>
@@ -2681,28 +2681,28 @@
         <v>76.7</v>
       </c>
       <c r="M17">
-        <v>11.438838</v>
+        <v>12.2014272</v>
       </c>
       <c r="N17">
-        <v>65.261162</v>
+        <v>64.49857280000001</v>
       </c>
       <c r="O17">
-        <v>20.88357184</v>
+        <v>20.639543296</v>
       </c>
       <c r="P17">
-        <v>44.37759016</v>
+        <v>43.85902950400001</v>
       </c>
       <c r="Q17">
-        <v>82.67759015999999</v>
+        <v>82.159029504</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09444791887195839</v>
+        <v>0.09486159165148184</v>
       </c>
       <c r="T17">
-        <v>0.6340454653911749</v>
+        <v>0.6394370084642291</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.705226527379791</v>
+        <v>6.286149869418554</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08559157698724473</v>
+        <v>0.08547942293332485</v>
       </c>
       <c r="C18">
-        <v>1279.018145866749</v>
+        <v>1269.048614206319</v>
       </c>
       <c r="D18">
-        <v>1441.522145866749</v>
+        <v>1445.596614206319</v>
       </c>
       <c r="E18">
-        <v>95.70400000000001</v>
+        <v>109.748</v>
       </c>
       <c r="F18">
-        <v>224.704</v>
+        <v>238.748</v>
       </c>
       <c r="G18">
         <v>62.2</v>
@@ -2763,45 +2763,45 @@
         <v>76.7</v>
       </c>
       <c r="M18">
-        <v>12.2014272</v>
+        <v>13.2027644</v>
       </c>
       <c r="N18">
-        <v>64.49857280000001</v>
+        <v>63.4972356</v>
       </c>
       <c r="O18">
-        <v>20.639543296</v>
+        <v>20.319115392</v>
       </c>
       <c r="P18">
-        <v>43.85902950400001</v>
+        <v>43.178120208</v>
       </c>
       <c r="Q18">
-        <v>82.159029504</v>
+        <v>81.47812020800001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09486159165148184</v>
+        <v>0.09528523244978898</v>
       </c>
       <c r="T18">
-        <v>0.6394370084642291</v>
+        <v>0.6449584682378388</v>
       </c>
       <c r="U18">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.32</v>
       </c>
       <c r="W18">
-        <v>0.036924</v>
+        <v>0.037604</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.286149869418554</v>
+        <v>5.809389433624976</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08547942293332485</v>
+        <v>0.08525846887940498</v>
       </c>
       <c r="C19">
-        <v>1269.048614206319</v>
+        <v>1263.099465357738</v>
       </c>
       <c r="D19">
-        <v>1445.596614206319</v>
+        <v>1453.691465357738</v>
       </c>
       <c r="E19">
-        <v>109.748</v>
+        <v>123.7920000000001</v>
       </c>
       <c r="F19">
-        <v>238.748</v>
+        <v>252.7920000000001</v>
       </c>
       <c r="G19">
         <v>62.2</v>
@@ -2845,28 +2845,28 @@
         <v>76.7</v>
       </c>
       <c r="M19">
-        <v>13.2027644</v>
+        <v>13.9793976</v>
       </c>
       <c r="N19">
-        <v>63.4972356</v>
+        <v>62.7206024</v>
       </c>
       <c r="O19">
-        <v>20.319115392</v>
+        <v>20.070592768</v>
       </c>
       <c r="P19">
-        <v>43.178120208</v>
+        <v>42.65000963199999</v>
       </c>
       <c r="Q19">
-        <v>81.47812020800001</v>
+        <v>80.95000963199999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09528523244978898</v>
+        <v>0.09571920595049388</v>
       </c>
       <c r="T19">
-        <v>0.6449584682378388</v>
+        <v>0.6506145977620243</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.809389433624976</v>
+        <v>5.486645576201365</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.085258468879405</v>
+        <v>0.08503751482548511</v>
       </c>
       <c r="C20">
-        <v>1263.099465357738</v>
+        <v>1257.24148386192</v>
       </c>
       <c r="D20">
-        <v>1453.691465357738</v>
+        <v>1461.87748386192</v>
       </c>
       <c r="E20">
-        <v>123.792</v>
+        <v>137.836</v>
       </c>
       <c r="F20">
-        <v>252.792</v>
+        <v>266.836</v>
       </c>
       <c r="G20">
         <v>62.2</v>
@@ -2927,28 +2927,28 @@
         <v>76.7</v>
       </c>
       <c r="M20">
-        <v>13.9793976</v>
+        <v>14.7560308</v>
       </c>
       <c r="N20">
-        <v>62.7206024</v>
+        <v>61.9439692</v>
       </c>
       <c r="O20">
-        <v>20.070592768</v>
+        <v>19.822070144</v>
       </c>
       <c r="P20">
-        <v>42.65000963200001</v>
+        <v>42.121899056</v>
       </c>
       <c r="Q20">
-        <v>80.950009632</v>
+        <v>80.421899056</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09571920595049388</v>
+        <v>0.09616389484627791</v>
       </c>
       <c r="T20">
-        <v>0.6506145977620243</v>
+        <v>0.6564103848053257</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.486645576201367</v>
+        <v>5.197874756401294</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08503751482548511</v>
+        <v>0.08481656077156521</v>
       </c>
       <c r="C21">
-        <v>1257.24148386192</v>
+        <v>1251.476218583944</v>
       </c>
       <c r="D21">
-        <v>1461.87748386192</v>
+        <v>1470.156218583944</v>
       </c>
       <c r="E21">
-        <v>137.836</v>
+        <v>151.8800000000001</v>
       </c>
       <c r="F21">
-        <v>266.836</v>
+        <v>280.8800000000001</v>
       </c>
       <c r="G21">
         <v>62.2</v>
@@ -3009,28 +3009,28 @@
         <v>76.7</v>
       </c>
       <c r="M21">
-        <v>14.7560308</v>
+        <v>15.532664</v>
       </c>
       <c r="N21">
-        <v>61.9439692</v>
+        <v>61.167336</v>
       </c>
       <c r="O21">
-        <v>19.822070144</v>
+        <v>19.57354752</v>
       </c>
       <c r="P21">
-        <v>42.121899056</v>
+        <v>41.59378848</v>
       </c>
       <c r="Q21">
-        <v>80.421899056</v>
+        <v>79.89378848</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09616389484627791</v>
+        <v>0.09661970096445652</v>
       </c>
       <c r="T21">
-        <v>0.6564103848053257</v>
+        <v>0.6623510665247094</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.197874756401294</v>
+        <v>4.937981018581229</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08481656077156521</v>
+        <v>0.08459560671764534</v>
       </c>
       <c r="C22">
-        <v>1251.476218583944</v>
+        <v>1245.805253674123</v>
       </c>
       <c r="D22">
-        <v>1470.156218583944</v>
+        <v>1478.529253674123</v>
       </c>
       <c r="E22">
-        <v>151.8800000000001</v>
+        <v>165.924</v>
       </c>
       <c r="F22">
-        <v>280.8800000000001</v>
+        <v>294.924</v>
       </c>
       <c r="G22">
         <v>62.2</v>
@@ -3091,28 +3091,28 @@
         <v>76.7</v>
       </c>
       <c r="M22">
-        <v>15.532664</v>
+        <v>16.3092972</v>
       </c>
       <c r="N22">
-        <v>61.167336</v>
+        <v>60.3907028</v>
       </c>
       <c r="O22">
-        <v>19.57354752</v>
+        <v>19.325024896</v>
       </c>
       <c r="P22">
-        <v>41.59378848</v>
+        <v>41.065677904</v>
       </c>
       <c r="Q22">
-        <v>79.89378848</v>
+        <v>79.36567790399999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09661970096445652</v>
+        <v>0.09708704647803207</v>
       </c>
       <c r="T22">
-        <v>0.6623510665247094</v>
+        <v>0.6684421452496473</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.937981018581229</v>
+        <v>4.702839065315456</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08459560671764534</v>
+        <v>0.08474865266372546</v>
       </c>
       <c r="C23">
-        <v>1245.805253674123</v>
+        <v>1225.951478676529</v>
       </c>
       <c r="D23">
-        <v>1478.529253674123</v>
+        <v>1472.719478676529</v>
       </c>
       <c r="E23">
-        <v>165.924</v>
+        <v>179.968</v>
       </c>
       <c r="F23">
-        <v>294.924</v>
+        <v>308.968</v>
       </c>
       <c r="G23">
         <v>62.2</v>
@@ -3173,45 +3173,45 @@
         <v>76.7</v>
       </c>
       <c r="M23">
-        <v>16.3092972</v>
+        <v>17.8583504</v>
       </c>
       <c r="N23">
-        <v>60.3907028</v>
+        <v>58.8416496</v>
       </c>
       <c r="O23">
-        <v>19.325024896</v>
+        <v>18.829327872</v>
       </c>
       <c r="P23">
-        <v>41.065677904</v>
+        <v>40.012321728</v>
       </c>
       <c r="Q23">
-        <v>79.36567790399999</v>
+        <v>78.312321728</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09708704647803207</v>
+        <v>0.09756637520990444</v>
       </c>
       <c r="T23">
-        <v>0.6684421452496473</v>
+        <v>0.6746894054803527</v>
       </c>
       <c r="U23">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V23">
         <v>0.32</v>
       </c>
       <c r="W23">
-        <v>0.037604</v>
+        <v>0.039304</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.702839065315456</v>
+        <v>4.294909567907235</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08474865266372546</v>
+        <v>0.08454469860980557</v>
       </c>
       <c r="C24">
-        <v>1225.951478676529</v>
+        <v>1219.65994853022</v>
       </c>
       <c r="D24">
-        <v>1472.719478676529</v>
+        <v>1480.47194853022</v>
       </c>
       <c r="E24">
-        <v>179.968</v>
+        <v>194.0120000000001</v>
       </c>
       <c r="F24">
-        <v>308.968</v>
+        <v>323.0120000000001</v>
       </c>
       <c r="G24">
         <v>62.2</v>
@@ -3255,28 +3255,28 @@
         <v>76.7</v>
       </c>
       <c r="M24">
-        <v>17.8583504</v>
+        <v>18.6700936</v>
       </c>
       <c r="N24">
-        <v>58.8416496</v>
+        <v>58.0299064</v>
       </c>
       <c r="O24">
-        <v>18.829327872</v>
+        <v>18.569570048</v>
       </c>
       <c r="P24">
-        <v>40.012321728</v>
+        <v>39.460336352</v>
       </c>
       <c r="Q24">
-        <v>78.312321728</v>
+        <v>77.760336352</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09756637520990444</v>
+        <v>0.09805815403870853</v>
       </c>
       <c r="T24">
-        <v>0.6746894054803527</v>
+        <v>0.681098932210557</v>
       </c>
       <c r="U24">
         <v>0.0578</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.294909567907235</v>
+        <v>4.108174369302573</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08454469860980557</v>
+        <v>0.0849119445558857</v>
       </c>
       <c r="C25">
-        <v>1219.65994853022</v>
+        <v>1191.714892789915</v>
       </c>
       <c r="D25">
-        <v>1480.47194853022</v>
+        <v>1466.570892789915</v>
       </c>
       <c r="E25">
-        <v>194.0120000000001</v>
+        <v>208.056</v>
       </c>
       <c r="F25">
-        <v>323.0120000000001</v>
+        <v>337.056</v>
       </c>
       <c r="G25">
         <v>62.2</v>
@@ -3337,45 +3337,45 @@
         <v>76.7</v>
       </c>
       <c r="M25">
-        <v>18.6700936</v>
+        <v>20.6615328</v>
       </c>
       <c r="N25">
-        <v>58.0299064</v>
+        <v>56.0384672</v>
       </c>
       <c r="O25">
-        <v>18.569570048</v>
+        <v>17.932309504</v>
       </c>
       <c r="P25">
-        <v>39.460336352</v>
+        <v>38.106157696</v>
       </c>
       <c r="Q25">
-        <v>77.760336352</v>
+        <v>76.40615769599999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09805815403870853</v>
+        <v>0.09856287441563907</v>
       </c>
       <c r="T25">
-        <v>0.681098932210557</v>
+        <v>0.6876771306968193</v>
       </c>
       <c r="U25">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V25">
         <v>0.32</v>
       </c>
       <c r="W25">
-        <v>0.039304</v>
+        <v>0.041684</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.108174369302573</v>
+        <v>3.712212484061201</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0849119445558857</v>
+        <v>0.0847317905019658</v>
       </c>
       <c r="C26">
-        <v>1191.714892789915</v>
+        <v>1184.45734386988</v>
       </c>
       <c r="D26">
-        <v>1466.570892789915</v>
+        <v>1473.35734386988</v>
       </c>
       <c r="E26">
-        <v>208.056</v>
+        <v>222.1</v>
       </c>
       <c r="F26">
-        <v>337.056</v>
+        <v>351.1</v>
       </c>
       <c r="G26">
         <v>62.2</v>
@@ -3419,28 +3419,28 @@
         <v>76.7</v>
       </c>
       <c r="M26">
-        <v>20.6615328</v>
+        <v>21.52243</v>
       </c>
       <c r="N26">
-        <v>56.0384672</v>
+        <v>55.17757</v>
       </c>
       <c r="O26">
-        <v>17.932309504</v>
+        <v>17.6568224</v>
       </c>
       <c r="P26">
-        <v>38.106157696</v>
+        <v>37.5207476</v>
       </c>
       <c r="Q26">
-        <v>76.40615769599999</v>
+        <v>75.8207476</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09856287441563907</v>
+        <v>0.09908105400262107</v>
       </c>
       <c r="T26">
-        <v>0.6876771306968193</v>
+        <v>0.694430747809382</v>
       </c>
       <c r="U26">
         <v>0.0613</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.712212484061202</v>
+        <v>3.563723984698754</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0847317905019658</v>
+        <v>0.08504667644804594</v>
       </c>
       <c r="C27">
-        <v>1184.45734386988</v>
+        <v>1158.592227711096</v>
       </c>
       <c r="D27">
-        <v>1473.35734386988</v>
+        <v>1461.536227711096</v>
       </c>
       <c r="E27">
-        <v>222.1</v>
+        <v>236.1440000000001</v>
       </c>
       <c r="F27">
-        <v>351.1</v>
+        <v>365.1440000000001</v>
       </c>
       <c r="G27">
         <v>62.2</v>
@@ -3501,45 +3501,45 @@
         <v>76.7</v>
       </c>
       <c r="M27">
-        <v>21.52243</v>
+        <v>23.40573040000001</v>
       </c>
       <c r="N27">
-        <v>55.17757</v>
+        <v>53.29426959999999</v>
       </c>
       <c r="O27">
-        <v>17.6568224</v>
+        <v>17.054166272</v>
       </c>
       <c r="P27">
-        <v>37.5207476</v>
+        <v>36.240103328</v>
       </c>
       <c r="Q27">
-        <v>75.8207476</v>
+        <v>74.54010332799999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09908105400262107</v>
+        <v>0.09961323844330532</v>
       </c>
       <c r="T27">
-        <v>0.694430747809382</v>
+        <v>0.701366895114176</v>
       </c>
       <c r="U27">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V27">
         <v>0.32</v>
       </c>
       <c r="W27">
-        <v>0.041684</v>
+        <v>0.043588</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.563723984698754</v>
+        <v>3.276975282941821</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08504667644804594</v>
+        <v>0.08488556239412605</v>
       </c>
       <c r="C28">
-        <v>1158.592227711096</v>
+        <v>1150.572805897354</v>
       </c>
       <c r="D28">
-        <v>1461.536227711096</v>
+        <v>1467.560805897354</v>
       </c>
       <c r="E28">
-        <v>236.1440000000001</v>
+        <v>250.188</v>
       </c>
       <c r="F28">
-        <v>365.1440000000001</v>
+        <v>379.188</v>
       </c>
       <c r="G28">
         <v>62.2</v>
@@ -3583,28 +3583,28 @@
         <v>76.7</v>
       </c>
       <c r="M28">
-        <v>23.40573040000001</v>
+        <v>24.30595080000001</v>
       </c>
       <c r="N28">
-        <v>53.29426959999999</v>
+        <v>52.3940492</v>
       </c>
       <c r="O28">
-        <v>17.054166272</v>
+        <v>16.766095744</v>
       </c>
       <c r="P28">
-        <v>36.240103328</v>
+        <v>35.627953456</v>
       </c>
       <c r="Q28">
-        <v>74.54010332799999</v>
+        <v>73.927953456</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09961323844330532</v>
+        <v>0.1001600032796247</v>
       </c>
       <c r="T28">
-        <v>0.701366895114176</v>
+        <v>0.7084930738519781</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.276975282941821</v>
+        <v>3.15560582801805</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08488556239412605</v>
+        <v>0.08472444834020616</v>
       </c>
       <c r="C29">
-        <v>1150.572805897354</v>
+        <v>1142.603257325554</v>
       </c>
       <c r="D29">
-        <v>1467.560805897354</v>
+        <v>1473.635257325554</v>
       </c>
       <c r="E29">
-        <v>250.188</v>
+        <v>264.2320000000001</v>
       </c>
       <c r="F29">
-        <v>379.188</v>
+        <v>393.2320000000001</v>
       </c>
       <c r="G29">
         <v>62.2</v>
@@ -3665,28 +3665,28 @@
         <v>76.7</v>
       </c>
       <c r="M29">
-        <v>24.30595080000001</v>
+        <v>25.20617120000001</v>
       </c>
       <c r="N29">
-        <v>52.3940492</v>
+        <v>51.4938288</v>
       </c>
       <c r="O29">
-        <v>16.766095744</v>
+        <v>16.478025216</v>
       </c>
       <c r="P29">
-        <v>35.627953456</v>
+        <v>35.015803584</v>
       </c>
       <c r="Q29">
-        <v>73.927953456</v>
+        <v>73.31580358399999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1001600032796247</v>
+        <v>0.1007219560280641</v>
       </c>
       <c r="T29">
-        <v>0.7084930738519781</v>
+        <v>0.7158172019991637</v>
       </c>
       <c r="U29">
         <v>0.0641</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.15560582801805</v>
+        <v>3.042905619874548</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08472444834020616</v>
+        <v>0.08610149428628627</v>
       </c>
       <c r="C30">
-        <v>1142.603257325554</v>
+        <v>1078.207192395014</v>
       </c>
       <c r="D30">
-        <v>1473.635257325554</v>
+        <v>1423.283192395014</v>
       </c>
       <c r="E30">
-        <v>264.2320000000001</v>
+        <v>278.2760000000001</v>
       </c>
       <c r="F30">
-        <v>393.2320000000001</v>
+        <v>407.2760000000001</v>
       </c>
       <c r="G30">
         <v>62.2</v>
@@ -3747,45 +3747,45 @@
         <v>76.7</v>
       </c>
       <c r="M30">
-        <v>25.20617120000001</v>
+        <v>29.28314440000001</v>
       </c>
       <c r="N30">
-        <v>51.4938288</v>
+        <v>47.41685559999999</v>
       </c>
       <c r="O30">
-        <v>16.478025216</v>
+        <v>15.173393792</v>
       </c>
       <c r="P30">
-        <v>35.015803584</v>
+        <v>32.24346180799999</v>
       </c>
       <c r="Q30">
-        <v>73.31580358399999</v>
+        <v>70.54346180799999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1007219560280641</v>
+        <v>0.1012997384313891</v>
       </c>
       <c r="T30">
-        <v>0.7158172019991637</v>
+        <v>0.7233476436152839</v>
       </c>
       <c r="U30">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V30">
         <v>0.32</v>
       </c>
       <c r="W30">
-        <v>0.043588</v>
+        <v>0.048892</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.042905619874548</v>
+        <v>2.619254235552654</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08610149428628627</v>
+        <v>0.0859934202323664</v>
       </c>
       <c r="C31">
-        <v>1078.207192395014</v>
+        <v>1067.990186554478</v>
       </c>
       <c r="D31">
-        <v>1423.283192395014</v>
+        <v>1427.110186554478</v>
       </c>
       <c r="E31">
-        <v>278.276</v>
+        <v>292.32</v>
       </c>
       <c r="F31">
-        <v>407.276</v>
+        <v>421.32</v>
       </c>
       <c r="G31">
         <v>62.2</v>
@@ -3829,28 +3829,28 @@
         <v>76.7</v>
       </c>
       <c r="M31">
-        <v>29.2831444</v>
+        <v>30.292908</v>
       </c>
       <c r="N31">
-        <v>47.4168556</v>
+        <v>46.40709200000001</v>
       </c>
       <c r="O31">
-        <v>15.173393792</v>
+        <v>14.85026944</v>
       </c>
       <c r="P31">
-        <v>32.243461808</v>
+        <v>31.55682256</v>
       </c>
       <c r="Q31">
-        <v>70.54346180799999</v>
+        <v>69.85682256</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1012997384313891</v>
+        <v>0.1018940289033806</v>
       </c>
       <c r="T31">
-        <v>0.7233476436152839</v>
+        <v>0.7310932407061506</v>
       </c>
       <c r="U31">
         <v>0.07190000000000001</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.619254235552654</v>
+        <v>2.531945761034233</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0859934202323664</v>
+        <v>0.08670746617844652</v>
       </c>
       <c r="C32">
-        <v>1067.990186554478</v>
+        <v>1029.035764606717</v>
       </c>
       <c r="D32">
-        <v>1427.110186554478</v>
+        <v>1402.199764606717</v>
       </c>
       <c r="E32">
-        <v>292.32</v>
+        <v>306.364</v>
       </c>
       <c r="F32">
-        <v>421.32</v>
+        <v>435.364</v>
       </c>
       <c r="G32">
         <v>62.2</v>
@@ -3911,45 +3911,45 @@
         <v>76.7</v>
       </c>
       <c r="M32">
-        <v>30.292908</v>
+        <v>33.0005912</v>
       </c>
       <c r="N32">
-        <v>46.40709200000001</v>
+        <v>43.6994088</v>
       </c>
       <c r="O32">
-        <v>14.85026944</v>
+        <v>13.983810816</v>
       </c>
       <c r="P32">
-        <v>31.55682256</v>
+        <v>29.715597984</v>
       </c>
       <c r="Q32">
-        <v>69.85682256</v>
+        <v>68.015597984</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1018940289033806</v>
+        <v>0.1025055451861544</v>
       </c>
       <c r="T32">
-        <v>0.7310932407061506</v>
+        <v>0.7390633478576221</v>
       </c>
       <c r="U32">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V32">
         <v>0.32</v>
       </c>
       <c r="W32">
-        <v>0.048892</v>
+        <v>0.051544</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.531945761034233</v>
+        <v>2.324200785833194</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08670746617844652</v>
+        <v>0.08662591212452664</v>
       </c>
       <c r="C33">
-        <v>1029.035764606717</v>
+        <v>1017.792806133</v>
       </c>
       <c r="D33">
-        <v>1402.199764606717</v>
+        <v>1405.000806133</v>
       </c>
       <c r="E33">
-        <v>306.364</v>
+        <v>320.408</v>
       </c>
       <c r="F33">
-        <v>435.364</v>
+        <v>449.408</v>
       </c>
       <c r="G33">
         <v>62.2</v>
@@ -3993,28 +3993,28 @@
         <v>76.7</v>
       </c>
       <c r="M33">
-        <v>33.0005912</v>
+        <v>34.0651264</v>
       </c>
       <c r="N33">
-        <v>43.6994088</v>
+        <v>42.6348736</v>
       </c>
       <c r="O33">
-        <v>13.983810816</v>
+        <v>13.643159552</v>
       </c>
       <c r="P33">
-        <v>29.715597984</v>
+        <v>28.991714048</v>
       </c>
       <c r="Q33">
-        <v>68.015597984</v>
+        <v>67.29171404799999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1025055451861544</v>
+        <v>0.103135047241951</v>
       </c>
       <c r="T33">
-        <v>0.7390633478576221</v>
+        <v>0.7472678699253132</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.324200785833194</v>
+        <v>2.251569511275907</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08662591212452664</v>
+        <v>0.08654435807060676</v>
       </c>
       <c r="C34">
-        <v>1017.792806133</v>
+        <v>1006.561060808906</v>
       </c>
       <c r="D34">
-        <v>1405.000806133</v>
+        <v>1407.813060808906</v>
       </c>
       <c r="E34">
-        <v>320.408</v>
+        <v>334.4520000000001</v>
       </c>
       <c r="F34">
-        <v>449.408</v>
+        <v>463.4520000000001</v>
       </c>
       <c r="G34">
         <v>62.2</v>
@@ -4075,28 +4075,28 @@
         <v>76.7</v>
       </c>
       <c r="M34">
-        <v>34.0651264</v>
+        <v>35.12966160000001</v>
       </c>
       <c r="N34">
-        <v>42.6348736</v>
+        <v>41.5703384</v>
       </c>
       <c r="O34">
-        <v>13.643159552</v>
+        <v>13.302508288</v>
       </c>
       <c r="P34">
-        <v>28.991714048</v>
+        <v>28.267830112</v>
       </c>
       <c r="Q34">
-        <v>67.29171404799999</v>
+        <v>66.567830112</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.103135047241951</v>
+        <v>0.1037833404038907</v>
       </c>
       <c r="T34">
-        <v>0.7472678699253132</v>
+        <v>0.7557173030995027</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.251569511275907</v>
+        <v>2.183340132146334</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08654435807060676</v>
+        <v>0.08646280401668688</v>
       </c>
       <c r="C35">
-        <v>1006.561060808906</v>
+        <v>995.3405961023207</v>
       </c>
       <c r="D35">
-        <v>1407.813060808906</v>
+        <v>1410.636596102321</v>
       </c>
       <c r="E35">
-        <v>334.4520000000001</v>
+        <v>348.496</v>
       </c>
       <c r="F35">
-        <v>463.4520000000001</v>
+        <v>477.496</v>
       </c>
       <c r="G35">
         <v>62.2</v>
@@ -4157,28 +4157,28 @@
         <v>76.7</v>
       </c>
       <c r="M35">
-        <v>35.12966160000001</v>
+        <v>36.19419680000001</v>
       </c>
       <c r="N35">
-        <v>41.5703384</v>
+        <v>40.5058032</v>
       </c>
       <c r="O35">
-        <v>13.302508288</v>
+        <v>12.961857024</v>
       </c>
       <c r="P35">
-        <v>28.267830112</v>
+        <v>27.543946176</v>
       </c>
       <c r="Q35">
-        <v>66.567830112</v>
+        <v>65.843946176</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1037833404038907</v>
+        <v>0.1044512788131619</v>
       </c>
       <c r="T35">
-        <v>0.7557173030995027</v>
+        <v>0.764422779703213</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.183340132146334</v>
+        <v>2.119124245906736</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08646280401668688</v>
+        <v>0.08638124996276698</v>
       </c>
       <c r="C36">
-        <v>995.3405961023207</v>
+        <v>984.1314800234778</v>
       </c>
       <c r="D36">
-        <v>1410.636596102321</v>
+        <v>1413.471480023478</v>
       </c>
       <c r="E36">
-        <v>348.496</v>
+        <v>362.5400000000001</v>
       </c>
       <c r="F36">
-        <v>477.496</v>
+        <v>491.5400000000001</v>
       </c>
       <c r="G36">
         <v>62.2</v>
@@ -4239,28 +4239,28 @@
         <v>76.7</v>
       </c>
       <c r="M36">
-        <v>36.19419680000001</v>
+        <v>37.25873200000001</v>
       </c>
       <c r="N36">
-        <v>40.5058032</v>
+        <v>39.44126799999999</v>
       </c>
       <c r="O36">
-        <v>12.961857024</v>
+        <v>12.62120576</v>
       </c>
       <c r="P36">
-        <v>27.543946176</v>
+        <v>26.82006224</v>
       </c>
       <c r="Q36">
-        <v>65.843946176</v>
+        <v>65.12006224</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1044512788131619</v>
+        <v>0.1051397691734877</v>
       </c>
       <c r="T36">
-        <v>0.764422779703213</v>
+        <v>0.773396117125499</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.119124245906736</v>
+        <v>2.058577838880829</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08638124996276698</v>
+        <v>0.08629969590884712</v>
       </c>
       <c r="C37">
-        <v>984.1314800234778</v>
+        <v>972.9337811304163</v>
       </c>
       <c r="D37">
-        <v>1413.471480023478</v>
+        <v>1416.317781130416</v>
       </c>
       <c r="E37">
-        <v>362.5400000000001</v>
+        <v>376.5840000000001</v>
       </c>
       <c r="F37">
-        <v>491.5400000000001</v>
+        <v>505.5840000000001</v>
       </c>
       <c r="G37">
         <v>62.2</v>
@@ -4321,28 +4321,28 @@
         <v>76.7</v>
       </c>
       <c r="M37">
-        <v>37.25873200000001</v>
+        <v>38.32326720000001</v>
       </c>
       <c r="N37">
-        <v>39.44126799999999</v>
+        <v>38.37673279999999</v>
       </c>
       <c r="O37">
-        <v>12.62120576</v>
+        <v>12.280554496</v>
       </c>
       <c r="P37">
-        <v>26.82006224</v>
+        <v>26.096178304</v>
       </c>
       <c r="Q37">
-        <v>65.12006224</v>
+        <v>64.39617830399999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1051397691734877</v>
+        <v>0.1058497748575736</v>
       </c>
       <c r="T37">
-        <v>0.773396117125499</v>
+        <v>0.7826498713422315</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.058577838880829</v>
+        <v>2.001395121134139</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08629969590884713</v>
+        <v>0.08979086185492724</v>
       </c>
       <c r="C38">
-        <v>972.9337811304158</v>
+        <v>846.4891552318708</v>
       </c>
       <c r="D38">
-        <v>1416.317781130416</v>
+        <v>1303.917155231871</v>
       </c>
       <c r="E38">
-        <v>376.584</v>
+        <v>390.628</v>
       </c>
       <c r="F38">
-        <v>505.584</v>
+        <v>519.628</v>
       </c>
       <c r="G38">
         <v>62.2</v>
@@ -4403,45 +4403,45 @@
         <v>76.7</v>
       </c>
       <c r="M38">
-        <v>38.3232672</v>
+        <v>46.76652</v>
       </c>
       <c r="N38">
-        <v>38.3767328</v>
+        <v>29.93348</v>
       </c>
       <c r="O38">
-        <v>12.280554496</v>
+        <v>9.5787136</v>
       </c>
       <c r="P38">
-        <v>26.096178304</v>
+        <v>20.3547664</v>
       </c>
       <c r="Q38">
-        <v>64.39617830399999</v>
+        <v>58.6547664</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1058497748575736</v>
+        <v>0.1065823204046464</v>
       </c>
       <c r="T38">
-        <v>0.7826498713422314</v>
+        <v>0.7921973955340983</v>
       </c>
       <c r="U38">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V38">
         <v>0.32</v>
       </c>
       <c r="W38">
-        <v>0.051544</v>
+        <v>0.06119999999999999</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.00139512113414</v>
+        <v>1.640062164129382</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08979086185492724</v>
+        <v>0.08980586780100736</v>
       </c>
       <c r="C39">
-        <v>846.4891552318708</v>
+        <v>832.0005211068758</v>
       </c>
       <c r="D39">
-        <v>1303.917155231871</v>
+        <v>1303.472521106876</v>
       </c>
       <c r="E39">
-        <v>390.628</v>
+        <v>404.672</v>
       </c>
       <c r="F39">
-        <v>519.628</v>
+        <v>533.672</v>
       </c>
       <c r="G39">
         <v>62.2</v>
@@ -4485,28 +4485,28 @@
         <v>76.7</v>
       </c>
       <c r="M39">
-        <v>46.76652</v>
+        <v>48.03048</v>
       </c>
       <c r="N39">
-        <v>29.93348</v>
+        <v>28.66952000000001</v>
       </c>
       <c r="O39">
-        <v>9.5787136</v>
+        <v>9.174246400000001</v>
       </c>
       <c r="P39">
-        <v>20.3547664</v>
+        <v>19.4952736</v>
       </c>
       <c r="Q39">
-        <v>58.6547664</v>
+        <v>57.7952736</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1065823204046464</v>
+        <v>0.1073384964532377</v>
       </c>
       <c r="T39">
-        <v>0.7921973955340983</v>
+        <v>0.8020529043773157</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.640062164129382</v>
+        <v>1.596902633494398</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08980586780100736</v>
+        <v>0.08982087374708747</v>
       </c>
       <c r="C40">
-        <v>832.0005211068758</v>
+        <v>817.5121901178769</v>
       </c>
       <c r="D40">
-        <v>1303.472521106876</v>
+        <v>1303.028190117877</v>
       </c>
       <c r="E40">
-        <v>404.672</v>
+        <v>418.716</v>
       </c>
       <c r="F40">
-        <v>533.672</v>
+        <v>547.716</v>
       </c>
       <c r="G40">
         <v>62.2</v>
@@ -4567,28 +4567,28 @@
         <v>76.7</v>
       </c>
       <c r="M40">
-        <v>48.03048</v>
+        <v>49.29444</v>
       </c>
       <c r="N40">
-        <v>28.66952000000001</v>
+        <v>27.40556</v>
       </c>
       <c r="O40">
-        <v>9.174246400000001</v>
+        <v>8.7697792</v>
       </c>
       <c r="P40">
-        <v>19.4952736</v>
+        <v>18.6357808</v>
       </c>
       <c r="Q40">
-        <v>57.7952736</v>
+        <v>56.9357808</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1073384964532377</v>
+        <v>0.1081194651591598</v>
       </c>
       <c r="T40">
-        <v>0.8020529043773157</v>
+        <v>0.8122315446580155</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.596902633494398</v>
+        <v>1.555956412122746</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08982087374708747</v>
+        <v>0.08983587969316759</v>
       </c>
       <c r="C41">
-        <v>817.5121901178769</v>
+        <v>803.0241619549782</v>
       </c>
       <c r="D41">
-        <v>1303.028190117877</v>
+        <v>1302.584161954978</v>
       </c>
       <c r="E41">
-        <v>418.716</v>
+        <v>432.7600000000001</v>
       </c>
       <c r="F41">
-        <v>547.716</v>
+        <v>561.7600000000001</v>
       </c>
       <c r="G41">
         <v>62.2</v>
@@ -4649,28 +4649,28 @@
         <v>76.7</v>
       </c>
       <c r="M41">
-        <v>49.29444</v>
+        <v>50.55840000000001</v>
       </c>
       <c r="N41">
-        <v>27.40556</v>
+        <v>26.1416</v>
       </c>
       <c r="O41">
-        <v>8.7697792</v>
+        <v>8.365311999999999</v>
       </c>
       <c r="P41">
-        <v>18.6357808</v>
+        <v>17.776288</v>
       </c>
       <c r="Q41">
-        <v>56.9357808</v>
+        <v>56.07628799999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1081194651591598</v>
+        <v>0.1089264661552793</v>
       </c>
       <c r="T41">
-        <v>0.8122315446580155</v>
+        <v>0.8227494729480721</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.555956412122746</v>
+        <v>1.517057501819678</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08983587969316759</v>
+        <v>0.1079981373857649</v>
       </c>
       <c r="C42">
-        <v>803.0241619549782</v>
+        <v>408.6171766618415</v>
       </c>
       <c r="D42">
-        <v>1302.584161954978</v>
+        <v>922.2211766618416</v>
       </c>
       <c r="E42">
-        <v>432.7600000000001</v>
+        <v>446.8040000000001</v>
       </c>
       <c r="F42">
-        <v>561.7600000000001</v>
+        <v>575.8040000000001</v>
       </c>
       <c r="G42">
         <v>62.2</v>
@@ -4731,45 +4731,45 @@
         <v>76.7</v>
       </c>
       <c r="M42">
-        <v>50.55840000000001</v>
+        <v>84.52802720000003</v>
       </c>
       <c r="N42">
-        <v>26.1416</v>
+        <v>-7.828027200000022</v>
       </c>
       <c r="O42">
-        <v>8.365311999999999</v>
+        <v>-2.504968704000007</v>
       </c>
       <c r="P42">
-        <v>17.776288</v>
+        <v>-5.323058496000016</v>
       </c>
       <c r="Q42">
-        <v>56.07628799999999</v>
+        <v>32.97694150399998</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1089264661552793</v>
+        <v>0.1106553217063178</v>
       </c>
       <c r="T42">
-        <v>0.8227494729480721</v>
+        <v>0.8452822564230954</v>
       </c>
       <c r="U42">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.32</v>
+        <v>0.290365229297579</v>
       </c>
       <c r="W42">
-        <v>0.06119999999999999</v>
+        <v>0.1041743843391154</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y42">
-        <v>1.517057501819678</v>
+        <v>0.9073913415549344</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1079981373857649</v>
+        <v>0.1090081373857648</v>
       </c>
       <c r="C43">
-        <v>408.6171766618415</v>
+        <v>379.8370457307281</v>
       </c>
       <c r="D43">
-        <v>922.2211766618416</v>
+        <v>907.4850457307281</v>
       </c>
       <c r="E43">
-        <v>446.8040000000001</v>
+        <v>460.8480000000001</v>
       </c>
       <c r="F43">
-        <v>575.8040000000001</v>
+        <v>589.8480000000001</v>
       </c>
       <c r="G43">
         <v>62.2</v>
@@ -4813,37 +4813,37 @@
         <v>76.7</v>
       </c>
       <c r="M43">
-        <v>84.52802720000003</v>
+        <v>86.58968640000002</v>
       </c>
       <c r="N43">
-        <v>-7.828027200000022</v>
+        <v>-9.889686400000016</v>
       </c>
       <c r="O43">
-        <v>-2.504968704000007</v>
+        <v>-3.164699648000005</v>
       </c>
       <c r="P43">
-        <v>-5.323058496000016</v>
+        <v>-6.724986752000011</v>
       </c>
       <c r="Q43">
-        <v>32.97694150399998</v>
+        <v>31.57501324799999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1106553217063178</v>
+        <v>0.1117735169081509</v>
       </c>
       <c r="T43">
-        <v>0.8452822564230954</v>
+        <v>0.8598560884303901</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.290365229297579</v>
+        <v>0.2834517714571605</v>
       </c>
       <c r="W43">
-        <v>0.1041743843391154</v>
+        <v>0.1051892799500889</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.9073913415549344</v>
+        <v>0.8857867858036265</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1090081373857649</v>
+        <v>0.1100181373857649</v>
       </c>
       <c r="C44">
-        <v>379.8370457307279</v>
+        <v>351.5204440406138</v>
       </c>
       <c r="D44">
-        <v>907.485045730728</v>
+        <v>893.2124440406138</v>
       </c>
       <c r="E44">
-        <v>460.8480000000001</v>
+        <v>474.8920000000001</v>
       </c>
       <c r="F44">
-        <v>589.8480000000001</v>
+        <v>603.8920000000001</v>
       </c>
       <c r="G44">
         <v>62.2</v>
@@ -4895,37 +4895,37 @@
         <v>76.7</v>
       </c>
       <c r="M44">
-        <v>86.58968640000002</v>
+        <v>88.65134560000001</v>
       </c>
       <c r="N44">
-        <v>-9.889686400000016</v>
+        <v>-11.95134560000001</v>
       </c>
       <c r="O44">
-        <v>-3.164699648000005</v>
+        <v>-3.824430592000003</v>
       </c>
       <c r="P44">
-        <v>-6.724986752000011</v>
+        <v>-8.126915008000008</v>
       </c>
       <c r="Q44">
-        <v>31.57501324799999</v>
+        <v>30.17308499199999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1117735169081509</v>
+        <v>0.1129309470293465</v>
       </c>
       <c r="T44">
-        <v>0.8598560884303901</v>
+        <v>0.8749412829642566</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.2834517714571605</v>
+        <v>0.276859869795366</v>
       </c>
       <c r="W44">
-        <v>0.1051892799500889</v>
+        <v>0.1061569711140403</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8857867858036265</v>
+        <v>0.8651870931105189</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1100181373857649</v>
+        <v>0.1110281373857648</v>
       </c>
       <c r="C45">
-        <v>351.5204440406138</v>
+        <v>323.6458395708643</v>
       </c>
       <c r="D45">
-        <v>893.2124440406138</v>
+        <v>879.3818395708643</v>
       </c>
       <c r="E45">
-        <v>474.8920000000001</v>
+        <v>488.936</v>
       </c>
       <c r="F45">
-        <v>603.8920000000001</v>
+        <v>617.936</v>
       </c>
       <c r="G45">
         <v>62.2</v>
@@ -4977,37 +4977,37 @@
         <v>76.7</v>
       </c>
       <c r="M45">
-        <v>88.65134560000001</v>
+        <v>90.71300480000001</v>
       </c>
       <c r="N45">
-        <v>-11.95134560000001</v>
+        <v>-14.0130048</v>
       </c>
       <c r="O45">
-        <v>-3.824430592000003</v>
+        <v>-4.484161536000001</v>
       </c>
       <c r="P45">
-        <v>-8.126915008000008</v>
+        <v>-9.528843264000002</v>
       </c>
       <c r="Q45">
-        <v>30.17308499199999</v>
+        <v>28.77115673599999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1129309470293465</v>
+        <v>0.1141297139405849</v>
       </c>
       <c r="T45">
-        <v>0.8749412829642566</v>
+        <v>0.8905652344457611</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.276859869795366</v>
+        <v>0.2705676000272896</v>
       </c>
       <c r="W45">
-        <v>0.1061569711140403</v>
+        <v>0.1070806763159939</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8651870931105189</v>
+        <v>0.8455237500852799</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1110281373857648</v>
+        <v>0.1120381373857648</v>
       </c>
       <c r="C46">
-        <v>323.6458395708643</v>
+        <v>296.1930135829906</v>
       </c>
       <c r="D46">
-        <v>879.3818395708643</v>
+        <v>865.9730135829906</v>
       </c>
       <c r="E46">
-        <v>488.936</v>
+        <v>502.98</v>
       </c>
       <c r="F46">
-        <v>617.936</v>
+        <v>631.98</v>
       </c>
       <c r="G46">
         <v>62.2</v>
@@ -5059,37 +5059,37 @@
         <v>76.7</v>
       </c>
       <c r="M46">
-        <v>90.71300480000001</v>
+        <v>92.77466400000002</v>
       </c>
       <c r="N46">
-        <v>-14.0130048</v>
+        <v>-16.07466400000001</v>
       </c>
       <c r="O46">
-        <v>-4.484161536000001</v>
+        <v>-5.143892480000004</v>
       </c>
       <c r="P46">
-        <v>-9.528843264000002</v>
+        <v>-10.93077152000001</v>
       </c>
       <c r="Q46">
-        <v>28.77115673599999</v>
+        <v>27.36922847999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1141297139405849</v>
+        <v>0.1153720723758682</v>
       </c>
       <c r="T46">
-        <v>0.8905652344457611</v>
+        <v>0.9067573296175021</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.2705676000272896</v>
+        <v>0.2645549866933498</v>
       </c>
       <c r="W46">
-        <v>0.1070806763159939</v>
+        <v>0.1079633279534162</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8455237500852799</v>
+        <v>0.8267343334167181</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1120381373857648</v>
+        <v>0.1130481373857649</v>
       </c>
       <c r="C47">
-        <v>296.1930135829906</v>
+        <v>269.1429619997095</v>
       </c>
       <c r="D47">
-        <v>865.9730135829906</v>
+        <v>852.9669619997096</v>
       </c>
       <c r="E47">
-        <v>502.98</v>
+        <v>517.0240000000001</v>
       </c>
       <c r="F47">
-        <v>631.98</v>
+        <v>646.0240000000001</v>
       </c>
       <c r="G47">
         <v>62.2</v>
@@ -5141,37 +5141,37 @@
         <v>76.7</v>
       </c>
       <c r="M47">
-        <v>92.77466400000002</v>
+        <v>94.83632320000002</v>
       </c>
       <c r="N47">
-        <v>-16.07466400000001</v>
+        <v>-18.13632320000002</v>
       </c>
       <c r="O47">
-        <v>-5.143892480000004</v>
+        <v>-5.803623424000007</v>
       </c>
       <c r="P47">
-        <v>-10.93077152000001</v>
+        <v>-12.33269977600001</v>
       </c>
       <c r="Q47">
-        <v>27.36922847999999</v>
+        <v>25.96730022399998</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1153720723758682</v>
+        <v>0.1166604440865325</v>
       </c>
       <c r="T47">
-        <v>0.9067573296175021</v>
+        <v>0.9235491320178265</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.2645549866933498</v>
+        <v>0.2588037913304508</v>
       </c>
       <c r="W47">
-        <v>0.1079633279534162</v>
+        <v>0.1088076034326898</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8267343334167181</v>
+        <v>0.8087618479076589</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1130481373857649</v>
+        <v>0.1408287455049616</v>
       </c>
       <c r="C48">
-        <v>269.1429619997095</v>
+        <v>5.743456104932534</v>
       </c>
       <c r="D48">
-        <v>852.9669619997096</v>
+        <v>603.6114561049326</v>
       </c>
       <c r="E48">
-        <v>517.0240000000001</v>
+        <v>531.0680000000001</v>
       </c>
       <c r="F48">
-        <v>646.0240000000001</v>
+        <v>660.0680000000001</v>
       </c>
       <c r="G48">
         <v>62.2</v>
@@ -5223,45 +5223,45 @@
         <v>76.7</v>
       </c>
       <c r="M48">
-        <v>94.83632320000002</v>
+        <v>132.5416544</v>
       </c>
       <c r="N48">
-        <v>-18.13632320000002</v>
+        <v>-55.84165440000002</v>
       </c>
       <c r="O48">
-        <v>-5.803623424000007</v>
+        <v>-17.86932940800001</v>
       </c>
       <c r="P48">
-        <v>-12.33269977600001</v>
+        <v>-37.97232499200001</v>
       </c>
       <c r="Q48">
-        <v>25.96730022399998</v>
+        <v>0.3276750079999857</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1166604440865325</v>
+        <v>0.1206212225017439</v>
       </c>
       <c r="T48">
-        <v>0.9235491320178265</v>
+        <v>0.9751713524913037</v>
       </c>
       <c r="U48">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.2588037913304508</v>
+        <v>0.1851795204391231</v>
       </c>
       <c r="W48">
-        <v>0.1088076034326898</v>
+        <v>0.1636159522958241</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.8087618479076589</v>
+        <v>0.5786860013722599</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1408287455049616</v>
+        <v>0.1423787455049616</v>
       </c>
       <c r="C49">
-        <v>5.743456104932534</v>
+        <v>-17.98795236233286</v>
       </c>
       <c r="D49">
-        <v>603.6114561049326</v>
+        <v>593.9240476376672</v>
       </c>
       <c r="E49">
-        <v>531.0680000000001</v>
+        <v>545.1120000000001</v>
       </c>
       <c r="F49">
-        <v>660.0680000000001</v>
+        <v>674.1120000000001</v>
       </c>
       <c r="G49">
         <v>62.2</v>
@@ -5305,37 +5305,37 @@
         <v>76.7</v>
       </c>
       <c r="M49">
-        <v>132.5416544</v>
+        <v>135.3616896</v>
       </c>
       <c r="N49">
-        <v>-55.84165440000002</v>
+        <v>-58.66168960000003</v>
       </c>
       <c r="O49">
-        <v>-17.86932940800001</v>
+        <v>-18.77174067200001</v>
       </c>
       <c r="P49">
-        <v>-37.97232499200001</v>
+        <v>-39.88994892800002</v>
       </c>
       <c r="Q49">
-        <v>0.3276750079999857</v>
+        <v>-1.589948928000027</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1206212225017439</v>
+        <v>0.122060092165239</v>
       </c>
       <c r="T49">
-        <v>0.9751713524913037</v>
+        <v>0.9939246477315211</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1851795204391231</v>
+        <v>0.1813216137633081</v>
       </c>
       <c r="W49">
-        <v>0.1636159522958241</v>
+        <v>0.1643906199563278</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5786860013722599</v>
+        <v>0.5666300430103377</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1423787455049616</v>
+        <v>0.1439287455049616</v>
       </c>
       <c r="C50">
-        <v>-17.98795236233263</v>
+        <v>-41.41332444755778</v>
       </c>
       <c r="D50">
-        <v>593.9240476376673</v>
+        <v>584.5426755524422</v>
       </c>
       <c r="E50">
-        <v>545.112</v>
+        <v>559.1560000000001</v>
       </c>
       <c r="F50">
-        <v>674.112</v>
+        <v>688.1560000000001</v>
       </c>
       <c r="G50">
         <v>62.2</v>
@@ -5387,37 +5387,37 @@
         <v>76.7</v>
       </c>
       <c r="M50">
-        <v>135.3616896</v>
+        <v>138.1817248</v>
       </c>
       <c r="N50">
-        <v>-58.6616896</v>
+        <v>-61.48172480000001</v>
       </c>
       <c r="O50">
-        <v>-18.771740672</v>
+        <v>-19.674151936</v>
       </c>
       <c r="P50">
-        <v>-39.889948928</v>
+        <v>-41.80757286400001</v>
       </c>
       <c r="Q50">
-        <v>-1.589948928000005</v>
+        <v>-3.507572864000011</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.122060092165239</v>
+        <v>0.1235553880900476</v>
       </c>
       <c r="T50">
-        <v>0.9939246477315208</v>
+        <v>1.013413366314492</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1813216137633081</v>
+        <v>0.1776211726660978</v>
       </c>
       <c r="W50">
-        <v>0.1643906199563277</v>
+        <v>0.1651336685286476</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5666300430103378</v>
+        <v>0.5550661645815553</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1439287455049616</v>
+        <v>0.1454787455049616</v>
       </c>
       <c r="C51">
-        <v>-41.41332444755778</v>
+        <v>-64.54693670658423</v>
       </c>
       <c r="D51">
-        <v>584.5426755524422</v>
+        <v>575.4530632934158</v>
       </c>
       <c r="E51">
-        <v>559.1560000000001</v>
+        <v>573.2</v>
       </c>
       <c r="F51">
-        <v>688.1560000000001</v>
+        <v>702.2</v>
       </c>
       <c r="G51">
         <v>62.2</v>
@@ -5469,37 +5469,37 @@
         <v>76.7</v>
       </c>
       <c r="M51">
-        <v>138.1817248</v>
+        <v>141.00176</v>
       </c>
       <c r="N51">
-        <v>-61.48172480000001</v>
+        <v>-64.30176000000002</v>
       </c>
       <c r="O51">
-        <v>-19.674151936</v>
+        <v>-20.57656320000001</v>
       </c>
       <c r="P51">
-        <v>-41.80757286400001</v>
+        <v>-43.72519680000001</v>
       </c>
       <c r="Q51">
-        <v>-3.507572864000011</v>
+        <v>-5.425196800000009</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1235553880900476</v>
+        <v>0.1251104958518486</v>
       </c>
       <c r="T51">
-        <v>1.013413366314492</v>
+        <v>1.033681633640782</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1776211726660978</v>
+        <v>0.1740687492127758</v>
       </c>
       <c r="W51">
-        <v>0.1651336685286476</v>
+        <v>0.1658469951580746</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5550661645815553</v>
+        <v>0.5439648412899243</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1454787455049616</v>
+        <v>0.1470287455049616</v>
       </c>
       <c r="C52">
-        <v>-64.54693670658423</v>
+        <v>-87.40219129297122</v>
       </c>
       <c r="D52">
-        <v>575.4530632934158</v>
+        <v>566.6418087070288</v>
       </c>
       <c r="E52">
-        <v>573.2</v>
+        <v>587.244</v>
       </c>
       <c r="F52">
-        <v>702.2</v>
+        <v>716.244</v>
       </c>
       <c r="G52">
         <v>62.2</v>
@@ -5551,37 +5551,37 @@
         <v>76.7</v>
       </c>
       <c r="M52">
-        <v>141.00176</v>
+        <v>143.8217952</v>
       </c>
       <c r="N52">
-        <v>-64.30176000000002</v>
+        <v>-67.12179519999999</v>
       </c>
       <c r="O52">
-        <v>-20.57656320000001</v>
+        <v>-21.478974464</v>
       </c>
       <c r="P52">
-        <v>-43.72519680000001</v>
+        <v>-45.64282073599999</v>
       </c>
       <c r="Q52">
-        <v>-5.425196800000009</v>
+        <v>-7.342820735999993</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1251104958518486</v>
+        <v>0.1267290773998455</v>
       </c>
       <c r="T52">
-        <v>1.033681633640782</v>
+        <v>1.054777177184471</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1740687492127758</v>
+        <v>0.1706556364831135</v>
       </c>
       <c r="W52">
-        <v>0.1658469951580746</v>
+        <v>0.1665323481941908</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5439648412899243</v>
+        <v>0.5332988640097298</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1470287455049616</v>
+        <v>0.1485787455049616</v>
       </c>
       <c r="C53">
-        <v>-87.40219129297122</v>
+        <v>-109.9916818920319</v>
       </c>
       <c r="D53">
-        <v>566.6418087070288</v>
+        <v>558.0963181079682</v>
       </c>
       <c r="E53">
-        <v>587.244</v>
+        <v>601.2880000000001</v>
       </c>
       <c r="F53">
-        <v>716.244</v>
+        <v>730.2880000000001</v>
       </c>
       <c r="G53">
         <v>62.2</v>
@@ -5633,37 +5633,37 @@
         <v>76.7</v>
       </c>
       <c r="M53">
-        <v>143.8217952</v>
+        <v>146.6418304</v>
       </c>
       <c r="N53">
-        <v>-67.12179519999999</v>
+        <v>-69.94183040000003</v>
       </c>
       <c r="O53">
-        <v>-21.478974464</v>
+        <v>-22.38138572800001</v>
       </c>
       <c r="P53">
-        <v>-45.64282073599999</v>
+        <v>-47.56044467200002</v>
       </c>
       <c r="Q53">
-        <v>-7.342820735999993</v>
+        <v>-9.26044467200002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1267290773998455</v>
+        <v>0.1284150998456756</v>
       </c>
       <c r="T53">
-        <v>1.054777177184471</v>
+        <v>1.076751701709148</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1706556364831135</v>
+        <v>0.1673737973199767</v>
       </c>
       <c r="W53">
-        <v>0.1665323481941908</v>
+        <v>0.1671913414981487</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5332988640097298</v>
+        <v>0.5230431166249272</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1485787455049616</v>
+        <v>0.1501287455049616</v>
       </c>
       <c r="C54">
-        <v>-109.9916818920319</v>
+        <v>-132.3272537774258</v>
       </c>
       <c r="D54">
-        <v>558.0963181079682</v>
+        <v>549.8047462225743</v>
       </c>
       <c r="E54">
-        <v>601.2880000000001</v>
+        <v>615.3320000000001</v>
       </c>
       <c r="F54">
-        <v>730.2880000000001</v>
+        <v>744.3320000000001</v>
       </c>
       <c r="G54">
         <v>62.2</v>
@@ -5715,37 +5715,37 @@
         <v>76.7</v>
       </c>
       <c r="M54">
-        <v>146.6418304</v>
+        <v>149.4618656</v>
       </c>
       <c r="N54">
-        <v>-69.94183040000003</v>
+        <v>-72.76186560000004</v>
       </c>
       <c r="O54">
-        <v>-22.38138572800001</v>
+        <v>-23.28379699200001</v>
       </c>
       <c r="P54">
-        <v>-47.56044467200002</v>
+        <v>-49.47806860800002</v>
       </c>
       <c r="Q54">
-        <v>-9.26044467200002</v>
+        <v>-11.17806860800003</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1284150998456756</v>
+        <v>0.1301728679274985</v>
       </c>
       <c r="T54">
-        <v>1.076751701709148</v>
+        <v>1.099661312383811</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1673737973199767</v>
+        <v>0.1642158011441281</v>
       </c>
       <c r="W54">
-        <v>0.1671913414981487</v>
+        <v>0.1678254671302591</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5230431166249272</v>
+        <v>0.5131743785754002</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1501287455049616</v>
+        <v>0.1516787455049616</v>
       </c>
       <c r="C55">
-        <v>-132.3272537774258</v>
+        <v>-154.4200585926004</v>
       </c>
       <c r="D55">
-        <v>549.8047462225743</v>
+        <v>541.7559414073996</v>
       </c>
       <c r="E55">
-        <v>615.3320000000001</v>
+        <v>629.3760000000001</v>
       </c>
       <c r="F55">
-        <v>744.3320000000001</v>
+        <v>758.3760000000001</v>
       </c>
       <c r="G55">
         <v>62.2</v>
@@ -5797,37 +5797,37 @@
         <v>76.7</v>
       </c>
       <c r="M55">
-        <v>149.4618656</v>
+        <v>152.2819008</v>
       </c>
       <c r="N55">
-        <v>-72.76186560000004</v>
+        <v>-75.58190080000001</v>
       </c>
       <c r="O55">
-        <v>-23.28379699200001</v>
+        <v>-24.186208256</v>
       </c>
       <c r="P55">
-        <v>-49.47806860800002</v>
+        <v>-51.39569254400001</v>
       </c>
       <c r="Q55">
-        <v>-11.17806860800003</v>
+        <v>-13.09569254400002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1301728679274985</v>
+        <v>0.132007060708531</v>
       </c>
       <c r="T55">
-        <v>1.099661312383811</v>
+        <v>1.123566993087806</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1642158011441281</v>
+        <v>0.1611747677896072</v>
       </c>
       <c r="W55">
-        <v>0.1678254671302591</v>
+        <v>0.1684361066278469</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5131743785754002</v>
+        <v>0.5036711493425226</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1516787455049616</v>
+        <v>0.1730398726777408</v>
       </c>
       <c r="C56">
-        <v>-154.4200585926004</v>
+        <v>-259.4144605182753</v>
       </c>
       <c r="D56">
-        <v>541.7559414073996</v>
+        <v>450.8055394817248</v>
       </c>
       <c r="E56">
-        <v>629.3760000000001</v>
+        <v>643.4200000000001</v>
       </c>
       <c r="F56">
-        <v>758.3760000000001</v>
+        <v>772.4200000000001</v>
       </c>
       <c r="G56">
         <v>62.2</v>
@@ -5879,45 +5879,45 @@
         <v>76.7</v>
       </c>
       <c r="M56">
-        <v>152.2819008</v>
+        <v>182.136636</v>
       </c>
       <c r="N56">
-        <v>-75.58190080000001</v>
+        <v>-105.436636</v>
       </c>
       <c r="O56">
-        <v>-24.186208256</v>
+        <v>-33.73972352000001</v>
       </c>
       <c r="P56">
-        <v>-51.39569254400001</v>
+        <v>-71.69691248000002</v>
       </c>
       <c r="Q56">
-        <v>-13.09569254400002</v>
+        <v>-33.39691248000003</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.132007060708531</v>
+        <v>0.1351697224415634</v>
       </c>
       <c r="T56">
-        <v>1.123566993087806</v>
+        <v>1.16478707766477</v>
       </c>
       <c r="U56">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.1611747677896072</v>
+        <v>0.1347559751789859</v>
       </c>
       <c r="W56">
-        <v>0.1684361066278469</v>
+        <v>0.2040245410527951</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.5036711493425226</v>
+        <v>0.421112422434331</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1730398726777408</v>
+        <v>0.1749398726777409</v>
       </c>
       <c r="C57">
-        <v>-259.4144605182753</v>
+        <v>-280.0910404276012</v>
       </c>
       <c r="D57">
-        <v>450.8055394817248</v>
+        <v>444.172959572399</v>
       </c>
       <c r="E57">
-        <v>643.4200000000001</v>
+        <v>657.4640000000002</v>
       </c>
       <c r="F57">
-        <v>772.4200000000001</v>
+        <v>786.4640000000002</v>
       </c>
       <c r="G57">
         <v>62.2</v>
@@ -5961,37 +5961,37 @@
         <v>76.7</v>
       </c>
       <c r="M57">
-        <v>182.136636</v>
+        <v>185.4482112000001</v>
       </c>
       <c r="N57">
-        <v>-105.436636</v>
+        <v>-108.7482112000001</v>
       </c>
       <c r="O57">
-        <v>-33.73972352000001</v>
+        <v>-34.79942758400002</v>
       </c>
       <c r="P57">
-        <v>-71.69691248000002</v>
+        <v>-73.94878361600004</v>
       </c>
       <c r="Q57">
-        <v>-33.39691248000003</v>
+        <v>-35.64878361600005</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1351697224415634</v>
+        <v>0.1372008524970535</v>
       </c>
       <c r="T57">
-        <v>1.16478707766477</v>
+        <v>1.19125951124806</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.1347559751789859</v>
+        <v>0.1323496184793612</v>
       </c>
       <c r="W57">
-        <v>0.2040245410527951</v>
+        <v>0.2045919599625667</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.421112422434331</v>
+        <v>0.4135925577480036</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1749398726777409</v>
+        <v>0.1768398726777409</v>
       </c>
       <c r="C58">
-        <v>-280.0910404276012</v>
+        <v>-300.5752834310646</v>
       </c>
       <c r="D58">
-        <v>444.172959572399</v>
+        <v>437.7327165689356</v>
       </c>
       <c r="E58">
-        <v>657.4640000000002</v>
+        <v>671.5080000000002</v>
       </c>
       <c r="F58">
-        <v>786.4640000000002</v>
+        <v>800.5080000000002</v>
       </c>
       <c r="G58">
         <v>62.2</v>
@@ -6043,37 +6043,37 @@
         <v>76.7</v>
       </c>
       <c r="M58">
-        <v>185.4482112000001</v>
+        <v>188.7597864000001</v>
       </c>
       <c r="N58">
-        <v>-108.7482112000001</v>
+        <v>-112.0597864</v>
       </c>
       <c r="O58">
-        <v>-34.79942758400002</v>
+        <v>-35.85913164800002</v>
       </c>
       <c r="P58">
-        <v>-73.94878361600004</v>
+        <v>-76.20065475200003</v>
       </c>
       <c r="Q58">
-        <v>-35.64878361600005</v>
+        <v>-37.90065475200004</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1372008524970535</v>
+        <v>0.1393264537179152</v>
       </c>
       <c r="T58">
-        <v>1.19125951124806</v>
+        <v>1.218963220811968</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1323496184793612</v>
+        <v>0.1300276953481443</v>
       </c>
       <c r="W58">
-        <v>0.2045919599625667</v>
+        <v>0.2051394694369076</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4135925577480036</v>
+        <v>0.4063365479629509</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1768398726777409</v>
+        <v>0.1787398726777408</v>
       </c>
       <c r="C59">
-        <v>-300.5752834310646</v>
+        <v>-320.8754362671446</v>
       </c>
       <c r="D59">
-        <v>437.7327165689356</v>
+        <v>431.4765637328555</v>
       </c>
       <c r="E59">
-        <v>671.5080000000002</v>
+        <v>685.5520000000001</v>
       </c>
       <c r="F59">
-        <v>800.5080000000002</v>
+        <v>814.5520000000001</v>
       </c>
       <c r="G59">
         <v>62.2</v>
@@ -6125,37 +6125,37 @@
         <v>76.7</v>
       </c>
       <c r="M59">
-        <v>188.7597864000001</v>
+        <v>192.0713616</v>
       </c>
       <c r="N59">
-        <v>-112.0597864</v>
+        <v>-115.3713616</v>
       </c>
       <c r="O59">
-        <v>-35.85913164800002</v>
+        <v>-36.91883571200002</v>
       </c>
       <c r="P59">
-        <v>-76.20065475200003</v>
+        <v>-78.45252588800003</v>
       </c>
       <c r="Q59">
-        <v>-37.90065475200004</v>
+        <v>-40.15252588800003</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1393264537179152</v>
+        <v>0.1415532740445322</v>
       </c>
       <c r="T59">
-        <v>1.218963220811968</v>
+        <v>1.247986154640825</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.1300276953481443</v>
+        <v>0.127785838531797</v>
       </c>
       <c r="W59">
-        <v>0.2051394694369076</v>
+        <v>0.2056680992742023</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4063365479629509</v>
+        <v>0.3993307454118656</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1787398726777409</v>
+        <v>0.1806398726777408</v>
       </c>
       <c r="C60">
-        <v>-320.8754362671446</v>
+        <v>-340.9992808621607</v>
       </c>
       <c r="D60">
-        <v>431.4765637328554</v>
+        <v>425.3967191378393</v>
       </c>
       <c r="E60">
-        <v>685.552</v>
+        <v>699.596</v>
       </c>
       <c r="F60">
-        <v>814.552</v>
+        <v>828.596</v>
       </c>
       <c r="G60">
         <v>62.2</v>
@@ -6207,37 +6207,37 @@
         <v>76.7</v>
       </c>
       <c r="M60">
-        <v>192.0713616</v>
+        <v>195.3829368</v>
       </c>
       <c r="N60">
-        <v>-115.3713616</v>
+        <v>-118.6829368</v>
       </c>
       <c r="O60">
-        <v>-36.918835712</v>
+        <v>-37.97853977600001</v>
       </c>
       <c r="P60">
-        <v>-78.45252588800001</v>
+        <v>-80.704397024</v>
       </c>
       <c r="Q60">
-        <v>-40.15252588800001</v>
+        <v>-42.404397024</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1415532740445322</v>
+        <v>0.1438887197529354</v>
       </c>
       <c r="T60">
-        <v>1.247986154640824</v>
+        <v>1.278424841339381</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.127785838531797</v>
+        <v>0.1256199768617666</v>
       </c>
       <c r="W60">
-        <v>0.2056680992742023</v>
+        <v>0.2061788094559955</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3993307454118656</v>
+        <v>0.3925624276930205</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1806398726777408</v>
+        <v>0.1825398726777409</v>
       </c>
       <c r="C61">
-        <v>-340.9992808621607</v>
+        <v>-360.9541666230882</v>
       </c>
       <c r="D61">
-        <v>425.3967191378393</v>
+        <v>419.4858333769118</v>
       </c>
       <c r="E61">
-        <v>699.596</v>
+        <v>713.64</v>
       </c>
       <c r="F61">
-        <v>828.596</v>
+        <v>842.64</v>
       </c>
       <c r="G61">
         <v>62.2</v>
@@ -6289,37 +6289,37 @@
         <v>76.7</v>
       </c>
       <c r="M61">
-        <v>195.3829368</v>
+        <v>198.694512</v>
       </c>
       <c r="N61">
-        <v>-118.6829368</v>
+        <v>-121.994512</v>
       </c>
       <c r="O61">
-        <v>-37.97853977600001</v>
+        <v>-39.03824384</v>
       </c>
       <c r="P61">
-        <v>-80.704397024</v>
+        <v>-82.95626816000001</v>
       </c>
       <c r="Q61">
-        <v>-42.404397024</v>
+        <v>-44.65626816000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1438887197529354</v>
+        <v>0.1463409377467588</v>
       </c>
       <c r="T61">
-        <v>1.278424841339381</v>
+        <v>1.310385462372865</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1256199768617666</v>
+        <v>0.1235263105807371</v>
       </c>
       <c r="W61">
-        <v>0.2061788094559955</v>
+        <v>0.2066724959650622</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3925624276930205</v>
+        <v>0.3860197205648035</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1825398726777409</v>
+        <v>0.1844398726777408</v>
       </c>
       <c r="C62">
-        <v>-360.9541666230882</v>
+        <v>-380.747040075019</v>
       </c>
       <c r="D62">
-        <v>419.4858333769118</v>
+        <v>413.7369599249811</v>
       </c>
       <c r="E62">
-        <v>713.64</v>
+        <v>727.6840000000001</v>
       </c>
       <c r="F62">
-        <v>842.64</v>
+        <v>856.6840000000001</v>
       </c>
       <c r="G62">
         <v>62.2</v>
@@ -6371,37 +6371,37 @@
         <v>76.7</v>
       </c>
       <c r="M62">
-        <v>198.694512</v>
+        <v>202.0060872</v>
       </c>
       <c r="N62">
-        <v>-121.994512</v>
+        <v>-125.3060872</v>
       </c>
       <c r="O62">
-        <v>-39.03824384</v>
+        <v>-40.09794790400001</v>
       </c>
       <c r="P62">
-        <v>-82.95626816000001</v>
+        <v>-85.20813929600001</v>
       </c>
       <c r="Q62">
-        <v>-44.65626816000001</v>
+        <v>-46.90813929600002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1463409377467588</v>
+        <v>0.1489189105094962</v>
       </c>
       <c r="T62">
-        <v>1.310385462372865</v>
+        <v>1.343985089613196</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1235263105807371</v>
+        <v>0.121501289095807</v>
       </c>
       <c r="W62">
-        <v>0.2066724959650622</v>
+        <v>0.2071499960312087</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3860197205648035</v>
+        <v>0.3796915284243969</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1844398726777408</v>
+        <v>0.1863398726777409</v>
       </c>
       <c r="C63">
-        <v>-380.747040075019</v>
+        <v>-400.3844720945571</v>
       </c>
       <c r="D63">
-        <v>413.7369599249811</v>
+        <v>408.143527905443</v>
       </c>
       <c r="E63">
-        <v>727.6840000000001</v>
+        <v>741.7280000000001</v>
       </c>
       <c r="F63">
-        <v>856.6840000000001</v>
+        <v>870.7280000000001</v>
       </c>
       <c r="G63">
         <v>62.2</v>
@@ -6453,37 +6453,37 @@
         <v>76.7</v>
       </c>
       <c r="M63">
-        <v>202.0060872</v>
+        <v>205.3176624</v>
       </c>
       <c r="N63">
-        <v>-125.3060872</v>
+        <v>-128.6176624</v>
       </c>
       <c r="O63">
-        <v>-40.09794790400001</v>
+        <v>-41.15765196800001</v>
       </c>
       <c r="P63">
-        <v>-85.20813929600001</v>
+        <v>-87.46001043200002</v>
       </c>
       <c r="Q63">
-        <v>-46.90813929600002</v>
+        <v>-49.16001043200002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1489189105094962</v>
+        <v>0.1516325660492198</v>
       </c>
       <c r="T63">
-        <v>1.343985089613196</v>
+        <v>1.379353118287227</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.121501289095807</v>
+        <v>0.1195415908845843</v>
       </c>
       <c r="W63">
-        <v>0.2071499960312087</v>
+        <v>0.207612092869415</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3796915284243969</v>
+        <v>0.3735674715143259</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1863398726777409</v>
+        <v>0.1882398726777409</v>
       </c>
       <c r="C64">
-        <v>-400.3844720945571</v>
+        <v>-419.8726829636216</v>
       </c>
       <c r="D64">
-        <v>408.143527905443</v>
+        <v>402.6993170363784</v>
       </c>
       <c r="E64">
-        <v>741.7280000000001</v>
+        <v>755.772</v>
       </c>
       <c r="F64">
-        <v>870.7280000000001</v>
+        <v>884.772</v>
       </c>
       <c r="G64">
         <v>62.2</v>
@@ -6535,37 +6535,37 @@
         <v>76.7</v>
       </c>
       <c r="M64">
-        <v>205.3176624</v>
+        <v>208.6292376</v>
       </c>
       <c r="N64">
-        <v>-128.6176624</v>
+        <v>-131.9292376</v>
       </c>
       <c r="O64">
-        <v>-41.15765196800001</v>
+        <v>-42.217356032</v>
       </c>
       <c r="P64">
-        <v>-87.46001043200002</v>
+        <v>-89.71188156800002</v>
       </c>
       <c r="Q64">
-        <v>-49.16001043200002</v>
+        <v>-51.41188156800003</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1516325660492198</v>
+        <v>0.1544929056721717</v>
       </c>
       <c r="T64">
-        <v>1.379353118287227</v>
+        <v>1.41663293229499</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1195415908845843</v>
+        <v>0.1176441053149877</v>
       </c>
       <c r="W64">
-        <v>0.207612092869415</v>
+        <v>0.2080595199667259</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3735674715143259</v>
+        <v>0.3676378291093366</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1882398726777409</v>
+        <v>0.1901398726777409</v>
       </c>
       <c r="C65">
-        <v>-419.8726829636216</v>
+        <v>-439.2175654444964</v>
       </c>
       <c r="D65">
-        <v>402.6993170363784</v>
+        <v>397.3984345555037</v>
       </c>
       <c r="E65">
-        <v>755.772</v>
+        <v>769.816</v>
       </c>
       <c r="F65">
-        <v>884.772</v>
+        <v>898.816</v>
       </c>
       <c r="G65">
         <v>62.2</v>
@@ -6617,37 +6617,37 @@
         <v>76.7</v>
       </c>
       <c r="M65">
-        <v>208.6292376</v>
+        <v>211.9408128</v>
       </c>
       <c r="N65">
-        <v>-131.9292376</v>
+        <v>-135.2408128</v>
       </c>
       <c r="O65">
-        <v>-42.217356032</v>
+        <v>-43.27706009600001</v>
       </c>
       <c r="P65">
-        <v>-89.71188156800002</v>
+        <v>-91.963752704</v>
       </c>
       <c r="Q65">
-        <v>-51.41188156800003</v>
+        <v>-53.663752704</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1544929056721717</v>
+        <v>0.1575121530519543</v>
       </c>
       <c r="T65">
-        <v>1.41663293229499</v>
+        <v>1.455983847080962</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1176441053149877</v>
+        <v>0.1158059161694411</v>
       </c>
       <c r="W65">
-        <v>0.2080595199667259</v>
+        <v>0.2084929649672458</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3676378291093366</v>
+        <v>0.3618934880295033</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1901398726777409</v>
+        <v>0.1920398726777409</v>
       </c>
       <c r="C66">
-        <v>-439.2175654444964</v>
+        <v>-458.4247060560814</v>
       </c>
       <c r="D66">
-        <v>397.3984345555037</v>
+        <v>392.2352939439187</v>
       </c>
       <c r="E66">
-        <v>769.816</v>
+        <v>783.8600000000001</v>
       </c>
       <c r="F66">
-        <v>898.816</v>
+        <v>912.8600000000001</v>
       </c>
       <c r="G66">
         <v>62.2</v>
@@ -6699,37 +6699,37 @@
         <v>76.7</v>
       </c>
       <c r="M66">
-        <v>211.9408128</v>
+        <v>215.252388</v>
       </c>
       <c r="N66">
-        <v>-135.2408128</v>
+        <v>-138.552388</v>
       </c>
       <c r="O66">
-        <v>-43.27706009600001</v>
+        <v>-44.33676416</v>
       </c>
       <c r="P66">
-        <v>-91.963752704</v>
+        <v>-94.21562384000001</v>
       </c>
       <c r="Q66">
-        <v>-53.663752704</v>
+        <v>-55.91562384000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1575121530519543</v>
+        <v>0.1607039288534387</v>
       </c>
       <c r="T66">
-        <v>1.455983847080962</v>
+        <v>1.49758338556899</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.1158059161694411</v>
+        <v>0.1140242866899112</v>
       </c>
       <c r="W66">
-        <v>0.2084929649672458</v>
+        <v>0.208913073198519</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3618934880295033</v>
+        <v>0.3563258959059725</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1920398726777409</v>
+        <v>0.1939398726777408</v>
       </c>
       <c r="C67">
-        <v>-458.4247060560814</v>
+        <v>-477.4994047128476</v>
       </c>
       <c r="D67">
-        <v>392.2352939439187</v>
+        <v>387.2045952871525</v>
       </c>
       <c r="E67">
-        <v>783.8600000000001</v>
+        <v>797.9040000000001</v>
       </c>
       <c r="F67">
-        <v>912.8600000000001</v>
+        <v>926.9040000000001</v>
       </c>
       <c r="G67">
         <v>62.2</v>
@@ -6781,37 +6781,37 @@
         <v>76.7</v>
       </c>
       <c r="M67">
-        <v>215.252388</v>
+        <v>218.5639632</v>
       </c>
       <c r="N67">
-        <v>-138.552388</v>
+        <v>-141.8639632000001</v>
       </c>
       <c r="O67">
-        <v>-44.33676416</v>
+        <v>-45.39646822400002</v>
       </c>
       <c r="P67">
-        <v>-94.21562384000001</v>
+        <v>-96.46749497600004</v>
       </c>
       <c r="Q67">
-        <v>-55.91562384000001</v>
+        <v>-58.16749497600004</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1607039288534387</v>
+        <v>0.1640834561726575</v>
       </c>
       <c r="T67">
-        <v>1.49758338556899</v>
+        <v>1.541629955732783</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1140242866899112</v>
+        <v>0.1122966459824883</v>
       </c>
       <c r="W67">
-        <v>0.208913073198519</v>
+        <v>0.2093204508773293</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3563258959059725</v>
+        <v>0.3509270186952758</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1939398726777408</v>
+        <v>0.1958398726777409</v>
       </c>
       <c r="C68">
-        <v>-477.4994047128476</v>
+        <v>-496.4466928716274</v>
       </c>
       <c r="D68">
-        <v>387.2045952871525</v>
+        <v>382.3013071283727</v>
       </c>
       <c r="E68">
-        <v>797.9040000000001</v>
+        <v>811.9480000000001</v>
       </c>
       <c r="F68">
-        <v>926.9040000000001</v>
+        <v>940.9480000000001</v>
       </c>
       <c r="G68">
         <v>62.2</v>
@@ -6863,37 +6863,37 @@
         <v>76.7</v>
       </c>
       <c r="M68">
-        <v>218.5639632</v>
+        <v>221.8755384</v>
       </c>
       <c r="N68">
-        <v>-141.8639632000001</v>
+        <v>-145.1755384000001</v>
       </c>
       <c r="O68">
-        <v>-45.39646822400002</v>
+        <v>-46.45617228800002</v>
       </c>
       <c r="P68">
-        <v>-96.46749497600004</v>
+        <v>-98.71936611200003</v>
       </c>
       <c r="Q68">
-        <v>-58.16749497600004</v>
+        <v>-60.41936611200003</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1640834561726575</v>
+        <v>0.1676678033294047</v>
       </c>
       <c r="T68">
-        <v>1.541629955732783</v>
+        <v>1.588346014997413</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1122966459824883</v>
+        <v>0.1106205766394661</v>
       </c>
       <c r="W68">
-        <v>0.2093204508773293</v>
+        <v>0.2097156680284139</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3509270186952758</v>
+        <v>0.3456893019983314</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1958398726777409</v>
+        <v>0.1977398726777409</v>
       </c>
       <c r="C69">
-        <v>-496.4466928716274</v>
+        <v>-515.2713503168559</v>
       </c>
       <c r="D69">
-        <v>382.3013071283727</v>
+        <v>377.5206496831441</v>
       </c>
       <c r="E69">
-        <v>811.9480000000001</v>
+        <v>825.9920000000001</v>
       </c>
       <c r="F69">
-        <v>940.9480000000001</v>
+        <v>954.9920000000001</v>
       </c>
       <c r="G69">
         <v>62.2</v>
@@ -6945,37 +6945,37 @@
         <v>76.7</v>
       </c>
       <c r="M69">
-        <v>221.8755384</v>
+        <v>225.1871136</v>
       </c>
       <c r="N69">
-        <v>-145.1755384000001</v>
+        <v>-148.4871136</v>
       </c>
       <c r="O69">
-        <v>-46.45617228800002</v>
+        <v>-47.51587635200001</v>
       </c>
       <c r="P69">
-        <v>-98.71936611200003</v>
+        <v>-100.971237248</v>
       </c>
       <c r="Q69">
-        <v>-60.41936611200003</v>
+        <v>-62.67123724800003</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1676678033294047</v>
+        <v>0.1714761721834486</v>
       </c>
       <c r="T69">
-        <v>1.588346014997413</v>
+        <v>1.637981827966083</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1106205766394661</v>
+        <v>0.1089938034535916</v>
       </c>
       <c r="W69">
-        <v>0.2097156680284139</v>
+        <v>0.2100992611456431</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3456893019983314</v>
+        <v>0.3406056357924736</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1977398726777409</v>
+        <v>0.1996398726777409</v>
       </c>
       <c r="C70">
-        <v>-515.2713503168559</v>
+        <v>-533.9779207019767</v>
       </c>
       <c r="D70">
-        <v>377.5206496831441</v>
+        <v>372.8580792980235</v>
       </c>
       <c r="E70">
-        <v>825.9920000000001</v>
+        <v>840.0360000000002</v>
       </c>
       <c r="F70">
-        <v>954.9920000000001</v>
+        <v>969.0360000000002</v>
       </c>
       <c r="G70">
         <v>62.2</v>
@@ -7027,37 +7027,37 @@
         <v>76.7</v>
       </c>
       <c r="M70">
-        <v>225.1871136</v>
+        <v>228.4986888000001</v>
       </c>
       <c r="N70">
-        <v>-148.4871136</v>
+        <v>-151.7986888</v>
       </c>
       <c r="O70">
-        <v>-47.51587635200001</v>
+        <v>-48.57558041600002</v>
       </c>
       <c r="P70">
-        <v>-100.971237248</v>
+        <v>-103.223108384</v>
       </c>
       <c r="Q70">
-        <v>-62.67123724800003</v>
+        <v>-64.92310838400003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1714761721834486</v>
+        <v>0.1755302422538824</v>
       </c>
       <c r="T70">
-        <v>1.637981827966083</v>
+        <v>1.69081995144886</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1089938034535916</v>
+        <v>0.1074141831136844</v>
       </c>
       <c r="W70">
-        <v>0.2100992611456431</v>
+        <v>0.2104717356217932</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3406056357924736</v>
+        <v>0.3356693222302639</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1996398726777409</v>
+        <v>0.2015398726777408</v>
       </c>
       <c r="C71">
-        <v>-533.9779207019767</v>
+        <v>-552.5707259532313</v>
       </c>
       <c r="D71">
-        <v>372.8580792980235</v>
+        <v>368.3092740467688</v>
       </c>
       <c r="E71">
-        <v>840.0360000000002</v>
+        <v>854.0800000000002</v>
       </c>
       <c r="F71">
-        <v>969.0360000000002</v>
+        <v>983.0800000000002</v>
       </c>
       <c r="G71">
         <v>62.2</v>
@@ -7109,37 +7109,37 @@
         <v>76.7</v>
       </c>
       <c r="M71">
-        <v>228.4986888000001</v>
+        <v>231.810264</v>
       </c>
       <c r="N71">
-        <v>-151.7986888</v>
+        <v>-155.110264</v>
       </c>
       <c r="O71">
-        <v>-48.57558041600002</v>
+        <v>-49.63528448000001</v>
       </c>
       <c r="P71">
-        <v>-103.223108384</v>
+        <v>-105.47497952</v>
       </c>
       <c r="Q71">
-        <v>-64.92310838400003</v>
+        <v>-67.17497952000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1755302422538824</v>
+        <v>0.1798545836623451</v>
       </c>
       <c r="T71">
-        <v>1.69081995144886</v>
+        <v>1.747180616497155</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1074141831136844</v>
+        <v>0.1058796947834889</v>
       </c>
       <c r="W71">
-        <v>0.2104717356217932</v>
+        <v>0.2108335679700533</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3356693222302639</v>
+        <v>0.330874046198403</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2015398726777408</v>
+        <v>0.2034398726777409</v>
       </c>
       <c r="C72">
-        <v>-552.5707259532313</v>
+        <v>-571.0538796318151</v>
       </c>
       <c r="D72">
-        <v>368.3092740467688</v>
+        <v>363.870120368185</v>
       </c>
       <c r="E72">
-        <v>854.0800000000002</v>
+        <v>868.1240000000001</v>
       </c>
       <c r="F72">
-        <v>983.0800000000002</v>
+        <v>997.1240000000001</v>
       </c>
       <c r="G72">
         <v>62.2</v>
@@ -7191,37 +7191,37 @@
         <v>76.7</v>
       </c>
       <c r="M72">
-        <v>231.810264</v>
+        <v>235.1218392</v>
       </c>
       <c r="N72">
-        <v>-155.110264</v>
+        <v>-158.4218392</v>
       </c>
       <c r="O72">
-        <v>-49.63528448000001</v>
+        <v>-50.69498854400001</v>
       </c>
       <c r="P72">
-        <v>-105.47497952</v>
+        <v>-107.726850656</v>
       </c>
       <c r="Q72">
-        <v>-67.17497952000002</v>
+        <v>-69.42685065600001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1798545836623451</v>
+        <v>0.1844771555127709</v>
       </c>
       <c r="T72">
-        <v>1.747180616497155</v>
+        <v>1.807428223962574</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1058796947834889</v>
+        <v>0.1043884314766792</v>
       </c>
       <c r="W72">
-        <v>0.2108335679700533</v>
+        <v>0.211185207857799</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.330874046198403</v>
+        <v>0.3262138483646227</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2034398726777408</v>
+        <v>0.2053398726777408</v>
       </c>
       <c r="C73">
-        <v>-571.0538796318149</v>
+        <v>-589.4312993412316</v>
       </c>
       <c r="D73">
-        <v>363.8701203681851</v>
+        <v>359.5367006587685</v>
       </c>
       <c r="E73">
-        <v>868.124</v>
+        <v>882.168</v>
       </c>
       <c r="F73">
-        <v>997.124</v>
+        <v>1011.168</v>
       </c>
       <c r="G73">
         <v>62.2</v>
@@ -7273,37 +7273,37 @@
         <v>76.7</v>
       </c>
       <c r="M73">
-        <v>235.1218392</v>
+        <v>238.4334144</v>
       </c>
       <c r="N73">
-        <v>-158.4218392</v>
+        <v>-161.7334144</v>
       </c>
       <c r="O73">
-        <v>-50.69498854400001</v>
+        <v>-51.75469260800001</v>
       </c>
       <c r="P73">
-        <v>-107.726850656</v>
+        <v>-109.978721792</v>
       </c>
       <c r="Q73">
-        <v>-69.42685065600001</v>
+        <v>-71.67872179200002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1844771555127708</v>
+        <v>0.1894299110667983</v>
       </c>
       <c r="T73">
-        <v>1.807428223962573</v>
+        <v>1.871979231961237</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.1043884314766793</v>
+        <v>0.1029385921506143</v>
       </c>
       <c r="W73">
-        <v>0.211185207857799</v>
+        <v>0.2115270799708852</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3262138483646226</v>
+        <v>0.3216831004706695</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2053398726777408</v>
+        <v>0.2072398726777408</v>
       </c>
       <c r="C74">
-        <v>-589.4312993412316</v>
+        <v>-607.7067182585101</v>
       </c>
       <c r="D74">
-        <v>359.5367006587685</v>
+        <v>355.3052817414898</v>
       </c>
       <c r="E74">
-        <v>882.168</v>
+        <v>896.212</v>
       </c>
       <c r="F74">
-        <v>1011.168</v>
+        <v>1025.212</v>
       </c>
       <c r="G74">
         <v>62.2</v>
@@ -7355,37 +7355,37 @@
         <v>76.7</v>
       </c>
       <c r="M74">
-        <v>238.4334144</v>
+        <v>241.7449896</v>
       </c>
       <c r="N74">
-        <v>-161.7334144</v>
+        <v>-165.0449896</v>
       </c>
       <c r="O74">
-        <v>-51.75469260800001</v>
+        <v>-52.814396672</v>
       </c>
       <c r="P74">
-        <v>-109.978721792</v>
+        <v>-112.230592928</v>
       </c>
       <c r="Q74">
-        <v>-71.67872179200002</v>
+        <v>-73.93059292800001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1894299110667983</v>
+        <v>0.1947495374026057</v>
       </c>
       <c r="T74">
-        <v>1.871979231961237</v>
+        <v>1.941311796107949</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1029385921506143</v>
+        <v>0.1015284744499209</v>
       </c>
       <c r="W74">
-        <v>0.2115270799708852</v>
+        <v>0.2118595857247086</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3216831004706695</v>
+        <v>0.3172764826560028</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2072398726777408</v>
+        <v>0.2091398726777409</v>
       </c>
       <c r="C75">
-        <v>-607.7067182585101</v>
+        <v>-625.8836958606219</v>
       </c>
       <c r="D75">
-        <v>355.3052817414898</v>
+        <v>351.1723041393782</v>
       </c>
       <c r="E75">
-        <v>896.212</v>
+        <v>910.2560000000001</v>
       </c>
       <c r="F75">
-        <v>1025.212</v>
+        <v>1039.256</v>
       </c>
       <c r="G75">
         <v>62.2</v>
@@ -7437,37 +7437,37 @@
         <v>76.7</v>
       </c>
       <c r="M75">
-        <v>241.7449896</v>
+        <v>245.0565648</v>
       </c>
       <c r="N75">
-        <v>-165.0449896</v>
+        <v>-168.3565648</v>
       </c>
       <c r="O75">
-        <v>-52.814396672</v>
+        <v>-53.874100736</v>
       </c>
       <c r="P75">
-        <v>-112.230592928</v>
+        <v>-114.482464064</v>
       </c>
       <c r="Q75">
-        <v>-73.93059292800001</v>
+        <v>-76.182464064</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1947495374026057</v>
+        <v>0.2004783657642444</v>
       </c>
       <c r="T75">
-        <v>1.941311796107949</v>
+        <v>2.015977634419793</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1015284744499209</v>
+        <v>0.1001564680384355</v>
       </c>
       <c r="W75">
-        <v>0.2118595857247086</v>
+        <v>0.2121831048365369</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3172764826560028</v>
+        <v>0.312988962620111</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2091398726777409</v>
+        <v>0.2110398726777409</v>
       </c>
       <c r="C76">
-        <v>-625.8836958606219</v>
+        <v>-643.9656279108727</v>
       </c>
       <c r="D76">
-        <v>351.1723041393782</v>
+        <v>347.1343720891275</v>
       </c>
       <c r="E76">
-        <v>910.2560000000001</v>
+        <v>924.3000000000002</v>
       </c>
       <c r="F76">
-        <v>1039.256</v>
+        <v>1053.3</v>
       </c>
       <c r="G76">
         <v>62.2</v>
@@ -7519,37 +7519,37 @@
         <v>76.7</v>
       </c>
       <c r="M76">
-        <v>245.0565648</v>
+        <v>248.36814</v>
       </c>
       <c r="N76">
-        <v>-168.3565648</v>
+        <v>-171.6681400000001</v>
       </c>
       <c r="O76">
-        <v>-53.874100736</v>
+        <v>-54.93380480000002</v>
       </c>
       <c r="P76">
-        <v>-114.482464064</v>
+        <v>-116.7343352</v>
       </c>
       <c r="Q76">
-        <v>-76.182464064</v>
+        <v>-78.43433520000004</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2004783657642444</v>
+        <v>0.2066655003948142</v>
       </c>
       <c r="T76">
-        <v>2.015977634419793</v>
+        <v>2.096616739796585</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1001564680384355</v>
+        <v>0.09882104846458969</v>
       </c>
       <c r="W76">
-        <v>0.2121831048365369</v>
+        <v>0.2124979967720498</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.312988962620111</v>
+        <v>0.3088157764518428</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2110398726777409</v>
+        <v>0.2129398726777409</v>
       </c>
       <c r="C77">
-        <v>-643.9656279108727</v>
+        <v>-661.9557557641648</v>
       </c>
       <c r="D77">
-        <v>347.1343720891275</v>
+        <v>343.1882442358353</v>
       </c>
       <c r="E77">
-        <v>924.3000000000002</v>
+        <v>938.3440000000001</v>
       </c>
       <c r="F77">
-        <v>1053.3</v>
+        <v>1067.344</v>
       </c>
       <c r="G77">
         <v>62.2</v>
@@ -7601,37 +7601,37 @@
         <v>76.7</v>
       </c>
       <c r="M77">
-        <v>248.36814</v>
+        <v>251.6797152</v>
       </c>
       <c r="N77">
-        <v>-171.6681400000001</v>
+        <v>-174.9797152</v>
       </c>
       <c r="O77">
-        <v>-54.93380480000002</v>
+        <v>-55.99350886400001</v>
       </c>
       <c r="P77">
-        <v>-116.7343352</v>
+        <v>-118.986206336</v>
       </c>
       <c r="Q77">
-        <v>-78.43433520000004</v>
+        <v>-80.68620633600004</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2066655003948142</v>
+        <v>0.2133682295779314</v>
       </c>
       <c r="T77">
-        <v>2.096616739796585</v>
+        <v>2.183975770621443</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.09882104846458969</v>
+        <v>0.09752077151110826</v>
       </c>
       <c r="W77">
-        <v>0.2124979967720498</v>
+        <v>0.2128046020776807</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3088157764518428</v>
+        <v>0.3047524109722132</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2129398726777409</v>
+        <v>0.2148398726777409</v>
       </c>
       <c r="C78">
-        <v>-661.9557557641648</v>
+        <v>-679.8571750447104</v>
       </c>
       <c r="D78">
-        <v>343.1882442358353</v>
+        <v>339.3308249552898</v>
       </c>
       <c r="E78">
-        <v>938.3440000000001</v>
+        <v>952.3880000000001</v>
       </c>
       <c r="F78">
-        <v>1067.344</v>
+        <v>1081.388</v>
       </c>
       <c r="G78">
         <v>62.2</v>
@@ -7683,37 +7683,37 @@
         <v>76.7</v>
       </c>
       <c r="M78">
-        <v>251.6797152</v>
+        <v>254.9912904000001</v>
       </c>
       <c r="N78">
-        <v>-174.9797152</v>
+        <v>-178.2912904</v>
       </c>
       <c r="O78">
-        <v>-55.99350886400001</v>
+        <v>-57.05321292800001</v>
       </c>
       <c r="P78">
-        <v>-118.986206336</v>
+        <v>-121.238077472</v>
       </c>
       <c r="Q78">
-        <v>-80.68620633600004</v>
+        <v>-82.93807747200002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2133682295779314</v>
+        <v>0.2206538047769719</v>
       </c>
       <c r="T78">
-        <v>2.183975770621443</v>
+        <v>2.278931238909332</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.09752077151110826</v>
+        <v>0.09625426798498996</v>
       </c>
       <c r="W78">
-        <v>0.2128046020776807</v>
+        <v>0.2131032436091394</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3047524109722132</v>
+        <v>0.3007945874530936</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2148398726777409</v>
+        <v>0.2167398726777409</v>
       </c>
       <c r="C79">
-        <v>-679.8571750447104</v>
+        <v>-697.6728437450288</v>
       </c>
       <c r="D79">
-        <v>339.3308249552898</v>
+        <v>335.5591562549712</v>
       </c>
       <c r="E79">
-        <v>952.3880000000001</v>
+        <v>966.432</v>
       </c>
       <c r="F79">
-        <v>1081.388</v>
+        <v>1095.432</v>
       </c>
       <c r="G79">
         <v>62.2</v>
@@ -7765,37 +7765,37 @@
         <v>76.7</v>
       </c>
       <c r="M79">
-        <v>254.9912904000001</v>
+        <v>258.3028656</v>
       </c>
       <c r="N79">
-        <v>-178.2912904</v>
+        <v>-181.6028656</v>
       </c>
       <c r="O79">
-        <v>-57.05321292800001</v>
+        <v>-58.11291699200001</v>
       </c>
       <c r="P79">
-        <v>-121.238077472</v>
+        <v>-123.489948608</v>
       </c>
       <c r="Q79">
-        <v>-82.93807747200002</v>
+        <v>-85.18994860800002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2206538047769719</v>
+        <v>0.228601704994107</v>
       </c>
       <c r="T79">
-        <v>2.278931238909332</v>
+        <v>2.38251902249612</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.09625426798498996</v>
+        <v>0.09502023890825934</v>
       </c>
       <c r="W79">
-        <v>0.2131032436091394</v>
+        <v>0.2133942276654325</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3007945874530936</v>
+        <v>0.2969382465883104</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2167398726777409</v>
+        <v>0.2186398726777408</v>
       </c>
       <c r="C80">
-        <v>-697.6728437450288</v>
+        <v>-715.4055897907588</v>
       </c>
       <c r="D80">
-        <v>335.5591562549712</v>
+        <v>331.8704102092414</v>
       </c>
       <c r="E80">
-        <v>966.432</v>
+        <v>980.4760000000001</v>
       </c>
       <c r="F80">
-        <v>1095.432</v>
+        <v>1109.476</v>
       </c>
       <c r="G80">
         <v>62.2</v>
@@ -7847,37 +7847,37 @@
         <v>76.7</v>
       </c>
       <c r="M80">
-        <v>258.3028656</v>
+        <v>261.6144408</v>
       </c>
       <c r="N80">
-        <v>-181.6028656</v>
+        <v>-184.9144408</v>
       </c>
       <c r="O80">
-        <v>-58.11291699200001</v>
+        <v>-59.17262105600001</v>
       </c>
       <c r="P80">
-        <v>-123.489948608</v>
+        <v>-125.741819744</v>
       </c>
       <c r="Q80">
-        <v>-85.18994860800002</v>
+        <v>-87.44181974400001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.228601704994107</v>
+        <v>0.2373065480890645</v>
       </c>
       <c r="T80">
-        <v>2.38251902249612</v>
+        <v>2.495972309281649</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.09502023890825934</v>
+        <v>0.09381745107397757</v>
       </c>
       <c r="W80">
-        <v>0.2133942276654325</v>
+        <v>0.2136778450367561</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2969382465883104</v>
+        <v>0.2931795346061798</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2186398726777408</v>
+        <v>0.2205398726777408</v>
       </c>
       <c r="C81">
-        <v>-715.4055897907588</v>
+        <v>-733.0581181119416</v>
       </c>
       <c r="D81">
-        <v>331.8704102092414</v>
+        <v>328.2618818880587</v>
       </c>
       <c r="E81">
-        <v>980.4760000000001</v>
+        <v>994.5200000000002</v>
       </c>
       <c r="F81">
-        <v>1109.476</v>
+        <v>1123.52</v>
       </c>
       <c r="G81">
         <v>62.2</v>
@@ -7929,37 +7929,37 @@
         <v>76.7</v>
       </c>
       <c r="M81">
-        <v>261.6144408</v>
+        <v>264.9260160000001</v>
       </c>
       <c r="N81">
-        <v>-184.9144408</v>
+        <v>-188.2260160000001</v>
       </c>
       <c r="O81">
-        <v>-59.17262105600001</v>
+        <v>-60.23232512000003</v>
       </c>
       <c r="P81">
-        <v>-125.741819744</v>
+        <v>-127.99369088</v>
       </c>
       <c r="Q81">
-        <v>-87.44181974400001</v>
+        <v>-89.69369088000005</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2373065480890645</v>
+        <v>0.2468818754935177</v>
       </c>
       <c r="T81">
-        <v>2.495972309281649</v>
+        <v>2.620770924745732</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.09381745107397757</v>
+        <v>0.09264473293555282</v>
       </c>
       <c r="W81">
-        <v>0.2136778450367561</v>
+        <v>0.2139543719737966</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2931795346061798</v>
+        <v>0.2895147904236025</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2205398726777408</v>
+        <v>0.2224398726777408</v>
       </c>
       <c r="C82">
-        <v>-733.0581181119416</v>
+        <v>-750.6330172579412</v>
       </c>
       <c r="D82">
-        <v>328.2618818880587</v>
+        <v>324.7309827420589</v>
       </c>
       <c r="E82">
-        <v>994.5200000000002</v>
+        <v>1008.564</v>
       </c>
       <c r="F82">
-        <v>1123.52</v>
+        <v>1137.564</v>
       </c>
       <c r="G82">
         <v>62.2</v>
@@ -8011,37 +8011,37 @@
         <v>76.7</v>
       </c>
       <c r="M82">
-        <v>264.9260160000001</v>
+        <v>268.2375912000001</v>
       </c>
       <c r="N82">
-        <v>-188.2260160000001</v>
+        <v>-191.5375912000001</v>
       </c>
       <c r="O82">
-        <v>-60.23232512000003</v>
+        <v>-61.29202918400002</v>
       </c>
       <c r="P82">
-        <v>-127.99369088</v>
+        <v>-130.245562016</v>
       </c>
       <c r="Q82">
-        <v>-89.69369088000005</v>
+        <v>-91.94556201600004</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2468818754935177</v>
+        <v>0.2574651320984397</v>
       </c>
       <c r="T82">
-        <v>2.620770924745732</v>
+        <v>2.758706236574455</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.09264473293555282</v>
+        <v>0.09150097080054601</v>
       </c>
       <c r="W82">
-        <v>0.2139543719737966</v>
+        <v>0.2142240710852313</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2895147904236025</v>
+        <v>0.2859405337517062</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2224398726777408</v>
+        <v>0.2243398726777408</v>
       </c>
       <c r="C83">
-        <v>-750.6330172579412</v>
+        <v>-768.132765589988</v>
       </c>
       <c r="D83">
-        <v>324.7309827420589</v>
+        <v>321.2752344100122</v>
       </c>
       <c r="E83">
-        <v>1008.564</v>
+        <v>1022.608</v>
       </c>
       <c r="F83">
-        <v>1137.564</v>
+        <v>1151.608</v>
       </c>
       <c r="G83">
         <v>62.2</v>
@@ -8093,37 +8093,37 @@
         <v>76.7</v>
       </c>
       <c r="M83">
-        <v>268.2375912000001</v>
+        <v>271.5491664</v>
       </c>
       <c r="N83">
-        <v>-191.5375912000001</v>
+        <v>-194.8491664000001</v>
       </c>
       <c r="O83">
-        <v>-61.29202918400002</v>
+        <v>-62.35173324800002</v>
       </c>
       <c r="P83">
-        <v>-130.245562016</v>
+        <v>-132.497433152</v>
       </c>
       <c r="Q83">
-        <v>-91.94556201600004</v>
+        <v>-94.19743315200004</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2574651320984397</v>
+        <v>0.2692243061039086</v>
       </c>
       <c r="T83">
-        <v>2.758706236574455</v>
+        <v>2.911967694161925</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.09150097080054601</v>
+        <v>0.09038510530297839</v>
       </c>
       <c r="W83">
-        <v>0.2142240710852313</v>
+        <v>0.2144871921695577</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2859405337517062</v>
+        <v>0.2824534540718073</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2243398726777408</v>
+        <v>0.2262398726777409</v>
       </c>
       <c r="C84">
-        <v>-768.132765589988</v>
+        <v>-785.5597370824873</v>
       </c>
       <c r="D84">
-        <v>321.2752344100122</v>
+        <v>317.8922629175129</v>
       </c>
       <c r="E84">
-        <v>1022.608</v>
+        <v>1036.652</v>
       </c>
       <c r="F84">
-        <v>1151.608</v>
+        <v>1165.652</v>
       </c>
       <c r="G84">
         <v>62.2</v>
@@ -8175,37 +8175,37 @@
         <v>76.7</v>
       </c>
       <c r="M84">
-        <v>271.5491664</v>
+        <v>274.8607416000001</v>
       </c>
       <c r="N84">
-        <v>-194.8491664000001</v>
+        <v>-198.1607416000001</v>
       </c>
       <c r="O84">
-        <v>-62.35173324800002</v>
+        <v>-63.41143731200004</v>
       </c>
       <c r="P84">
-        <v>-132.497433152</v>
+        <v>-134.7493042880001</v>
       </c>
       <c r="Q84">
-        <v>-94.19743315200004</v>
+        <v>-96.44930428800008</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2692243061039086</v>
+        <v>0.282366912345315</v>
       </c>
       <c r="T84">
-        <v>2.911967694161925</v>
+        <v>3.083259911465568</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.09038510530297839</v>
+        <v>0.08929612813065331</v>
       </c>
       <c r="W84">
-        <v>0.2144871921695577</v>
+        <v>0.214743972986792</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2824534540718073</v>
+        <v>0.2790504004082915</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2262398726777409</v>
+        <v>0.2281398726777409</v>
       </c>
       <c r="C85">
-        <v>-785.5597370824873</v>
+        <v>-802.9162067616272</v>
       </c>
       <c r="D85">
-        <v>317.8922629175129</v>
+        <v>314.5797932383729</v>
       </c>
       <c r="E85">
-        <v>1036.652</v>
+        <v>1050.696</v>
       </c>
       <c r="F85">
-        <v>1165.652</v>
+        <v>1179.696</v>
       </c>
       <c r="G85">
         <v>62.2</v>
@@ -8257,37 +8257,37 @@
         <v>76.7</v>
       </c>
       <c r="M85">
-        <v>274.8607416000001</v>
+        <v>278.1723168</v>
       </c>
       <c r="N85">
-        <v>-198.1607416000001</v>
+        <v>-201.4723168</v>
       </c>
       <c r="O85">
-        <v>-63.41143731200004</v>
+        <v>-64.47114137600002</v>
       </c>
       <c r="P85">
-        <v>-134.7493042880001</v>
+        <v>-137.001175424</v>
       </c>
       <c r="Q85">
-        <v>-96.44930428800008</v>
+        <v>-98.70117542400003</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.282366912345315</v>
+        <v>0.2971523443668972</v>
       </c>
       <c r="T85">
-        <v>3.083259911465568</v>
+        <v>3.275963655932166</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08929612813065331</v>
+        <v>0.0882330789862408</v>
       </c>
       <c r="W85">
-        <v>0.214743972986792</v>
+        <v>0.2149946399750444</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2790504004082915</v>
+        <v>0.2757283718320025</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2281398726777409</v>
+        <v>0.2300398726777408</v>
       </c>
       <c r="C86">
-        <v>-802.9162067616273</v>
+        <v>-820.2043558074657</v>
       </c>
       <c r="D86">
-        <v>314.5797932383728</v>
+        <v>311.3356441925343</v>
       </c>
       <c r="E86">
-        <v>1050.696</v>
+        <v>1064.74</v>
       </c>
       <c r="F86">
-        <v>1179.696</v>
+        <v>1193.74</v>
       </c>
       <c r="G86">
         <v>62.2</v>
@@ -8339,37 +8339,37 @@
         <v>76.7</v>
       </c>
       <c r="M86">
-        <v>278.1723168</v>
+        <v>281.483892</v>
       </c>
       <c r="N86">
-        <v>-201.4723168</v>
+        <v>-204.783892</v>
       </c>
       <c r="O86">
-        <v>-64.47114137600002</v>
+        <v>-65.53084544000001</v>
       </c>
       <c r="P86">
-        <v>-137.001175424</v>
+        <v>-139.25304656</v>
       </c>
       <c r="Q86">
-        <v>-98.70117542400003</v>
+        <v>-100.95304656</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2971523443668971</v>
+        <v>0.3139091673246902</v>
       </c>
       <c r="T86">
-        <v>3.275963655932165</v>
+        <v>3.494361232994308</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0882330789862408</v>
+        <v>0.08719504276287326</v>
       </c>
       <c r="W86">
-        <v>0.2149946399750444</v>
+        <v>0.2152394089165145</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2757283718320025</v>
+        <v>0.2724845086339789</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2300398726777408</v>
+        <v>0.2319398726777409</v>
       </c>
       <c r="C87">
-        <v>-820.2043558074657</v>
+        <v>-837.4262763435452</v>
       </c>
       <c r="D87">
-        <v>311.3356441925343</v>
+        <v>308.1577236564549</v>
       </c>
       <c r="E87">
-        <v>1064.74</v>
+        <v>1078.784</v>
       </c>
       <c r="F87">
-        <v>1193.74</v>
+        <v>1207.784</v>
       </c>
       <c r="G87">
         <v>62.2</v>
@@ -8421,37 +8421,37 @@
         <v>76.7</v>
       </c>
       <c r="M87">
-        <v>281.483892</v>
+        <v>284.7954672</v>
       </c>
       <c r="N87">
-        <v>-204.783892</v>
+        <v>-208.0954672</v>
       </c>
       <c r="O87">
-        <v>-65.53084544000001</v>
+        <v>-66.59054950400001</v>
       </c>
       <c r="P87">
-        <v>-139.25304656</v>
+        <v>-141.504917696</v>
       </c>
       <c r="Q87">
-        <v>-100.95304656</v>
+        <v>-103.204917696</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3139091673246902</v>
+        <v>0.3330598221335966</v>
       </c>
       <c r="T87">
-        <v>3.494361232994308</v>
+        <v>3.743958463922473</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08719504276287326</v>
+        <v>0.08618114691679335</v>
       </c>
       <c r="W87">
-        <v>0.2152394089165145</v>
+        <v>0.2154784855570201</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2724845086339789</v>
+        <v>0.2693160841149791</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2319398726777409</v>
+        <v>0.2338398726777409</v>
       </c>
       <c r="C88">
-        <v>-837.4262763435452</v>
+        <v>-854.5839759361347</v>
       </c>
       <c r="D88">
-        <v>308.1577236564549</v>
+        <v>305.0440240638653</v>
       </c>
       <c r="E88">
-        <v>1078.784</v>
+        <v>1092.828</v>
       </c>
       <c r="F88">
-        <v>1207.784</v>
+        <v>1221.828</v>
       </c>
       <c r="G88">
         <v>62.2</v>
@@ -8503,37 +8503,37 @@
         <v>76.7</v>
       </c>
       <c r="M88">
-        <v>284.7954672</v>
+        <v>288.1070424</v>
       </c>
       <c r="N88">
-        <v>-208.0954672</v>
+        <v>-211.4070424</v>
       </c>
       <c r="O88">
-        <v>-66.59054950400001</v>
+        <v>-67.65025356800001</v>
       </c>
       <c r="P88">
-        <v>-141.504917696</v>
+        <v>-143.756788832</v>
       </c>
       <c r="Q88">
-        <v>-103.204917696</v>
+        <v>-105.456788832</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3330598221335966</v>
+        <v>0.3551567315284888</v>
       </c>
       <c r="T88">
-        <v>3.743958463922473</v>
+        <v>4.031955268839587</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08618114691679335</v>
+        <v>0.08519055902119803</v>
       </c>
       <c r="W88">
-        <v>0.2154784855570201</v>
+        <v>0.2157120661828015</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2693160841149791</v>
+        <v>0.2662204969412437</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2338398726777409</v>
+        <v>0.2357398726777409</v>
       </c>
       <c r="C89">
-        <v>-854.5839759361347</v>
+        <v>-871.6793818234321</v>
       </c>
       <c r="D89">
-        <v>305.0440240638653</v>
+        <v>301.992618176568</v>
       </c>
       <c r="E89">
-        <v>1092.828</v>
+        <v>1106.872</v>
       </c>
       <c r="F89">
-        <v>1221.828</v>
+        <v>1235.872</v>
       </c>
       <c r="G89">
         <v>62.2</v>
@@ -8585,37 +8585,37 @@
         <v>76.7</v>
       </c>
       <c r="M89">
-        <v>288.1070424</v>
+        <v>291.4186176</v>
       </c>
       <c r="N89">
-        <v>-211.4070424</v>
+        <v>-214.7186176</v>
       </c>
       <c r="O89">
-        <v>-67.65025356800001</v>
+        <v>-68.70995763200001</v>
       </c>
       <c r="P89">
-        <v>-143.756788832</v>
+        <v>-146.008659968</v>
       </c>
       <c r="Q89">
-        <v>-105.456788832</v>
+        <v>-107.708659968</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3551567315284888</v>
+        <v>0.3809364591558628</v>
       </c>
       <c r="T89">
-        <v>4.031955268839587</v>
+        <v>4.367951541242887</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08519055902119803</v>
+        <v>0.08422248448686621</v>
       </c>
       <c r="W89">
-        <v>0.2157120661828015</v>
+        <v>0.215940338157997</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2662204969412437</v>
+        <v>0.2631952640214569</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2357398726777409</v>
+        <v>0.2376398726777408</v>
       </c>
       <c r="C90">
-        <v>-871.6793818234321</v>
+        <v>-888.7143448934469</v>
       </c>
       <c r="D90">
-        <v>301.992618176568</v>
+        <v>299.0016551065533</v>
       </c>
       <c r="E90">
-        <v>1106.872</v>
+        <v>1120.916</v>
       </c>
       <c r="F90">
-        <v>1235.872</v>
+        <v>1249.916</v>
       </c>
       <c r="G90">
         <v>62.2</v>
@@ -8667,37 +8667,37 @@
         <v>76.7</v>
       </c>
       <c r="M90">
-        <v>291.4186176</v>
+        <v>294.7301928000001</v>
       </c>
       <c r="N90">
-        <v>-214.7186176</v>
+        <v>-218.0301928000001</v>
       </c>
       <c r="O90">
-        <v>-68.70995763200001</v>
+        <v>-69.76966169600003</v>
       </c>
       <c r="P90">
-        <v>-146.008659968</v>
+        <v>-148.2605311040001</v>
       </c>
       <c r="Q90">
-        <v>-107.708659968</v>
+        <v>-109.9605311040001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3809364591558628</v>
+        <v>0.411403409988214</v>
       </c>
       <c r="T90">
-        <v>4.367951541242887</v>
+        <v>4.765038044992239</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08422248448686621</v>
+        <v>0.08327616443645199</v>
       </c>
       <c r="W90">
-        <v>0.215940338157997</v>
+        <v>0.2161634804258846</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2631952640214569</v>
+        <v>0.2602380138639124</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2376398726777408</v>
+        <v>0.2395398726777409</v>
       </c>
       <c r="C91">
-        <v>-888.7143448934469</v>
+        <v>-905.6906434278194</v>
       </c>
       <c r="D91">
-        <v>299.0016551065533</v>
+        <v>296.0693565721806</v>
       </c>
       <c r="E91">
-        <v>1120.916</v>
+        <v>1134.96</v>
       </c>
       <c r="F91">
-        <v>1249.916</v>
+        <v>1263.96</v>
       </c>
       <c r="G91">
         <v>62.2</v>
@@ -8749,37 +8749,37 @@
         <v>76.7</v>
       </c>
       <c r="M91">
-        <v>294.7301928000001</v>
+        <v>298.041768</v>
       </c>
       <c r="N91">
-        <v>-218.0301928000001</v>
+        <v>-221.3417680000001</v>
       </c>
       <c r="O91">
-        <v>-69.76966169600003</v>
+        <v>-70.82936576000002</v>
       </c>
       <c r="P91">
-        <v>-148.2605311040001</v>
+        <v>-150.51240224</v>
       </c>
       <c r="Q91">
-        <v>-109.9605311040001</v>
+        <v>-112.21240224</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.411403409988214</v>
+        <v>0.4479637509870354</v>
       </c>
       <c r="T91">
-        <v>4.765038044992239</v>
+        <v>5.241541849491465</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08327616443645199</v>
+        <v>0.08235087372049141</v>
       </c>
       <c r="W91">
-        <v>0.2161634804258846</v>
+        <v>0.2163816639767081</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2602380138639124</v>
+        <v>0.2573464803765356</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2395398726777409</v>
+        <v>0.2414398726777409</v>
       </c>
       <c r="C92">
-        <v>-905.6906434278194</v>
+        <v>-922.6099866274837</v>
       </c>
       <c r="D92">
-        <v>296.0693565721806</v>
+        <v>293.1940133725165</v>
       </c>
       <c r="E92">
-        <v>1134.96</v>
+        <v>1149.004</v>
       </c>
       <c r="F92">
-        <v>1263.96</v>
+        <v>1278.004</v>
       </c>
       <c r="G92">
         <v>62.2</v>
@@ -8831,37 +8831,37 @@
         <v>76.7</v>
       </c>
       <c r="M92">
-        <v>298.041768</v>
+        <v>301.3533432</v>
       </c>
       <c r="N92">
-        <v>-221.3417680000001</v>
+        <v>-224.6533432000001</v>
       </c>
       <c r="O92">
-        <v>-70.82936576000002</v>
+        <v>-71.88906982400002</v>
       </c>
       <c r="P92">
-        <v>-150.51240224</v>
+        <v>-152.764273376</v>
       </c>
       <c r="Q92">
-        <v>-112.21240224</v>
+        <v>-114.464273376</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4479637509870354</v>
+        <v>0.4926486122078172</v>
       </c>
       <c r="T92">
-        <v>5.241541849491465</v>
+        <v>5.82393538832385</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.08235087372049141</v>
+        <v>0.08144591906422229</v>
       </c>
       <c r="W92">
-        <v>0.2163816639767081</v>
+        <v>0.2165950522846564</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2573464803765356</v>
+        <v>0.2545184970756945</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2414398726777409</v>
+        <v>0.2433398726777409</v>
       </c>
       <c r="C93">
-        <v>-922.6099866274837</v>
+        <v>-939.4740179348673</v>
       </c>
       <c r="D93">
-        <v>293.1940133725165</v>
+        <v>290.3739820651329</v>
       </c>
       <c r="E93">
-        <v>1149.004</v>
+        <v>1163.048</v>
       </c>
       <c r="F93">
-        <v>1278.004</v>
+        <v>1292.048</v>
       </c>
       <c r="G93">
         <v>62.2</v>
@@ -8913,37 +8913,37 @@
         <v>76.7</v>
       </c>
       <c r="M93">
-        <v>301.3533432</v>
+        <v>304.6649184000001</v>
       </c>
       <c r="N93">
-        <v>-224.6533432000001</v>
+        <v>-227.9649184000001</v>
       </c>
       <c r="O93">
-        <v>-71.88906982400002</v>
+        <v>-72.94877388800003</v>
       </c>
       <c r="P93">
-        <v>-152.764273376</v>
+        <v>-155.0161445120001</v>
       </c>
       <c r="Q93">
-        <v>-114.464273376</v>
+        <v>-116.7161445120001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4926486122078172</v>
+        <v>0.5485046887337944</v>
       </c>
       <c r="T93">
-        <v>5.82393538832385</v>
+        <v>6.551927311864333</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08144591906422229</v>
+        <v>0.08056063733526334</v>
       </c>
       <c r="W93">
-        <v>0.2165950522846564</v>
+        <v>0.2168038017163449</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2545184970756945</v>
+        <v>0.2517519916726978</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2433398726777409</v>
+        <v>0.2452398726777409</v>
       </c>
       <c r="C94">
-        <v>-939.4740179348673</v>
+        <v>-956.2843181661917</v>
       </c>
       <c r="D94">
-        <v>290.3739820651329</v>
+        <v>287.6076818338083</v>
       </c>
       <c r="E94">
-        <v>1163.048</v>
+        <v>1177.092</v>
       </c>
       <c r="F94">
-        <v>1292.048</v>
+        <v>1306.092</v>
       </c>
       <c r="G94">
         <v>62.2</v>
@@ -8995,37 +8995,37 @@
         <v>76.7</v>
       </c>
       <c r="M94">
-        <v>304.6649184000001</v>
+        <v>307.9764936</v>
       </c>
       <c r="N94">
-        <v>-227.9649184000001</v>
+        <v>-231.2764936</v>
       </c>
       <c r="O94">
-        <v>-72.94877388800003</v>
+        <v>-74.00847795200001</v>
       </c>
       <c r="P94">
-        <v>-155.0161445120001</v>
+        <v>-157.268015648</v>
       </c>
       <c r="Q94">
-        <v>-116.7161445120001</v>
+        <v>-118.968015648</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5485046887337944</v>
+        <v>0.6203196442671937</v>
       </c>
       <c r="T94">
-        <v>6.551927311864333</v>
+        <v>7.487916927844952</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08056063733526334</v>
+        <v>0.0796943939230562</v>
       </c>
       <c r="W94">
-        <v>0.2168038017163449</v>
+        <v>0.2170080619129434</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2517519916726978</v>
+        <v>0.2490449810095506</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2452398726777409</v>
+        <v>0.2471398726777408</v>
       </c>
       <c r="C95">
-        <v>-956.2843181661917</v>
+        <v>-973.042408466422</v>
       </c>
       <c r="D95">
-        <v>287.6076818338083</v>
+        <v>284.8935915335782</v>
       </c>
       <c r="E95">
-        <v>1177.092</v>
+        <v>1191.136</v>
       </c>
       <c r="F95">
-        <v>1306.092</v>
+        <v>1320.136</v>
       </c>
       <c r="G95">
         <v>62.2</v>
@@ -9077,37 +9077,37 @@
         <v>76.7</v>
       </c>
       <c r="M95">
-        <v>307.9764936</v>
+        <v>311.2880688000001</v>
       </c>
       <c r="N95">
-        <v>-231.2764936</v>
+        <v>-234.5880688000001</v>
       </c>
       <c r="O95">
-        <v>-74.00847795200001</v>
+        <v>-75.06818201600002</v>
       </c>
       <c r="P95">
-        <v>-157.268015648</v>
+        <v>-159.5198867840001</v>
       </c>
       <c r="Q95">
-        <v>-118.968015648</v>
+        <v>-121.2198867840001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6203196442671937</v>
+        <v>0.7160729183117261</v>
       </c>
       <c r="T95">
-        <v>7.487916927844952</v>
+        <v>8.73590308248578</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.0796943939230562</v>
+        <v>0.07884658122174709</v>
       </c>
       <c r="W95">
-        <v>0.2170080619129434</v>
+        <v>0.217207976147912</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2490449810095506</v>
+        <v>0.2463955663179596</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2471398726777408</v>
+        <v>0.2490398726777409</v>
       </c>
       <c r="C96">
-        <v>-973.042408466422</v>
+        <v>-989.7497530984672</v>
       </c>
       <c r="D96">
-        <v>284.8935915335782</v>
+        <v>282.2302469015331</v>
       </c>
       <c r="E96">
-        <v>1191.136</v>
+        <v>1205.18</v>
       </c>
       <c r="F96">
-        <v>1320.136</v>
+        <v>1334.18</v>
       </c>
       <c r="G96">
         <v>62.2</v>
@@ -9159,37 +9159,37 @@
         <v>76.7</v>
       </c>
       <c r="M96">
-        <v>311.2880688000001</v>
+        <v>314.5996440000001</v>
       </c>
       <c r="N96">
-        <v>-234.5880688000001</v>
+        <v>-237.8996440000001</v>
       </c>
       <c r="O96">
-        <v>-75.06818201600002</v>
+        <v>-76.12788608000002</v>
       </c>
       <c r="P96">
-        <v>-159.5198867840001</v>
+        <v>-161.7717579200001</v>
       </c>
       <c r="Q96">
-        <v>-121.2198867840001</v>
+        <v>-123.4717579200001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7160729183117261</v>
+        <v>0.8501275019740717</v>
       </c>
       <c r="T96">
-        <v>8.73590308248578</v>
+        <v>10.48308369898294</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07884658122174709</v>
+        <v>0.0780166172088866</v>
       </c>
       <c r="W96">
-        <v>0.217207976147912</v>
+        <v>0.2174036816621445</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2463955663179596</v>
+        <v>0.2438019287777705</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2490398726777409</v>
+        <v>0.2509398726777409</v>
       </c>
       <c r="C97">
-        <v>-989.7497530984672</v>
+        <v>-1006.407762077381</v>
       </c>
       <c r="D97">
-        <v>282.2302469015331</v>
+        <v>279.616237922619</v>
       </c>
       <c r="E97">
-        <v>1205.18</v>
+        <v>1219.224</v>
       </c>
       <c r="F97">
-        <v>1334.18</v>
+        <v>1348.224</v>
       </c>
       <c r="G97">
         <v>62.2</v>
@@ -9241,37 +9241,37 @@
         <v>76.7</v>
       </c>
       <c r="M97">
-        <v>314.5996440000001</v>
+        <v>317.9112192000001</v>
       </c>
       <c r="N97">
-        <v>-237.8996440000001</v>
+        <v>-241.2112192000001</v>
       </c>
       <c r="O97">
-        <v>-76.12788608000002</v>
+        <v>-77.18759014400003</v>
       </c>
       <c r="P97">
-        <v>-161.7717579200001</v>
+        <v>-164.0236290560001</v>
       </c>
       <c r="Q97">
-        <v>-123.4717579200001</v>
+        <v>-125.7236290560001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8501275019740717</v>
+        <v>1.05120937746759</v>
       </c>
       <c r="T97">
-        <v>10.48308369898294</v>
+        <v>13.10385462372868</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0780166172088866</v>
+        <v>0.07720394411296069</v>
       </c>
       <c r="W97">
-        <v>0.2174036816621445</v>
+        <v>0.2175953099781639</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2438019287777705</v>
+        <v>0.2412623253530021</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2509398726777409</v>
+        <v>0.2528398726777408</v>
       </c>
       <c r="C98">
-        <v>-1006.407762077381</v>
+        <v>-1023.017793659519</v>
       </c>
       <c r="D98">
-        <v>279.616237922619</v>
+        <v>277.0502063404807</v>
       </c>
       <c r="E98">
-        <v>1219.224</v>
+        <v>1233.268</v>
       </c>
       <c r="F98">
-        <v>1348.224</v>
+        <v>1362.268</v>
       </c>
       <c r="G98">
         <v>62.2</v>
@@ -9323,37 +9323,37 @@
         <v>76.7</v>
       </c>
       <c r="M98">
-        <v>317.9112192</v>
+        <v>321.2227944</v>
       </c>
       <c r="N98">
-        <v>-241.2112192</v>
+        <v>-244.5227944</v>
       </c>
       <c r="O98">
-        <v>-77.18759014400001</v>
+        <v>-78.247294208</v>
       </c>
       <c r="P98">
-        <v>-164.023629056</v>
+        <v>-166.275500192</v>
       </c>
       <c r="Q98">
-        <v>-125.723629056</v>
+        <v>-127.975500192</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.051209377467588</v>
+        <v>1.38634583662345</v>
       </c>
       <c r="T98">
-        <v>13.10385462372865</v>
+        <v>17.47180616497153</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07720394411296071</v>
+        <v>0.07640802716334257</v>
       </c>
       <c r="W98">
-        <v>0.2175953099781639</v>
+        <v>0.2177829871948838</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2412623253530022</v>
+        <v>0.2387750848854454</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2528398726777408</v>
+        <v>0.2547398726777408</v>
       </c>
       <c r="C99">
-        <v>-1023.017793659519</v>
+        <v>-1039.581156695883</v>
       </c>
       <c r="D99">
-        <v>277.0502063404807</v>
+        <v>274.5308433041167</v>
       </c>
       <c r="E99">
-        <v>1233.268</v>
+        <v>1247.312</v>
       </c>
       <c r="F99">
-        <v>1362.268</v>
+        <v>1376.312</v>
       </c>
       <c r="G99">
         <v>62.2</v>
@@ -9405,37 +9405,37 @@
         <v>76.7</v>
       </c>
       <c r="M99">
-        <v>321.2227944</v>
+        <v>324.5343696</v>
       </c>
       <c r="N99">
-        <v>-244.5227944</v>
+        <v>-247.8343696000001</v>
       </c>
       <c r="O99">
-        <v>-78.247294208</v>
+        <v>-79.30699827200002</v>
       </c>
       <c r="P99">
-        <v>-166.275500192</v>
+        <v>-168.527371328</v>
       </c>
       <c r="Q99">
-        <v>-127.975500192</v>
+        <v>-130.2273713280001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.38634583662345</v>
+        <v>2.056618754935175</v>
       </c>
       <c r="T99">
-        <v>17.47180616497153</v>
+        <v>26.2077092474573</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07640802716334257</v>
+        <v>0.07562835341677783</v>
       </c>
       <c r="W99">
-        <v>0.2177829871948838</v>
+        <v>0.2179668342643238</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2387750848854454</v>
+        <v>0.2363386044274307</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2547398726777408</v>
+        <v>0.2566398726777409</v>
       </c>
       <c r="C100">
-        <v>-1039.581156695883</v>
+        <v>-1056.099112858222</v>
       </c>
       <c r="D100">
-        <v>274.5308433041167</v>
+        <v>272.0568871417778</v>
       </c>
       <c r="E100">
-        <v>1247.312</v>
+        <v>1261.356</v>
       </c>
       <c r="F100">
-        <v>1376.312</v>
+        <v>1390.356</v>
       </c>
       <c r="G100">
         <v>62.2</v>
@@ -9487,37 +9487,37 @@
         <v>76.7</v>
       </c>
       <c r="M100">
-        <v>324.5343696</v>
+        <v>327.8459448</v>
       </c>
       <c r="N100">
-        <v>-247.8343696000001</v>
+        <v>-251.1459448</v>
       </c>
       <c r="O100">
-        <v>-79.30699827200002</v>
+        <v>-80.366702336</v>
       </c>
       <c r="P100">
-        <v>-168.527371328</v>
+        <v>-170.779242464</v>
       </c>
       <c r="Q100">
-        <v>-130.2273713280001</v>
+        <v>-132.479242464</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.056618754935175</v>
+        <v>4.06743750987035</v>
       </c>
       <c r="T100">
-        <v>26.2077092474573</v>
+        <v>52.41541849491459</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07562835341677783</v>
+        <v>0.07486443065499221</v>
       </c>
       <c r="W100">
-        <v>0.2179668342643238</v>
+        <v>0.2181469672515529</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2363386044274307</v>
+        <v>0.2339513457968506</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2566398726777409</v>
-      </c>
-      <c r="C101">
-        <v>-1056.099112858222</v>
-      </c>
-      <c r="D101">
-        <v>272.0568871417778</v>
-      </c>
-      <c r="E101">
-        <v>1261.356</v>
-      </c>
-      <c r="F101">
-        <v>1390.356</v>
-      </c>
-      <c r="G101">
-        <v>62.2</v>
-      </c>
-      <c r="H101">
-        <v>1275.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>115</v>
-      </c>
-      <c r="K101">
-        <v>38.3</v>
-      </c>
-      <c r="L101">
-        <v>76.7</v>
-      </c>
-      <c r="M101">
-        <v>327.8459448</v>
-      </c>
-      <c r="N101">
-        <v>-251.1459448</v>
-      </c>
-      <c r="O101">
-        <v>-80.366702336</v>
-      </c>
-      <c r="P101">
-        <v>-170.779242464</v>
-      </c>
-      <c r="Q101">
-        <v>-132.479242464</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.06743750987035</v>
-      </c>
-      <c r="T101">
-        <v>52.41541849491459</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07486443065499221</v>
-      </c>
-      <c r="W101">
-        <v>0.2181469672515529</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2339513457968506</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
